--- a/docs/MDS_Decision_Workbook.xlsx
+++ b/docs/MDS_Decision_Workbook.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="697">
   <si>
     <t xml:space="preserve">MDS decision workbook — Mess queue and allocation project (Group WGB3)</t>
   </si>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Output of our prototype's simulator</t>
   </si>
   <si>
-    <t xml:space="preserve">Average wait 7.0 → 1.1 min</t>
+    <t xml:space="preserve">Average wait 7.1 → 0.8 min</t>
   </si>
   <si>
     <t xml:space="preserve">Tabs and course sessions</t>
@@ -327,22 +327,28 @@
     <t xml:space="preserve">Group observation; normal day. Surges add queue time</t>
   </si>
   <si>
-    <t xml:space="preserve">Restock preparation lead time (low)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1 deck: 25–30 min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restock preparation lead time (high)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery time, kitchen to centre (low)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase 1 deck: 7–8 min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery time, kitchen to centre (high)</t>
+    <t xml:space="preserve">Restock after a 'running low' call: kitchen makes it and sends it (total)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group: the 30 min starts when the mess calls the kitchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restock when the food is already made: sending only (low)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group: 10–14 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restock when the food is already made: sending only (high)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chance the next batch is already made when the mess calls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulator default; ask CT how often food is cooked ahead</t>
   </si>
   <si>
     <t xml:space="preserve">Delay faced by students (observed)</t>
@@ -597,7 +603,7 @@
     <t xml:space="preserve">4. Why is it triggered late?</t>
   </si>
   <si>
-    <t xml:space="preserve">Lead time is 25–30 min prep + 7–8 min delivery, and the kitchen reacts to empty wells</t>
+    <t xml:space="preserve">The mess only calls the kitchen when the dish is running low; if it has to be made, the refill takes 30 min in total (10–14 min if already made)</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 1 deck</t>
@@ -1269,7 +1275,7 @@
     <t xml:space="preserve">Session 7: Decision making under certainty, risk and uncertainty (maximax, maximin, minimax regret, Hurwicz, Laplace, EMV, EVPI)</t>
   </si>
   <si>
-    <t xml:space="preserve">Everything on this tab is in MINUTES of waiting per student, so no rupee values are needed. Blue = input. S2 values for A1 and A2 come from our simulator (7.0 → 1.1 min); the other cells are illustrative estimates.</t>
+    <t xml:space="preserve">Everything on this tab is in MINUTES of waiting per student, so no rupee values are needed. Blue = input. S2 values for A1 and A2 come from our simulator (7.1 → 0.8 min); the other cells are illustrative estimates.</t>
   </si>
   <si>
     <t xml:space="preserve">Average wait per student (minutes)  [lower is better]</t>
@@ -1284,7 +1290,7 @@
     <t xml:space="preserve">S3 Surge + food run-out</t>
   </si>
   <si>
-    <t xml:space="preserve">Why these numbers: A1/A2 on a busy day are simulator results (Simulation Results tab). A surge with a run-out adds the 35-min restock gap, which screens can only partly hide (A2) and early kitchen alerts mostly prevent (A3). A 3rd station (A4) raises Central's serving capacity from 20 to 30/min but leaves the 85/15 imbalance and the single scanner. Replace with simulator runs or logs when available.</t>
+    <t xml:space="preserve">Why these numbers: A1/A2 on a busy day are simulator results (Simulation Results tab). A surge with a run-out adds the restock gap (up to 30 min after the call), which screens can only partly hide (A2) and early kitchen alerts mostly prevent (A3). A 3rd station (A4) raises Central's serving capacity from 20 to 30/min but leaves the 85/15 imbalance and the single scanner. Replace with simulator runs or logs when available.</t>
   </si>
   <si>
     <t xml:space="preserve">A1 No system (today)</t>
@@ -1428,7 +1434,7 @@
     <t xml:space="preserve">EMV of branch</t>
   </si>
   <si>
-    <t xml:space="preserve">□ Pre-stage extra batch at 12:30 (before the ~13:05 peak)</t>
+    <t xml:space="preserve">□ Cook the next batch ahead, before the ~13:05 peak (refill then takes 10–14 min, not 30)</t>
   </si>
   <si>
     <t xml:space="preserve">   ○ High-demand day</t>
@@ -1713,7 +1719,7 @@
     <t xml:space="preserve">Integer → optimal (same as ROUNDUP). Compare with today's 2 + 2 stations</t>
   </si>
   <si>
-    <t xml:space="preserve">If the integer answer needs more stations than exist today (2 per mess), the peak cannot meet the 85% target: that is the case for an extra station at peak (alternative A4) or for rebalancing with the screens. Replenishment trips can be modelled the same way: binary y(t) = 1 if the vehicle leaves at time t; each trip carries ≤ Q portions and must leave ≥ 25–30 min after cooking starts.</t>
+    <t xml:space="preserve">If the integer answer needs more stations than exist today (2 per mess), the peak cannot meet the 85% target: that is the case for an extra station at peak (alternative A4) or for rebalancing with the screens. Replenishment trips can be modelled the same way: binary y(t) = 1 if the vehicle leaves at time t; each trip carries ≤ Q portions and arrives 30 min after a call if it must be made, or 10–14 min if already made.</t>
   </si>
   <si>
     <t xml:space="preserve">AHP: weighting the decision criteria and ranking the alternatives</t>
@@ -1773,7 +1779,7 @@
     <t xml:space="preserve">Best alternative (AHP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Service-level scores can be anchored to the queuing results (S15) and the payoff matrix (S7): e.g. average wait 7.0 min → 3, 1.1 min → 8. Criteria come from our Phase 1 deck's weighted decision table.</t>
+    <t xml:space="preserve">Service-level scores can be anchored to the queuing results (S15) and the payoff matrix (S7): e.g. average wait 7.1 min → 3, 0.8 min → 8. Criteria come from our Phase 1 deck's weighted decision table.</t>
   </si>
   <si>
     <t xml:space="preserve">Best–Worst Method: the same criteria weights with fewer comparisons</t>
@@ -1971,7 +1977,7 @@
     <t xml:space="preserve">Central's serving capacity (2 stations × 10/min) — at peak the stations run flat out. Measure from trays issued per minute</t>
   </si>
   <si>
-    <t xml:space="preserve">Lead time = preparation + delivery (worst case, min)</t>
+    <t xml:space="preserve">Lead time from the call (worst case: has to be made, then sent, min)</t>
   </si>
   <si>
     <t xml:space="preserve">Safety margin</t>
@@ -1980,7 +1986,7 @@
     <t xml:space="preserve">Reorder point (portions left when the next batch must start)</t>
   </si>
   <si>
-    <t xml:space="preserve">Today the kitchen reacts to empty wells, so during the peak a batch arrives 32–38 min after the well empties.</t>
+    <t xml:space="preserve">Today the mess calls only when the dish is running low. If the kitchen then has to make it, the call must come this many portions before empty. If the batch is already made, the lead time is 10–14 min and the reorder point falls to about 40%.</t>
   </si>
   <si>
     <t xml:space="preserve">3. Heuristic vs full model (from 20 simulated lunches, door screens, 60% follow)</t>
@@ -2022,7 +2028,7 @@
     <t xml:space="preserve">Results from the prototype's simulator (simulated data, not measurements)</t>
   </si>
   <si>
-    <t xml:space="preserve">Feeds S7 (payoff anchors) and S18. 20 simulated lunches per row, 2,960 students, 11:30–14:30. Measured: students, seats, stations, scanners, 18-min visit, 35-min restock. Assumed: 85% habit, 10/min per station, 2 s per scan, arrival curve.</t>
+    <t xml:space="preserve">Feeds S7 (payoff anchors) and S18. 20 simulated lunches per row, 2,960 students, 11:30–14:30. Measured: students, seats, stations, scanners, 18-min visit, restock 30 min after a call (10–14 min if already made). Assumed: 85% habit, 10/min per station, 2 s per scan, 50% chance food is already made, arrival curve.</t>
   </si>
   <si>
     <t xml:space="preserve">Setting</t>
@@ -2079,7 +2085,46 @@
     <t xml:space="preserve">The spreadsheet model is simpler than the simulator (fixed 10-min bins, no stock-outs, no seat limit), so the two will not match exactly; both should show the same direction and rough size of improvement.</t>
   </si>
   <si>
-    <t xml:space="preserve">Two findings from the simulator: (1) Moving students moves the food run-outs: with screens Munch feeds more students and its 35-min restock causes about one extra run-out per lunch, so routing and food allocation (S10-11 LP) must be planned together. (2) The single face scanner (~30 scans/min at an assumed 2 s each) is close to Central's peak arrival rate, so a queue of 20–25 people can form OUTSIDE the scanner, which the biometric data cannot see.</t>
+    <t xml:space="preserve">Findings from the simulator: (1) Moving students moves the food run-outs: with screens Munch feeds more students and a 30-min call-back restock cannot keep up, so routing and food allocation (S10-11 LP) must be planned together; if the next batch is always made before the call (10–14 min to send), run-outs disappear in the model (table below). (2) The single face scanner (~30 scans/min at an assumed 2 s each) is close to Central's peak arrival rate, so a queue of 20–25 people can form OUTSIDE the scanner, which the biometric data cannot see.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next batch already made when the mess calls?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restock time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-outs, no screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-outs, screens (60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg wait no screens (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg wait screens (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Half the time (simulator default)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 or 10–14 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10–14 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reading: run-outs depend on whether the kitchen cooks ahead, not on the queue; waits barely move, because the serving stations set the queue. This is the case for early kitchen alerts (alternative A3) and for the pre-stage decision tree (S7).</t>
   </si>
 </sst>
 </file>
@@ -2827,11 +2872,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="64119581"/>
-        <c:axId val="28386906"/>
+        <c:axId val="5747881"/>
+        <c:axId val="12922687"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="64119581"/>
+        <c:axId val="5747881"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2897,7 +2942,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28386906"/>
+        <c:crossAx val="12922687"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2905,7 +2950,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28386906"/>
+        <c:axId val="12922687"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2981,7 +3026,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64119581"/>
+        <c:crossAx val="5747881"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3781,11 +3826,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74067484"/>
-        <c:axId val="88564475"/>
+        <c:axId val="1309127"/>
+        <c:axId val="65752071"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74067484"/>
+        <c:axId val="1309127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3817,7 +3862,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88564475"/>
+        <c:crossAx val="65752071"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3825,7 +3870,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88564475"/>
+        <c:axId val="65752071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3901,7 +3946,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74067484"/>
+        <c:crossAx val="1309127"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4079,16 +4124,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.2</c:v>
+                  <c:v>5.49</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.7</c:v>
+                  <c:v>5.99</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.25</c:v>
+                  <c:v>3.3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.77</c:v>
+                  <c:v>5.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4096,11 +4141,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="61818632"/>
-        <c:axId val="78407482"/>
+        <c:axId val="7307287"/>
+        <c:axId val="39068584"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="61818632"/>
+        <c:axId val="7307287"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4132,7 +4177,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78407482"/>
+        <c:crossAx val="39068584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4140,7 +4185,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78407482"/>
+        <c:axId val="39068584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4182,7 +4227,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61818632"/>
+        <c:crossAx val="7307287"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4538,11 +4583,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="50157218"/>
-        <c:axId val="46281188"/>
+        <c:axId val="56633981"/>
+        <c:axId val="29712866"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="50157218"/>
+        <c:axId val="56633981"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4574,7 +4619,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46281188"/>
+        <c:crossAx val="29712866"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4582,7 +4627,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46281188"/>
+        <c:axId val="29712866"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4624,7 +4669,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50157218"/>
+        <c:crossAx val="56633981"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4856,11 +4901,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="75676374"/>
-        <c:axId val="33661063"/>
+        <c:axId val="60833793"/>
+        <c:axId val="5964943"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="75676374"/>
+        <c:axId val="60833793"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4936,12 +4981,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33661063"/>
+        <c:crossAx val="5964943"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="33661063"/>
+        <c:axId val="5964943"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5017,7 +5062,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75676374"/>
+        <c:crossAx val="60833793"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5165,16 +5210,16 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>7</c:v>
+                  <c:v>7.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.5</c:v>
+                  <c:v>1.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>1.1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5182,11 +5227,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="42539193"/>
-        <c:axId val="75905116"/>
+        <c:axId val="17273015"/>
+        <c:axId val="27964619"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42539193"/>
+        <c:axId val="17273015"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5218,7 +5263,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75905116"/>
+        <c:crossAx val="27964619"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5226,7 +5271,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75905116"/>
+        <c:axId val="27964619"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5268,7 +5313,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42539193"/>
+        <c:crossAx val="17273015"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6021,7 +6066,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6036,12 +6081,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -6056,7 +6101,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -6071,7 +6116,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -6086,7 +6131,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -6101,37 +6146,37 @@
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6412,7 +6457,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F18" s="26" t="n">
         <f aca="false">SUM(F11:F16)</f>
@@ -6433,17 +6478,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F19" s="43" t="n">
         <f aca="false">(F18+G18)*Inputs!$B$35*Inputs!$B$34*0.5</f>
         <v>2850</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J19" s="43" t="n">
         <f aca="false">(J18+K18)*Inputs!$B$35*Inputs!$B$34*0.5</f>
@@ -6452,7 +6497,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J20" s="49" t="n">
         <f aca="false">F19-J19</f>
@@ -6461,7 +6506,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F21" s="27" t="n">
         <f aca="false">Inputs!$B$11</f>
@@ -6474,7 +6519,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F22" s="51" t="n">
         <f aca="false">MAX(F11:F16)</f>
@@ -6495,7 +6540,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -6510,7 +6555,7 @@
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -6525,18 +6570,18 @@
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6" t="s">
@@ -6548,7 +6593,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B28" s="7" t="str">
         <f aca="false">"LP relaxation, slot "&amp;INDEX($A$11:$A$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0))</f>
@@ -6565,7 +6610,7 @@
         <v>3.75</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
@@ -6573,7 +6618,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B29" s="7" t="str">
         <f aca="false">"Central ≤ "&amp;INT(INDEX($D$11:$D$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0)))</f>
@@ -6588,7 +6633,7 @@
         <v>28</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I29" s="23"/>
       <c r="J29" s="23"/>
@@ -6596,7 +6641,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B30" s="7" t="str">
         <f aca="false">"Central ≥ "&amp;ROUNDUP(INDEX($D$11:$D$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0)),0)</f>
@@ -6613,7 +6658,7 @@
         <v>4.56</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="I30" s="23"/>
       <c r="J30" s="23"/>
@@ -6621,7 +6666,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B31" s="7" t="str">
         <f aca="false">"Central ≥ "&amp;ROUNDUP(INDEX($D$11:$D$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0)),0)&amp;", Munch ≤ "&amp;INT(INDEX($E$11:$E$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0)))</f>
@@ -6636,7 +6681,7 @@
         <v>28</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
@@ -6661,7 +6706,7 @@
         <v>5</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I32" s="23"/>
       <c r="J32" s="23"/>
@@ -6669,7 +6714,7 @@
     </row>
     <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -6731,7 +6776,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6742,31 +6787,31 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B6" s="29" t="n">
         <v>1</v>
@@ -6783,7 +6828,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B7" s="29" t="n">
         <f aca="false">1/C6</f>
@@ -6801,7 +6846,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B8" s="29" t="n">
         <f aca="false">1/D6</f>
@@ -6820,7 +6865,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">1/E6</f>
@@ -6840,7 +6885,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B10" s="29" t="n">
         <f aca="false">SUM(B6:B9)</f>
@@ -6861,29 +6906,29 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B14" s="28" t="n">
         <f aca="false">B6/B$10</f>
@@ -6908,7 +6953,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">B7/B$10</f>
@@ -6933,7 +6978,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">B8/B$10</f>
@@ -6958,7 +7003,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B17" s="28" t="n">
         <f aca="false">B9/B$10</f>
@@ -6983,12 +7028,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B20" s="28" t="n">
         <f aca="false">B10*F14+C10*F15+D10*F16+E10*F17</f>
@@ -6997,7 +7042,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B21" s="55" t="n">
         <f aca="false">(B20-4)/3</f>
@@ -7006,7 +7051,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B22" s="53" t="n">
         <v>0.9</v>
@@ -7014,7 +7059,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B23" s="56" t="n">
         <f aca="false">B21/B22</f>
@@ -7027,35 +7072,35 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B27" s="16" t="n">
         <v>3</v>
@@ -7080,7 +7125,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B28" s="16" t="n">
         <v>7</v>
@@ -7105,7 +7150,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B29" s="16" t="n">
         <v>7</v>
@@ -7130,7 +7175,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>7</v>
@@ -7155,7 +7200,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B31" s="16" t="n">
         <v>9</v>
@@ -7180,7 +7225,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B33" s="45" t="str">
         <f aca="false">INDEX(A27:A31,MATCH(MAX(F27:F31),F27:F31,0))</f>
@@ -7192,7 +7237,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -7230,7 +7275,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7240,53 +7285,53 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>1</v>
@@ -7308,7 +7353,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>2</v>
@@ -7330,7 +7375,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>4</v>
@@ -7352,7 +7397,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>7</v>
@@ -7374,7 +7419,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D13" s="28" t="n">
         <f aca="false">SUM(D9:D12)</f>
@@ -7383,7 +7428,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D14" s="56" t="n">
         <f aca="false">MAX(E9:F12)</f>
@@ -7392,7 +7437,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D15" s="29" t="n">
         <f aca="false">INDEX({0,0.44,1,1.63,2.3,3,3.73,4.47,5.23},B12)</f>
@@ -7401,7 +7446,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D16" s="54" t="n">
         <f aca="false">D14/D15</f>
@@ -7410,7 +7455,7 @@
     </row>
     <row r="18" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -7420,26 +7465,26 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B22" s="28" t="n">
         <f aca="false">D9</f>
@@ -7456,7 +7501,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">D10</f>
@@ -7473,7 +7518,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B24" s="28" t="n">
         <f aca="false">D11</f>
@@ -7490,7 +7535,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B25" s="28" t="n">
         <f aca="false">D12</f>
@@ -7535,7 +7580,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7553,54 +7598,54 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B7" s="60" t="n">
         <v>1</v>
@@ -7635,7 +7680,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B8" s="60" t="n">
         <v>0</v>
@@ -7670,7 +7715,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B9" s="60" t="n">
         <v>0</v>
@@ -7705,7 +7750,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B10" s="60" t="n">
         <v>0</v>
@@ -7740,7 +7785,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B11" s="60" t="n">
         <v>0</v>
@@ -7775,7 +7820,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B12" s="60" t="n">
         <v>0</v>
@@ -7810,7 +7855,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B13" s="60" t="n">
         <v>0</v>
@@ -7845,7 +7890,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B14" s="60" t="n">
         <v>0</v>
@@ -7880,7 +7925,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B15" s="60" t="n">
         <v>0</v>
@@ -7915,7 +7960,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B16" s="60" t="n">
         <v>0</v>
@@ -7950,44 +7995,44 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B20" s="61" t="n">
         <f aca="false">IF(MMULT($B7:$K7,B$7:B$16)&gt;0,1,0)</f>
@@ -8032,7 +8077,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="59" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B21" s="61" t="n">
         <f aca="false">IF(MMULT($B8:$K8,B$7:B$16)&gt;0,1,0)</f>
@@ -8077,7 +8122,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B22" s="61" t="n">
         <f aca="false">IF(MMULT($B9:$K9,B$7:B$16)&gt;0,1,0)</f>
@@ -8122,7 +8167,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="59" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B23" s="61" t="n">
         <f aca="false">IF(MMULT($B10:$K10,B$7:B$16)&gt;0,1,0)</f>
@@ -8167,7 +8212,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B24" s="61" t="n">
         <f aca="false">IF(MMULT($B11:$K11,B$7:B$16)&gt;0,1,0)</f>
@@ -8212,7 +8257,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="59" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B25" s="61" t="n">
         <f aca="false">IF(MMULT($B12:$K12,B$7:B$16)&gt;0,1,0)</f>
@@ -8257,7 +8302,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="59" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B26" s="61" t="n">
         <f aca="false">IF(MMULT($B13:$K13,B$7:B$16)&gt;0,1,0)</f>
@@ -8302,7 +8347,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="59" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B27" s="61" t="n">
         <f aca="false">IF(MMULT($B14:$K14,B$7:B$16)&gt;0,1,0)</f>
@@ -8347,7 +8392,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B28" s="61" t="n">
         <f aca="false">IF(MMULT($B15:$K15,B$7:B$16)&gt;0,1,0)</f>
@@ -8392,7 +8437,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="59" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B29" s="61" t="n">
         <f aca="false">IF(MMULT($B16:$K16,B$7:B$16)&gt;0,1,0)</f>
@@ -8437,44 +8482,44 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="59" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B33" s="61" t="n">
         <f aca="false">IF(MMULT($B20:$K20,B$20:B$29)&gt;0,1,0)</f>
@@ -8519,7 +8564,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="59" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B34" s="61" t="n">
         <f aca="false">IF(MMULT($B21:$K21,B$20:B$29)&gt;0,1,0)</f>
@@ -8564,7 +8609,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="59" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B35" s="61" t="n">
         <f aca="false">IF(MMULT($B22:$K22,B$20:B$29)&gt;0,1,0)</f>
@@ -8609,7 +8654,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="59" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B36" s="61" t="n">
         <f aca="false">IF(MMULT($B23:$K23,B$20:B$29)&gt;0,1,0)</f>
@@ -8654,7 +8699,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="59" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B37" s="61" t="n">
         <f aca="false">IF(MMULT($B24:$K24,B$20:B$29)&gt;0,1,0)</f>
@@ -8699,7 +8744,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="59" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B38" s="61" t="n">
         <f aca="false">IF(MMULT($B25:$K25,B$20:B$29)&gt;0,1,0)</f>
@@ -8744,7 +8789,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="59" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B39" s="61" t="n">
         <f aca="false">IF(MMULT($B26:$K26,B$20:B$29)&gt;0,1,0)</f>
@@ -8789,7 +8834,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="59" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B40" s="61" t="n">
         <f aca="false">IF(MMULT($B27:$K27,B$20:B$29)&gt;0,1,0)</f>
@@ -8834,7 +8879,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="59" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B41" s="61" t="n">
         <f aca="false">IF(MMULT($B28:$K28,B$20:B$29)&gt;0,1,0)</f>
@@ -8879,7 +8924,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="59" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B42" s="61" t="n">
         <f aca="false">IF(MMULT($B29:$K29,B$20:B$29)&gt;0,1,0)</f>
@@ -8924,44 +8969,44 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="59" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B46" s="61" t="n">
         <f aca="false">IF(MMULT($B33:$K33,B$33:B$42)&gt;0,1,0)</f>
@@ -9006,7 +9051,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="59" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B47" s="61" t="n">
         <f aca="false">IF(MMULT($B34:$K34,B$33:B$42)&gt;0,1,0)</f>
@@ -9051,7 +9096,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="59" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B48" s="61" t="n">
         <f aca="false">IF(MMULT($B35:$K35,B$33:B$42)&gt;0,1,0)</f>
@@ -9096,7 +9141,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="59" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B49" s="61" t="n">
         <f aca="false">IF(MMULT($B36:$K36,B$33:B$42)&gt;0,1,0)</f>
@@ -9141,7 +9186,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="59" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B50" s="61" t="n">
         <f aca="false">IF(MMULT($B37:$K37,B$33:B$42)&gt;0,1,0)</f>
@@ -9186,7 +9231,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="59" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B51" s="61" t="n">
         <f aca="false">IF(MMULT($B38:$K38,B$33:B$42)&gt;0,1,0)</f>
@@ -9231,7 +9276,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="59" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B52" s="61" t="n">
         <f aca="false">IF(MMULT($B39:$K39,B$33:B$42)&gt;0,1,0)</f>
@@ -9276,7 +9321,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="59" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B53" s="61" t="n">
         <f aca="false">IF(MMULT($B40:$K40,B$33:B$42)&gt;0,1,0)</f>
@@ -9321,7 +9366,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="59" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B54" s="61" t="n">
         <f aca="false">IF(MMULT($B41:$K41,B$33:B$42)&gt;0,1,0)</f>
@@ -9366,7 +9411,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="59" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B55" s="61" t="n">
         <f aca="false">IF(MMULT($B42:$K42,B$33:B$42)&gt;0,1,0)</f>
@@ -9411,44 +9456,44 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="59" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B59" s="61" t="n">
         <f aca="false">IF(MMULT($B46:$K46,B$46:B$55)&gt;0,1,0)</f>
@@ -9493,7 +9538,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="59" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B60" s="61" t="n">
         <f aca="false">IF(MMULT($B47:$K47,B$46:B$55)&gt;0,1,0)</f>
@@ -9538,7 +9583,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="59" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B61" s="61" t="n">
         <f aca="false">IF(MMULT($B48:$K48,B$46:B$55)&gt;0,1,0)</f>
@@ -9583,7 +9628,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="59" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B62" s="61" t="n">
         <f aca="false">IF(MMULT($B49:$K49,B$46:B$55)&gt;0,1,0)</f>
@@ -9628,7 +9673,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="59" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B63" s="61" t="n">
         <f aca="false">IF(MMULT($B50:$K50,B$46:B$55)&gt;0,1,0)</f>
@@ -9673,7 +9718,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="59" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B64" s="61" t="n">
         <f aca="false">IF(MMULT($B51:$K51,B$46:B$55)&gt;0,1,0)</f>
@@ -9718,7 +9763,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="59" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B65" s="61" t="n">
         <f aca="false">IF(MMULT($B52:$K52,B$46:B$55)&gt;0,1,0)</f>
@@ -9763,7 +9808,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="59" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B66" s="61" t="n">
         <f aca="false">IF(MMULT($B53:$K53,B$46:B$55)&gt;0,1,0)</f>
@@ -9808,7 +9853,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="59" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B67" s="61" t="n">
         <f aca="false">IF(MMULT($B54:$K54,B$46:B$55)&gt;0,1,0)</f>
@@ -9853,7 +9898,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="59" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B68" s="61" t="n">
         <f aca="false">IF(MMULT($B55:$K55,B$46:B$55)&gt;0,1,0)</f>
@@ -9898,21 +9943,21 @@
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="L71" s="26" t="n">
         <f aca="false">SUM(B59:K59)</f>
@@ -9929,7 +9974,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L72" s="26" t="n">
         <f aca="false">SUM(B60:K60)</f>
@@ -9946,7 +9991,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L73" s="26" t="n">
         <f aca="false">SUM(B61:K61)</f>
@@ -9963,7 +10008,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L74" s="26" t="n">
         <f aca="false">SUM(B62:K62)</f>
@@ -9980,7 +10025,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="L75" s="26" t="n">
         <f aca="false">SUM(B63:K63)</f>
@@ -9997,7 +10042,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L76" s="26" t="n">
         <f aca="false">SUM(B64:K64)</f>
@@ -10014,7 +10059,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="L77" s="26" t="n">
         <f aca="false">SUM(B65:K65)</f>
@@ -10031,7 +10076,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="L78" s="26" t="n">
         <f aca="false">SUM(B66:K66)</f>
@@ -10048,7 +10093,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L79" s="26" t="n">
         <f aca="false">SUM(B67:K67)</f>
@@ -10065,7 +10110,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="L80" s="26" t="n">
         <f aca="false">SUM(B68:K68)</f>
@@ -10082,7 +10127,7 @@
     </row>
     <row r="82" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -10128,7 +10173,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10136,17 +10181,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B5" s="37" t="n">
         <v>6</v>
@@ -10154,7 +10199,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B6" s="37" t="n">
         <v>2</v>
@@ -10162,7 +10207,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B7" s="32" t="n">
         <f aca="false">Inputs!$B$26</f>
@@ -10171,7 +10216,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B8" s="32" t="n">
         <f aca="false">Inputs!$B$30</f>
@@ -10180,7 +10225,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">B5-(B6+B7)</f>
@@ -10189,7 +10234,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B10" s="45" t="str">
         <f aca="false">IF(B9&gt;=B8,"Other mess is faster → walk over",IF(B9&gt;0,"Small saving: stay","Come on in"))</f>
@@ -10200,33 +10245,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B13" s="32" t="n">
         <f aca="false">Inputs!$B$37</f>
         <v>20</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B14" s="27" t="n">
-        <f aca="false">Inputs!$B$17+Inputs!$B$19</f>
-        <v>38</v>
+        <f aca="false">Inputs!$B$16</f>
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B15" s="20" t="n">
         <v>0.2</v>
@@ -10234,14 +10279,14 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B16" s="51" t="n">
         <f aca="false">B13*B14*(1+B15)</f>
-        <v>912</v>
+        <v>720</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -10251,73 +10296,73 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B21" s="37" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="C21" s="37" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B22" s="37" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C22" s="37" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B23" s="37" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="C23" s="37" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -10344,7 +10389,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -10353,7 +10398,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10364,174 +10409,174 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C5" s="37" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="D5" s="37" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="E5" s="20" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>495</v>
+        <v>406</v>
       </c>
       <c r="G5" s="37" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B6" s="20" t="n">
         <v>0.3</v>
       </c>
       <c r="C6" s="37" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="D6" s="37" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="20" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>235</v>
+        <v>133</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B7" s="20" t="n">
         <v>0.6</v>
       </c>
       <c r="C7" s="37" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="D7" s="37" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>190</v>
+        <v>97</v>
       </c>
       <c r="G7" s="37" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B8" s="20" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="37" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="D8" s="37" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="E8" s="20" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>187</v>
+        <v>98</v>
       </c>
       <c r="G8" s="37" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C10" s="62" t="n">
         <f aca="false">1-C7/C5</f>
-        <v>0.842857142857143</v>
+        <v>0.887323943661972</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B13" s="37" t="n">
-        <v>20</v>
+        <v>18.3</v>
       </c>
       <c r="C13" s="37" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B14" s="37" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="C14" s="37" t="n">
-        <v>19.6</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C17" s="32" t="n">
         <f aca="false">'S15 Queuing'!$H$51</f>
@@ -10540,7 +10585,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C18" s="32" t="n">
         <f aca="false">'S15 Queuing'!$I$51</f>
@@ -10549,7 +10594,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -10558,17 +10603,108 @@
     </row>
     <row r="21" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>690</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="C25" s="37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="37" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" s="37" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="C26" s="37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D26" s="37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E26" s="37" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="F26" s="37" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="C27" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F27" s="37" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10807,7 +10943,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="16" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>82</v>
@@ -10824,7 +10960,7 @@
         <v>99</v>
       </c>
       <c r="B17" s="16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>82</v>
@@ -10833,15 +10969,15 @@
         <v>11</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" s="16" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>82</v>
@@ -10850,29 +10986,29 @@
         <v>11</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>8</v>
+      <c r="B19" s="17" t="n">
+        <v>0.5</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>11</v>
+        <v>103</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>15</v>
@@ -10884,68 +11020,68 @@
         <v>11</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B22" s="17" t="n">
         <v>0.85</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B23" s="18" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B25" s="19" t="n">
         <v>17</v>
@@ -10954,15 +11090,15 @@
         <v>82</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>0.5</v>
@@ -10974,51 +11110,51 @@
         <v>14</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B27" s="17" t="n">
         <v>0.6</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B29" s="20" t="n">
         <v>0.85</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>2</v>
@@ -11027,170 +11163,170 @@
         <v>82</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B32" s="21" t="n">
         <v>5</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B33" s="21" t="n">
         <v>30</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B34" s="21" t="n">
         <v>150</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B35" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B37" s="22" t="n">
         <f aca="false">B11*B23</f>
         <v>20</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B38" s="22" t="n">
         <f aca="false">B12*B23</f>
         <v>20</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B39" s="22" t="n">
         <f aca="false">Inputs!$B$9/Inputs!$B$15</f>
         <v>50</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B40" s="22" t="n">
         <f aca="false">Inputs!$B$10/Inputs!$B$15</f>
         <v>27.7777777777778</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B41" s="22" t="n">
         <f aca="false">Inputs!$B$13*60/Inputs!$B$24</f>
         <v>30</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B42" s="22" t="n">
         <f aca="false">Inputs!$B$14*60/Inputs!$B$24</f>
         <v>30</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -11225,7 +11361,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11234,17 +11370,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -11253,296 +11389,296 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>58</v>
@@ -11577,104 +11713,104 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>71</v>
@@ -11682,68 +11818,68 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -11774,7 +11910,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11784,37 +11920,37 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>20</v>
@@ -11824,15 +11960,15 @@
         <v>0.194174757281553</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>16</v>
@@ -11842,15 +11978,15 @@
         <v>0.155339805825243</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>40</v>
@@ -11860,15 +11996,15 @@
         <v>0.388349514563107</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>27</v>
@@ -11878,12 +12014,12 @@
         <v>0.262135922330097</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="26" t="n">
@@ -11898,12 +12034,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>3</v>
@@ -11911,27 +12047,27 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B16" s="24" t="n">
         <v>4</v>
@@ -11944,15 +12080,15 @@
         <v>Quick win</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B17" s="24" t="n">
         <v>5</v>
@@ -11965,15 +12101,15 @@
         <v>Quick win</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B18" s="24" t="n">
         <v>4</v>
@@ -11986,15 +12122,15 @@
         <v>Major project</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B19" s="24" t="n">
         <v>3</v>
@@ -12007,15 +12143,15 @@
         <v>Fill-in</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B20" s="24" t="n">
         <v>4</v>
@@ -12028,15 +12164,15 @@
         <v>Major project</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B21" s="24" t="n">
         <v>2</v>
@@ -12049,87 +12185,87 @@
         <v>Fill-in</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -12157,7 +12293,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12192,44 +12328,44 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K5" s="27" t="n">
         <f aca="false">Inputs!$B$23*60</f>
@@ -12268,21 +12404,21 @@
         <v>3</v>
       </c>
       <c r="J6" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>346</v>
-      </c>
       <c r="L6" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -12496,12 +12632,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -12535,14 +12671,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E25" s="30" t="n">
         <f aca="false">Inputs!$B$37/(Inputs!$B$37+Inputs!$B$38)</f>
         <v>0.5</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -12555,14 +12691,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E26" s="30" t="n">
         <f aca="false">Inputs!$B$22+Inputs!$B$27*(E25-Inputs!$B$22)</f>
         <v>0.64</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -12575,7 +12711,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D28" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
@@ -12585,7 +12721,7 @@
       <c r="J28" s="31"/>
       <c r="K28" s="31"/>
       <c r="L28" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M28" s="31"/>
       <c r="N28" s="31"/>
@@ -12595,7 +12731,7 @@
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="31" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="U28" s="31"/>
       <c r="V28" s="31"/>
@@ -12605,7 +12741,7 @@
       <c r="Z28" s="31"/>
       <c r="AA28" s="31"/>
       <c r="AB28" s="31" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AC28" s="31"/>
       <c r="AD28" s="31"/>
@@ -12617,109 +12753,109 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G29" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="M29" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="N29" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="O29" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="P29" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="Q29" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="L29" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="N29" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="O29" s="6" t="s">
+      <c r="R29" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="S29" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="T29" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="P29" s="6" t="s">
+      <c r="U29" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="Q29" s="6" t="s">
+      <c r="V29" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="W29" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="R29" s="6" t="s">
+      <c r="X29" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="S29" s="6" t="s">
+      <c r="Y29" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="T29" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="U29" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="V29" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="W29" s="6" t="s">
+      <c r="Z29" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="AA29" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="AB29" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="X29" s="6" t="s">
+      <c r="AC29" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="Y29" s="6" t="s">
+      <c r="AD29" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="AE29" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="Z29" s="6" t="s">
+      <c r="AF29" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="AA29" s="6" t="s">
+      <c r="AG29" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="AB29" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="AC29" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="AD29" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="AE29" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="AF29" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="AG29" s="6" t="s">
-        <v>373</v>
-      </c>
       <c r="AH29" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AI29" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12864,7 +13000,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B31" s="16" t="n">
         <v>25</v>
@@ -13004,7 +13140,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B32" s="16" t="n">
         <v>47</v>
@@ -13144,7 +13280,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>79</v>
@@ -13284,7 +13420,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>123</v>
@@ -13424,7 +13560,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B35" s="16" t="n">
         <v>178</v>
@@ -13564,7 +13700,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B36" s="16" t="n">
         <v>236</v>
@@ -13704,7 +13840,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B37" s="16" t="n">
         <v>289</v>
@@ -13844,7 +13980,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B38" s="16" t="n">
         <v>326</v>
@@ -13984,7 +14120,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B39" s="16" t="n">
         <v>340</v>
@@ -14124,7 +14260,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B40" s="16" t="n">
         <v>326</v>
@@ -14264,7 +14400,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B41" s="16" t="n">
         <v>289</v>
@@ -14404,7 +14540,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B42" s="16" t="n">
         <v>236</v>
@@ -14544,7 +14680,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B43" s="16" t="n">
         <v>178</v>
@@ -14684,7 +14820,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B44" s="16" t="n">
         <v>123</v>
@@ -14824,7 +14960,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B45" s="16" t="n">
         <v>79</v>
@@ -14964,7 +15100,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B46" s="16" t="n">
         <v>47</v>
@@ -15104,7 +15240,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B47" s="16" t="n">
         <v>25</v>
@@ -15244,37 +15380,37 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -15305,7 +15441,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -15328,7 +15464,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -15351,7 +15487,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -15374,7 +15510,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -15397,7 +15533,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -15420,7 +15556,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -15443,7 +15579,7 @@
     </row>
     <row r="59" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -15503,7 +15639,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15517,12 +15653,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -15536,19 +15672,19 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -15557,13 +15693,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B7" s="37" t="n">
         <v>2.5</v>
       </c>
       <c r="C7" s="37" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="D7" s="37" t="n">
         <v>15</v>
@@ -15576,13 +15712,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B8" s="37" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C8" s="37" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="D8" s="37" t="n">
         <v>6</v>
@@ -15595,13 +15731,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B9" s="37" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C9" s="37" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="D9" s="37" t="n">
         <v>3.5</v>
@@ -15614,7 +15750,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B10" s="37" t="n">
         <v>1.5</v>
@@ -15633,13 +15769,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B11" s="37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C11" s="37" t="n">
         <v>0.6</v>
-      </c>
-      <c r="C11" s="37" t="n">
-        <v>0.8</v>
       </c>
       <c r="D11" s="37" t="n">
         <v>4.5</v>
@@ -15647,21 +15783,21 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B14" s="20" t="n">
         <v>0.3</v>
@@ -15677,12 +15813,12 @@
         <v>1</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -15691,44 +15827,44 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">B$7-B7</f>
@@ -15769,15 +15905,15 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">B$7-B8</f>
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">C$7-C8</f>
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="D20" s="22" t="n">
         <f aca="false">D$7-D8</f>
@@ -15789,36 +15925,36 @@
       </c>
       <c r="F20" s="22" t="n">
         <f aca="false">MIN(B20:D20)</f>
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G20" s="22" t="n">
         <f aca="false">$B$26*E20+(1-$B$26)*F20</f>
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="H20" s="22" t="n">
         <f aca="false">AVERAGE(B20:D20)</f>
-        <v>5.46666666666667</v>
+        <v>5.7</v>
       </c>
       <c r="I20" s="29" t="n">
         <f aca="false">SUMPRODUCT(B20:D20,$B$14:$D$14)</f>
-        <v>5.2</v>
+        <v>5.49</v>
       </c>
       <c r="J20" s="40" t="n">
         <f aca="false">I20*$B$15/60</f>
-        <v>256.533333333333</v>
+        <v>270.84</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">B$7-B9</f>
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="C21" s="22" t="n">
         <f aca="false">C$7-C9</f>
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="D21" s="22" t="n">
         <f aca="false">D$7-D9</f>
@@ -15830,28 +15966,28 @@
       </c>
       <c r="F21" s="22" t="n">
         <f aca="false">MIN(B21:D21)</f>
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G21" s="22" t="n">
         <f aca="false">$B$26*E21+(1-$B$26)*F21</f>
-        <v>5.5</v>
+        <v>5.68</v>
       </c>
       <c r="H21" s="22" t="n">
         <f aca="false">AVERAGE(B21:D21)</f>
-        <v>6.3</v>
+        <v>6.53333333333333</v>
       </c>
       <c r="I21" s="29" t="n">
         <f aca="false">SUMPRODUCT(B21:D21,$B$14:$D$14)</f>
-        <v>5.7</v>
+        <v>5.99</v>
       </c>
       <c r="J21" s="40" t="n">
         <f aca="false">I21*$B$15/60</f>
-        <v>281.2</v>
+        <v>295.506666666667</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B22" s="22" t="n">
         <f aca="false">B$7-B10</f>
@@ -15859,7 +15995,7 @@
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">C$7-C10</f>
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">D$7-D10</f>
@@ -15879,28 +16015,28 @@
       </c>
       <c r="H22" s="22" t="n">
         <f aca="false">AVERAGE(B22:D22)</f>
-        <v>3.5</v>
+        <v>3.53333333333333</v>
       </c>
       <c r="I22" s="29" t="n">
         <f aca="false">SUMPRODUCT(B22:D22,$B$14:$D$14)</f>
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J22" s="40" t="n">
         <f aca="false">I22*$B$15/60</f>
-        <v>160.333333333333</v>
+        <v>162.8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B23" s="22" t="n">
         <f aca="false">B$7-B11</f>
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">C$7-C11</f>
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="D23" s="22" t="n">
         <f aca="false">D$7-D11</f>
@@ -15912,28 +16048,28 @@
       </c>
       <c r="F23" s="22" t="n">
         <f aca="false">MIN(B23:D23)</f>
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G23" s="22" t="n">
         <f aca="false">$B$26*E23+(1-$B$26)*F23</f>
-        <v>5.34</v>
+        <v>5.4</v>
       </c>
       <c r="H23" s="22" t="n">
         <f aca="false">AVERAGE(B23:D23)</f>
-        <v>6.2</v>
+        <v>6.33333333333333</v>
       </c>
       <c r="I23" s="29" t="n">
         <f aca="false">SUMPRODUCT(B23:D23,$B$14:$D$14)</f>
-        <v>5.77</v>
+        <v>5.95</v>
       </c>
       <c r="J23" s="40" t="n">
         <f aca="false">I23*$B$15/60</f>
-        <v>284.653333333333</v>
+        <v>293.533333333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E24" s="41" t="str">
         <f aca="false">INDEX($A$19:$A$23,MATCH(MAX(E19:E23),E19:E23,0))</f>
@@ -15953,12 +16089,12 @@
       </c>
       <c r="I24" s="41" t="str">
         <f aca="false">INDEX($A$19:$A$23,MATCH(MAX(I19:I23),I19:I23,0))</f>
-        <v>A5 Screens + 3rd serving station</v>
+        <v>A3 Screens + kitchen early alerts</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B26" s="37" t="n">
         <v>0.4</v>
@@ -15966,40 +16102,40 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B19</f>
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="C30" s="22" t="n">
         <f aca="false">MAX(C$19:C$23)-C19</f>
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="D30" s="22" t="n">
         <f aca="false">MAX(D$19:D$23)-D19</f>
@@ -16011,20 +16147,20 @@
       </c>
       <c r="F30" s="29" t="n">
         <f aca="false">SUMPRODUCT(B30:D30,$B$14:$D$14)</f>
-        <v>5.97</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B31" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B20</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C31" s="22" t="n">
         <f aca="false">MAX(C$19:C$23)-C20</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D31" s="22" t="n">
         <f aca="false">MAX(D$19:D$23)-D20</f>
@@ -16036,20 +16172,20 @@
       </c>
       <c r="F31" s="29" t="n">
         <f aca="false">SUMPRODUCT(B31:D31,$B$14:$D$14)</f>
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B32" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B21</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C32" s="22" t="n">
         <f aca="false">MAX(C$19:C$23)-C21</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D32" s="22" t="n">
         <f aca="false">MAX(D$19:D$23)-D21</f>
@@ -16057,24 +16193,24 @@
       </c>
       <c r="E32" s="22" t="n">
         <f aca="false">MAX(B32:D32)</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F32" s="29" t="n">
         <f aca="false">SUMPRODUCT(B32:D32,$B$14:$D$14)</f>
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B33" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B22</f>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C33" s="22" t="n">
         <f aca="false">MAX(C$19:C$23)-C22</f>
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="D33" s="22" t="n">
         <f aca="false">MAX(D$19:D$23)-D22</f>
@@ -16086,12 +16222,12 @@
       </c>
       <c r="F33" s="29" t="n">
         <f aca="false">SUMPRODUCT(B33:D33,$B$14:$D$14)</f>
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B34" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B23</f>
@@ -16116,7 +16252,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E35" s="41" t="str">
         <f aca="false">INDEX($A$30:$A$34,MATCH(MIN(E30:E34),E30:E34,0))</f>
@@ -16125,57 +16261,57 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F36" s="41" t="str">
         <f aca="false">INDEX($A$30:$A$34,MATCH(MIN(F30:F34),F30:F34,0))</f>
-        <v>A5 Screens + 3rd serving station</v>
+        <v>A3 Screens + kitchen early alerts</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B39" s="29" t="n">
         <f aca="false">B14*MAX(B19:B23)+C14*MAX(C19:C23)+D14*MAX(D19:D23)</f>
-        <v>5.97</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B40" s="29" t="n">
         <f aca="false">MAX(I19:I23)</f>
-        <v>5.77</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B41" s="42" t="n">
         <f aca="false">B39-B40</f>
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B42" s="29" t="n">
         <f aca="false">MIN(F30:F34)</f>
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -16219,7 +16355,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16229,15 +16365,15 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -16246,13 +16382,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B5" s="20" t="n">
         <v>0.4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -16265,13 +16401,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -16284,13 +16420,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>300</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -16303,13 +16439,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -16322,7 +16458,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B9" s="43" t="n">
         <f aca="false">Inputs!$B$33</f>
@@ -16336,7 +16472,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B10" s="43" t="n">
         <f aca="false">Inputs!$B$32</f>
@@ -16357,7 +16493,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -16367,19 +16503,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -16389,7 +16525,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="44"/>
@@ -16406,7 +16542,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">B5</f>
@@ -16424,7 +16560,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">1-B5</f>
@@ -16442,7 +16578,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B17" s="25"/>
       <c r="C17" s="44"/>
@@ -16454,7 +16590,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">B5</f>
@@ -16472,7 +16608,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">1-B5</f>
@@ -16490,7 +16626,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B21" s="45" t="str">
         <f aca="false">IF(E14&lt;=E17,"Pre-stage","Wait and react")</f>
@@ -16499,14 +16635,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B22" s="46" t="n">
         <f aca="false">(C16-C19)/((C16-C19)+(C18-C15))</f>
         <v>0.0740740740740741</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -16514,21 +16650,21 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16753,7 +16889,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16763,17 +16899,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -16783,7 +16919,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -16793,7 +16929,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -16803,12 +16939,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B10" s="13" t="n">
         <v>1000</v>
@@ -16816,13 +16952,13 @@
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B11" s="13" t="n">
         <v>650</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -16830,7 +16966,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>400</v>
@@ -16842,7 +16978,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B13" s="47" t="n">
         <v>60</v>
@@ -16850,7 +16986,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B14" s="47" t="n">
         <v>45</v>
@@ -16858,12 +16994,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B17" s="48" t="n">
         <v>650</v>
@@ -16871,7 +17007,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B18" s="48" t="n">
         <v>350</v>
@@ -16879,7 +17015,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B19" s="49" t="n">
         <f aca="false">B13*B17+B14*B18</f>
@@ -16888,36 +17024,36 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B23" s="40" t="n">
         <f aca="false">B17+B18</f>
         <v>1000</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D23" s="40" t="n">
         <f aca="false">B10</f>
@@ -16930,14 +17066,14 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B24" s="40" t="n">
         <f aca="false">B17</f>
         <v>650</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D24" s="40" t="n">
         <f aca="false">B11</f>
@@ -16950,14 +17086,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B25" s="40" t="n">
         <f aca="false">B18</f>
         <v>350</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D25" s="40" t="n">
         <f aca="false">B12</f>
@@ -16970,17 +17106,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B26" s="40" t="n">
         <f aca="false">MIN(B17:B18)</f>
         <v>350</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E26" s="7" t="str">
         <f aca="false">IF(B26&gt;=0,"OK","Violated")</f>
@@ -16989,29 +17125,29 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B30" s="40" t="n">
         <v>0</v>
@@ -17030,7 +17166,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B31" s="40" t="n">
         <f aca="false">B11</f>
@@ -17050,7 +17186,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B32" s="40" t="n">
         <f aca="false">B11</f>
@@ -17071,7 +17207,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B33" s="40" t="n">
         <f aca="false">MIN(B11,B10-B12)</f>
@@ -17092,7 +17228,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B34" s="40" t="n">
         <v>0</v>
@@ -17112,7 +17248,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B36" s="41" t="str">
         <f aca="false">INDEX(A30:A34,MATCH(MAX(E30:E34),E30:E34,0))</f>
@@ -17124,7 +17260,7 @@
     </row>
     <row r="38" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -17134,12 +17270,12 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>

--- a/docs/MDS_Decision_Workbook.xlsx
+++ b/docs/MDS_Decision_Workbook.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="699">
   <si>
     <t xml:space="preserve">MDS decision workbook — Mess queue and allocation project (Group WGB3)</t>
   </si>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Output of our prototype's simulator</t>
   </si>
   <si>
-    <t xml:space="preserve">Average wait 7.1 → 0.8 min</t>
+    <t xml:space="preserve">Average wait 7.2 → 0.8 min</t>
   </si>
   <si>
     <t xml:space="preserve">Tabs and course sessions</t>
@@ -348,7 +348,10 @@
     <t xml:space="preserve">share</t>
   </si>
   <si>
-    <t xml:space="preserve">Simulator default; ask CT how often food is cooked ahead</t>
+    <t xml:space="preserve">Group estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group: food is already made about 70% of the time</t>
   </si>
   <si>
     <t xml:space="preserve">Delay faced by students (observed)</t>
@@ -1275,7 +1278,7 @@
     <t xml:space="preserve">Session 7: Decision making under certainty, risk and uncertainty (maximax, maximin, minimax regret, Hurwicz, Laplace, EMV, EVPI)</t>
   </si>
   <si>
-    <t xml:space="preserve">Everything on this tab is in MINUTES of waiting per student, so no rupee values are needed. Blue = input. S2 values for A1 and A2 come from our simulator (7.1 → 0.8 min); the other cells are illustrative estimates.</t>
+    <t xml:space="preserve">Everything on this tab is in MINUTES of waiting per student, so no rupee values are needed. Blue = input. S2 values for A1 and A2 come from our simulator (7.2 → 0.8 min); the other cells are illustrative estimates.</t>
   </si>
   <si>
     <t xml:space="preserve">Average wait per student (minutes)  [lower is better]</t>
@@ -1779,7 +1782,7 @@
     <t xml:space="preserve">Best alternative (AHP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Service-level scores can be anchored to the queuing results (S15) and the payoff matrix (S7): e.g. average wait 7.1 min → 3, 0.8 min → 8. Criteria come from our Phase 1 deck's weighted decision table.</t>
+    <t xml:space="preserve">Service-level scores can be anchored to the queuing results (S15) and the payoff matrix (S7): e.g. average wait 7.2 min → 3, 0.8 min → 8. Criteria come from our Phase 1 deck's weighted decision table.</t>
   </si>
   <si>
     <t xml:space="preserve">Best–Worst Method: the same criteria weights with fewer comparisons</t>
@@ -2028,7 +2031,7 @@
     <t xml:space="preserve">Results from the prototype's simulator (simulated data, not measurements)</t>
   </si>
   <si>
-    <t xml:space="preserve">Feeds S7 (payoff anchors) and S18. 20 simulated lunches per row, 2,960 students, 11:30–14:30. Measured: students, seats, stations, scanners, 18-min visit, restock 30 min after a call (10–14 min if already made). Assumed: 85% habit, 10/min per station, 2 s per scan, 50% chance food is already made, arrival curve.</t>
+    <t xml:space="preserve">Feeds S7 (payoff anchors) and S18. 20 simulated lunches per row, 2,960 students, 11:30–14:30. Measured: students, seats, stations, scanners, 18-min visit, restock 30 min after a call (10–14 min if already made). Assumed: 85% habit, 10/min per station, 2 s per scan, arrival curve. Group estimate: food already made 70% of the time.</t>
   </si>
   <si>
     <t xml:space="preserve">Setting</t>
@@ -2112,10 +2115,13 @@
     <t xml:space="preserve">30 min</t>
   </si>
   <si>
-    <t xml:space="preserve">Half the time (simulator default)</t>
+    <t xml:space="preserve">Half the time</t>
   </si>
   <si>
     <t xml:space="preserve">30 or 10–14 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70% of the time (group estimate, default)</t>
   </si>
   <si>
     <t xml:space="preserve">Always</t>
@@ -2420,6 +2426,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2429,10 +2439,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2872,11 +2878,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="5747881"/>
-        <c:axId val="12922687"/>
+        <c:axId val="62409454"/>
+        <c:axId val="29120686"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="5747881"/>
+        <c:axId val="62409454"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2942,7 +2948,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12922687"/>
+        <c:crossAx val="29120686"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2950,7 +2956,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12922687"/>
+        <c:axId val="29120686"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3026,7 +3032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5747881"/>
+        <c:crossAx val="62409454"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3826,11 +3832,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="1309127"/>
-        <c:axId val="65752071"/>
+        <c:axId val="48426104"/>
+        <c:axId val="91551624"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1309127"/>
+        <c:axId val="48426104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3862,7 +3868,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65752071"/>
+        <c:crossAx val="91551624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3870,7 +3876,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65752071"/>
+        <c:axId val="91551624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3946,7 +3952,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1309127"/>
+        <c:crossAx val="48426104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4124,16 +4130,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.49</c:v>
+                  <c:v>5.54</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.99</c:v>
+                  <c:v>6.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.3</c:v>
+                  <c:v>3.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.95</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4141,11 +4147,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="7307287"/>
-        <c:axId val="39068584"/>
+        <c:axId val="74992750"/>
+        <c:axId val="66402931"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="7307287"/>
+        <c:axId val="74992750"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4177,7 +4183,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39068584"/>
+        <c:crossAx val="66402931"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4185,7 +4191,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39068584"/>
+        <c:axId val="66402931"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4227,7 +4233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7307287"/>
+        <c:crossAx val="74992750"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4583,11 +4589,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="56633981"/>
-        <c:axId val="29712866"/>
+        <c:axId val="61766926"/>
+        <c:axId val="59186027"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="56633981"/>
+        <c:axId val="61766926"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4619,7 +4625,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29712866"/>
+        <c:crossAx val="59186027"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4627,7 +4633,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29712866"/>
+        <c:axId val="59186027"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4669,7 +4675,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56633981"/>
+        <c:crossAx val="61766926"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4901,11 +4907,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="60833793"/>
-        <c:axId val="5964943"/>
+        <c:axId val="19812427"/>
+        <c:axId val="70670018"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="60833793"/>
+        <c:axId val="19812427"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4981,12 +4987,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5964943"/>
+        <c:crossAx val="70670018"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="5964943"/>
+        <c:axId val="70670018"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5062,7 +5068,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60833793"/>
+        <c:crossAx val="19812427"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5210,16 +5216,16 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>7.1</c:v>
+                  <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.3</c:v>
+                  <c:v>1.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.1</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5227,11 +5233,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17273015"/>
-        <c:axId val="27964619"/>
+        <c:axId val="22127919"/>
+        <c:axId val="95985930"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17273015"/>
+        <c:axId val="22127919"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5263,7 +5269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27964619"/>
+        <c:crossAx val="95985930"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5271,7 +5277,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27964619"/>
+        <c:axId val="95985930"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5313,7 +5319,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17273015"/>
+        <c:crossAx val="22127919"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6066,7 +6072,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6081,12 +6087,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -6101,7 +6107,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -6116,7 +6122,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -6131,7 +6137,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -6146,37 +6152,37 @@
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6457,7 +6463,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F18" s="26" t="n">
         <f aca="false">SUM(F11:F16)</f>
@@ -6478,17 +6484,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F19" s="43" t="n">
         <f aca="false">(F18+G18)*Inputs!$B$35*Inputs!$B$34*0.5</f>
         <v>2850</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J19" s="43" t="n">
         <f aca="false">(J18+K18)*Inputs!$B$35*Inputs!$B$34*0.5</f>
@@ -6497,7 +6503,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J20" s="49" t="n">
         <f aca="false">F19-J19</f>
@@ -6506,7 +6512,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F21" s="27" t="n">
         <f aca="false">Inputs!$B$11</f>
@@ -6519,7 +6525,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F22" s="51" t="n">
         <f aca="false">MAX(F11:F16)</f>
@@ -6540,7 +6546,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -6555,7 +6561,7 @@
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -6570,18 +6576,18 @@
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6" t="s">
@@ -6593,7 +6599,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B28" s="7" t="str">
         <f aca="false">"LP relaxation, slot "&amp;INDEX($A$11:$A$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0))</f>
@@ -6610,7 +6616,7 @@
         <v>3.75</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I28" s="23"/>
       <c r="J28" s="23"/>
@@ -6618,7 +6624,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B29" s="7" t="str">
         <f aca="false">"Central ≤ "&amp;INT(INDEX($D$11:$D$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0)))</f>
@@ -6633,7 +6639,7 @@
         <v>28</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I29" s="23"/>
       <c r="J29" s="23"/>
@@ -6641,7 +6647,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B30" s="7" t="str">
         <f aca="false">"Central ≥ "&amp;ROUNDUP(INDEX($D$11:$D$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0)),0)</f>
@@ -6658,7 +6664,7 @@
         <v>4.56</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I30" s="23"/>
       <c r="J30" s="23"/>
@@ -6666,7 +6672,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B31" s="7" t="str">
         <f aca="false">"Central ≥ "&amp;ROUNDUP(INDEX($D$11:$D$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0)),0)&amp;", Munch ≤ "&amp;INT(INDEX($E$11:$E$16,MATCH(MAX($B$11:$B$16),$B$11:$B$16,0)))</f>
@@ -6681,7 +6687,7 @@
         <v>28</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
@@ -6706,7 +6712,7 @@
         <v>5</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I32" s="23"/>
       <c r="J32" s="23"/>
@@ -6714,7 +6720,7 @@
     </row>
     <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -6776,7 +6782,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6787,31 +6793,31 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B6" s="29" t="n">
         <v>1</v>
@@ -6828,7 +6834,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B7" s="29" t="n">
         <f aca="false">1/C6</f>
@@ -6846,7 +6852,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B8" s="29" t="n">
         <f aca="false">1/D6</f>
@@ -6865,7 +6871,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">1/E6</f>
@@ -6885,7 +6891,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B10" s="29" t="n">
         <f aca="false">SUM(B6:B9)</f>
@@ -6906,29 +6912,29 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B14" s="28" t="n">
         <f aca="false">B6/B$10</f>
@@ -6953,7 +6959,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">B7/B$10</f>
@@ -6978,7 +6984,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">B8/B$10</f>
@@ -7003,7 +7009,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B17" s="28" t="n">
         <f aca="false">B9/B$10</f>
@@ -7028,12 +7034,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B20" s="28" t="n">
         <f aca="false">B10*F14+C10*F15+D10*F16+E10*F17</f>
@@ -7042,7 +7048,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B21" s="55" t="n">
         <f aca="false">(B20-4)/3</f>
@@ -7051,7 +7057,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B22" s="53" t="n">
         <v>0.9</v>
@@ -7059,7 +7065,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B23" s="56" t="n">
         <f aca="false">B21/B22</f>
@@ -7072,35 +7078,35 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B27" s="16" t="n">
         <v>3</v>
@@ -7125,7 +7131,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B28" s="16" t="n">
         <v>7</v>
@@ -7150,7 +7156,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B29" s="16" t="n">
         <v>7</v>
@@ -7175,7 +7181,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>7</v>
@@ -7200,7 +7206,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B31" s="16" t="n">
         <v>9</v>
@@ -7225,7 +7231,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B33" s="45" t="str">
         <f aca="false">INDEX(A27:A31,MATCH(MAX(F27:F31),F27:F31,0))</f>
@@ -7237,7 +7243,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -7275,7 +7281,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7285,53 +7291,53 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>1</v>
@@ -7353,7 +7359,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>2</v>
@@ -7375,7 +7381,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>4</v>
@@ -7397,7 +7403,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>7</v>
@@ -7419,7 +7425,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D13" s="28" t="n">
         <f aca="false">SUM(D9:D12)</f>
@@ -7428,7 +7434,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D14" s="56" t="n">
         <f aca="false">MAX(E9:F12)</f>
@@ -7437,7 +7443,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D15" s="29" t="n">
         <f aca="false">INDEX({0,0.44,1,1.63,2.3,3,3.73,4.47,5.23},B12)</f>
@@ -7446,7 +7452,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D16" s="54" t="n">
         <f aca="false">D14/D15</f>
@@ -7455,7 +7461,7 @@
     </row>
     <row r="18" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -7465,26 +7471,26 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B22" s="28" t="n">
         <f aca="false">D9</f>
@@ -7501,7 +7507,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">D10</f>
@@ -7518,7 +7524,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B24" s="28" t="n">
         <f aca="false">D11</f>
@@ -7535,7 +7541,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B25" s="28" t="n">
         <f aca="false">D12</f>
@@ -7580,7 +7586,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7598,54 +7604,54 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="59" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B7" s="60" t="n">
         <v>1</v>
@@ -7680,7 +7686,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="59" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B8" s="60" t="n">
         <v>0</v>
@@ -7715,7 +7721,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="59" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B9" s="60" t="n">
         <v>0</v>
@@ -7750,7 +7756,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="59" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B10" s="60" t="n">
         <v>0</v>
@@ -7785,7 +7791,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B11" s="60" t="n">
         <v>0</v>
@@ -7820,7 +7826,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="59" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B12" s="60" t="n">
         <v>0</v>
@@ -7855,7 +7861,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="59" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B13" s="60" t="n">
         <v>0</v>
@@ -7890,7 +7896,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="59" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B14" s="60" t="n">
         <v>0</v>
@@ -7925,7 +7931,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B15" s="60" t="n">
         <v>0</v>
@@ -7960,7 +7966,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B16" s="60" t="n">
         <v>0</v>
@@ -7995,44 +8001,44 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="59" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B20" s="61" t="n">
         <f aca="false">IF(MMULT($B7:$K7,B$7:B$16)&gt;0,1,0)</f>
@@ -8077,7 +8083,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="59" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B21" s="61" t="n">
         <f aca="false">IF(MMULT($B8:$K8,B$7:B$16)&gt;0,1,0)</f>
@@ -8122,7 +8128,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="59" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B22" s="61" t="n">
         <f aca="false">IF(MMULT($B9:$K9,B$7:B$16)&gt;0,1,0)</f>
@@ -8167,7 +8173,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="59" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B23" s="61" t="n">
         <f aca="false">IF(MMULT($B10:$K10,B$7:B$16)&gt;0,1,0)</f>
@@ -8212,7 +8218,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="59" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B24" s="61" t="n">
         <f aca="false">IF(MMULT($B11:$K11,B$7:B$16)&gt;0,1,0)</f>
@@ -8257,7 +8263,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="59" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B25" s="61" t="n">
         <f aca="false">IF(MMULT($B12:$K12,B$7:B$16)&gt;0,1,0)</f>
@@ -8302,7 +8308,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="59" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B26" s="61" t="n">
         <f aca="false">IF(MMULT($B13:$K13,B$7:B$16)&gt;0,1,0)</f>
@@ -8347,7 +8353,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="59" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B27" s="61" t="n">
         <f aca="false">IF(MMULT($B14:$K14,B$7:B$16)&gt;0,1,0)</f>
@@ -8392,7 +8398,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="59" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B28" s="61" t="n">
         <f aca="false">IF(MMULT($B15:$K15,B$7:B$16)&gt;0,1,0)</f>
@@ -8437,7 +8443,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="59" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B29" s="61" t="n">
         <f aca="false">IF(MMULT($B16:$K16,B$7:B$16)&gt;0,1,0)</f>
@@ -8482,44 +8488,44 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="59" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B33" s="61" t="n">
         <f aca="false">IF(MMULT($B20:$K20,B$20:B$29)&gt;0,1,0)</f>
@@ -8564,7 +8570,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="59" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B34" s="61" t="n">
         <f aca="false">IF(MMULT($B21:$K21,B$20:B$29)&gt;0,1,0)</f>
@@ -8609,7 +8615,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="59" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B35" s="61" t="n">
         <f aca="false">IF(MMULT($B22:$K22,B$20:B$29)&gt;0,1,0)</f>
@@ -8654,7 +8660,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="59" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B36" s="61" t="n">
         <f aca="false">IF(MMULT($B23:$K23,B$20:B$29)&gt;0,1,0)</f>
@@ -8699,7 +8705,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="59" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B37" s="61" t="n">
         <f aca="false">IF(MMULT($B24:$K24,B$20:B$29)&gt;0,1,0)</f>
@@ -8744,7 +8750,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="59" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B38" s="61" t="n">
         <f aca="false">IF(MMULT($B25:$K25,B$20:B$29)&gt;0,1,0)</f>
@@ -8789,7 +8795,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="59" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B39" s="61" t="n">
         <f aca="false">IF(MMULT($B26:$K26,B$20:B$29)&gt;0,1,0)</f>
@@ -8834,7 +8840,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="59" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B40" s="61" t="n">
         <f aca="false">IF(MMULT($B27:$K27,B$20:B$29)&gt;0,1,0)</f>
@@ -8879,7 +8885,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="59" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B41" s="61" t="n">
         <f aca="false">IF(MMULT($B28:$K28,B$20:B$29)&gt;0,1,0)</f>
@@ -8924,7 +8930,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="59" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B42" s="61" t="n">
         <f aca="false">IF(MMULT($B29:$K29,B$20:B$29)&gt;0,1,0)</f>
@@ -8969,44 +8975,44 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="59" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B46" s="61" t="n">
         <f aca="false">IF(MMULT($B33:$K33,B$33:B$42)&gt;0,1,0)</f>
@@ -9051,7 +9057,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="59" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B47" s="61" t="n">
         <f aca="false">IF(MMULT($B34:$K34,B$33:B$42)&gt;0,1,0)</f>
@@ -9096,7 +9102,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="59" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B48" s="61" t="n">
         <f aca="false">IF(MMULT($B35:$K35,B$33:B$42)&gt;0,1,0)</f>
@@ -9141,7 +9147,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="59" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B49" s="61" t="n">
         <f aca="false">IF(MMULT($B36:$K36,B$33:B$42)&gt;0,1,0)</f>
@@ -9186,7 +9192,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="59" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B50" s="61" t="n">
         <f aca="false">IF(MMULT($B37:$K37,B$33:B$42)&gt;0,1,0)</f>
@@ -9231,7 +9237,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="59" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B51" s="61" t="n">
         <f aca="false">IF(MMULT($B38:$K38,B$33:B$42)&gt;0,1,0)</f>
@@ -9276,7 +9282,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="59" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B52" s="61" t="n">
         <f aca="false">IF(MMULT($B39:$K39,B$33:B$42)&gt;0,1,0)</f>
@@ -9321,7 +9327,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="59" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B53" s="61" t="n">
         <f aca="false">IF(MMULT($B40:$K40,B$33:B$42)&gt;0,1,0)</f>
@@ -9366,7 +9372,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="59" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B54" s="61" t="n">
         <f aca="false">IF(MMULT($B41:$K41,B$33:B$42)&gt;0,1,0)</f>
@@ -9411,7 +9417,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="59" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B55" s="61" t="n">
         <f aca="false">IF(MMULT($B42:$K42,B$33:B$42)&gt;0,1,0)</f>
@@ -9456,44 +9462,44 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="6" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="59" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B59" s="61" t="n">
         <f aca="false">IF(MMULT($B46:$K46,B$46:B$55)&gt;0,1,0)</f>
@@ -9538,7 +9544,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="59" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B60" s="61" t="n">
         <f aca="false">IF(MMULT($B47:$K47,B$46:B$55)&gt;0,1,0)</f>
@@ -9583,7 +9589,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="59" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B61" s="61" t="n">
         <f aca="false">IF(MMULT($B48:$K48,B$46:B$55)&gt;0,1,0)</f>
@@ -9628,7 +9634,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="59" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B62" s="61" t="n">
         <f aca="false">IF(MMULT($B49:$K49,B$46:B$55)&gt;0,1,0)</f>
@@ -9673,7 +9679,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="59" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B63" s="61" t="n">
         <f aca="false">IF(MMULT($B50:$K50,B$46:B$55)&gt;0,1,0)</f>
@@ -9718,7 +9724,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="59" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B64" s="61" t="n">
         <f aca="false">IF(MMULT($B51:$K51,B$46:B$55)&gt;0,1,0)</f>
@@ -9763,7 +9769,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="59" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B65" s="61" t="n">
         <f aca="false">IF(MMULT($B52:$K52,B$46:B$55)&gt;0,1,0)</f>
@@ -9808,7 +9814,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="59" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B66" s="61" t="n">
         <f aca="false">IF(MMULT($B53:$K53,B$46:B$55)&gt;0,1,0)</f>
@@ -9853,7 +9859,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="59" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B67" s="61" t="n">
         <f aca="false">IF(MMULT($B54:$K54,B$46:B$55)&gt;0,1,0)</f>
@@ -9898,7 +9904,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="59" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B68" s="61" t="n">
         <f aca="false">IF(MMULT($B55:$K55,B$46:B$55)&gt;0,1,0)</f>
@@ -9943,21 +9949,21 @@
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L71" s="26" t="n">
         <f aca="false">SUM(B59:K59)</f>
@@ -9974,7 +9980,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="12" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L72" s="26" t="n">
         <f aca="false">SUM(B60:K60)</f>
@@ -9991,7 +9997,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="12" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L73" s="26" t="n">
         <f aca="false">SUM(B61:K61)</f>
@@ -10008,7 +10014,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="12" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L74" s="26" t="n">
         <f aca="false">SUM(B62:K62)</f>
@@ -10025,7 +10031,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="12" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L75" s="26" t="n">
         <f aca="false">SUM(B63:K63)</f>
@@ -10042,7 +10048,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="12" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L76" s="26" t="n">
         <f aca="false">SUM(B64:K64)</f>
@@ -10059,7 +10065,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="12" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L77" s="26" t="n">
         <f aca="false">SUM(B65:K65)</f>
@@ -10076,7 +10082,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="12" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L78" s="26" t="n">
         <f aca="false">SUM(B66:K66)</f>
@@ -10093,7 +10099,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L79" s="26" t="n">
         <f aca="false">SUM(B67:K67)</f>
@@ -10110,7 +10116,7 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L80" s="26" t="n">
         <f aca="false">SUM(B68:K68)</f>
@@ -10127,7 +10133,7 @@
     </row>
     <row r="82" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -10173,7 +10179,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10181,17 +10187,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B5" s="37" t="n">
         <v>6</v>
@@ -10199,7 +10205,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B6" s="37" t="n">
         <v>2</v>
@@ -10207,7 +10213,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B7" s="32" t="n">
         <f aca="false">Inputs!$B$26</f>
@@ -10216,7 +10222,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B8" s="32" t="n">
         <f aca="false">Inputs!$B$30</f>
@@ -10225,7 +10231,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B9" s="22" t="n">
         <f aca="false">B5-(B6+B7)</f>
@@ -10234,7 +10240,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B10" s="45" t="str">
         <f aca="false">IF(B9&gt;=B8,"Other mess is faster → walk over",IF(B9&gt;0,"Small saving: stay","Come on in"))</f>
@@ -10245,24 +10251,24 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B13" s="32" t="n">
         <f aca="false">Inputs!$B$37</f>
         <v>20</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">Inputs!$B$16</f>
@@ -10271,22 +10277,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>648</v>
-      </c>
-      <c r="B15" s="20" t="n">
+        <v>649</v>
+      </c>
+      <c r="B15" s="17" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B16" s="51" t="n">
         <f aca="false">B13*B14*(1+B15)</f>
         <v>720</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -10296,73 +10302,73 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B21" s="37" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="C21" s="37" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B22" s="37" t="n">
         <v>0.8</v>
       </c>
       <c r="C22" s="37" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B23" s="37" t="n">
         <v>0.8</v>
       </c>
       <c r="C23" s="37" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -10389,7 +10395,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -10398,7 +10404,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10409,161 +10415,161 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>670</v>
-      </c>
-      <c r="B5" s="20" t="s">
         <v>671</v>
       </c>
+      <c r="B5" s="17" t="s">
+        <v>672</v>
+      </c>
       <c r="C5" s="37" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="D5" s="37" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="E5" s="20" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E5" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G5" s="37" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>672</v>
-      </c>
-      <c r="B6" s="20" t="n">
+        <v>673</v>
+      </c>
+      <c r="B6" s="17" t="n">
         <v>0.3</v>
       </c>
       <c r="C6" s="37" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="D6" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>0.13</v>
+        <v>4.3</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.12</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>672</v>
-      </c>
-      <c r="B7" s="20" t="n">
+        <v>673</v>
+      </c>
+      <c r="B7" s="17" t="n">
         <v>0.6</v>
       </c>
       <c r="C7" s="37" t="n">
         <v>0.8</v>
       </c>
       <c r="D7" s="37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>0.14</v>
+        <v>2.5</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.13</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G7" s="37" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>672</v>
-      </c>
-      <c r="B8" s="20" t="n">
+        <v>673</v>
+      </c>
+      <c r="B8" s="17" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="37" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="D8" s="37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>0.18</v>
+        <v>2.7</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.16</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="G8" s="37" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C10" s="62" t="n">
         <f aca="false">1-C7/C5</f>
-        <v>0.887323943661972</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B13" s="37" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="C13" s="37" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B14" s="37" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="C14" s="37" t="n">
         <v>18.1</v>
@@ -10571,12 +10577,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C17" s="32" t="n">
         <f aca="false">'S15 Queuing'!$H$51</f>
@@ -10585,7 +10591,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C18" s="32" t="n">
         <f aca="false">'S15 Queuing'!$I$51</f>
@@ -10594,7 +10600,7 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -10603,7 +10609,7 @@
     </row>
     <row r="21" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -10612,30 +10618,30 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C25" s="37" t="n">
         <v>2</v>
@@ -10652,10 +10658,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C26" s="37" t="n">
         <v>1.3</v>
@@ -10672,39 +10678,59 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>694</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>695</v>
-      </c>
       <c r="C27" s="37" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D27" s="37" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E27" s="37" t="n">
         <v>7.2</v>
       </c>
       <c r="F27" s="37" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="C28" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F28" s="37" t="n">
         <v>0.9</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10994,21 +11020,21 @@
         <v>102</v>
       </c>
       <c r="B19" s="17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>103</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>15</v>
@@ -11020,87 +11046,87 @@
         <v>11</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" s="17" t="n">
+        <v>109</v>
+      </c>
+      <c r="B22" s="18" t="n">
         <v>0.85</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="18" t="n">
+        <v>112</v>
+      </c>
+      <c r="B23" s="19" t="n">
         <v>10</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" s="18" t="n">
+        <v>115</v>
+      </c>
+      <c r="B24" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B25" s="19" t="n">
+        <v>118</v>
+      </c>
+      <c r="B25" s="20" t="n">
         <v>17</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>82</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="B26" s="18" t="n">
+        <v>121</v>
+      </c>
+      <c r="B26" s="19" t="n">
         <v>0.5</v>
       </c>
       <c r="C26" s="12" t="s">
@@ -11110,51 +11136,51 @@
         <v>14</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="B27" s="18" t="n">
         <v>0.6</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="20" t="n">
+        <v>126</v>
+      </c>
+      <c r="B29" s="17" t="n">
         <v>0.85</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>2</v>
@@ -11163,170 +11189,170 @@
         <v>82</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B32" s="21" t="n">
         <v>5</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B33" s="21" t="n">
         <v>30</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B34" s="21" t="n">
         <v>150</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="B35" s="19" t="n">
+        <v>141</v>
+      </c>
+      <c r="B35" s="20" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="22" t="n">
         <f aca="false">B11*B23</f>
         <v>20</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="22" t="n">
         <f aca="false">B12*B23</f>
         <v>20</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B39" s="22" t="n">
         <f aca="false">Inputs!$B$9/Inputs!$B$15</f>
         <v>50</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="22" t="n">
         <f aca="false">Inputs!$B$10/Inputs!$B$15</f>
         <v>27.7777777777778</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="22" t="n">
         <f aca="false">Inputs!$B$13*60/Inputs!$B$24</f>
         <v>30</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" s="22" t="n">
         <f aca="false">Inputs!$B$14*60/Inputs!$B$24</f>
         <v>30</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -11361,7 +11387,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11370,17 +11396,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
@@ -11389,296 +11415,296 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>58</v>
@@ -11713,104 +11739,104 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>71</v>
@@ -11818,68 +11844,68 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -11910,7 +11936,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11920,37 +11946,37 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>20</v>
@@ -11960,15 +11986,15 @@
         <v>0.194174757281553</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>16</v>
@@ -11978,15 +12004,15 @@
         <v>0.155339805825243</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>40</v>
@@ -11996,15 +12022,15 @@
         <v>0.388349514563107</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>27</v>
@@ -12014,12 +12040,12 @@
         <v>0.262135922330097</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="26" t="n">
@@ -12034,12 +12060,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>3</v>
@@ -12047,27 +12073,27 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B16" s="24" t="n">
         <v>4</v>
@@ -12080,15 +12106,15 @@
         <v>Quick win</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B17" s="24" t="n">
         <v>5</v>
@@ -12101,15 +12127,15 @@
         <v>Quick win</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B18" s="24" t="n">
         <v>4</v>
@@ -12122,15 +12148,15 @@
         <v>Major project</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B19" s="24" t="n">
         <v>3</v>
@@ -12143,15 +12169,15 @@
         <v>Fill-in</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B20" s="24" t="n">
         <v>4</v>
@@ -12164,15 +12190,15 @@
         <v>Major project</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B21" s="24" t="n">
         <v>2</v>
@@ -12185,87 +12211,87 @@
         <v>Fill-in</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -12293,7 +12319,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12328,44 +12354,44 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K5" s="27" t="n">
         <f aca="false">Inputs!$B$23*60</f>
@@ -12404,21 +12430,21 @@
         <v>3</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -12427,7 +12453,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="K7" s="26" t="n">
@@ -12444,7 +12470,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J8" s="20" t="n">
+      <c r="J8" s="17" t="n">
         <v>0.6</v>
       </c>
       <c r="K8" s="26" t="n">
@@ -12461,7 +12487,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J9" s="20" t="n">
+      <c r="J9" s="17" t="n">
         <v>0.7</v>
       </c>
       <c r="K9" s="26" t="n">
@@ -12478,7 +12504,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J10" s="20" t="n">
+      <c r="J10" s="17" t="n">
         <v>0.75</v>
       </c>
       <c r="K10" s="26" t="n">
@@ -12495,7 +12521,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="17" t="n">
         <v>0.8</v>
       </c>
       <c r="K11" s="26" t="n">
@@ -12512,7 +12538,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="17" t="n">
         <v>0.85</v>
       </c>
       <c r="K12" s="26" t="n">
@@ -12529,7 +12555,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J13" s="20" t="n">
+      <c r="J13" s="17" t="n">
         <v>0.9</v>
       </c>
       <c r="K13" s="26" t="n">
@@ -12546,7 +12572,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J14" s="20" t="n">
+      <c r="J14" s="17" t="n">
         <v>0.93</v>
       </c>
       <c r="K14" s="26" t="n">
@@ -12563,7 +12589,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J15" s="20" t="n">
+      <c r="J15" s="17" t="n">
         <v>0.95</v>
       </c>
       <c r="K15" s="26" t="n">
@@ -12580,7 +12606,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J16" s="20" t="n">
+      <c r="J16" s="17" t="n">
         <v>0.96</v>
       </c>
       <c r="K16" s="26" t="n">
@@ -12597,7 +12623,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J17" s="20" t="n">
+      <c r="J17" s="17" t="n">
         <v>0.97</v>
       </c>
       <c r="K17" s="26" t="n">
@@ -12614,7 +12640,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J18" s="20" t="n">
+      <c r="J18" s="17" t="n">
         <v>0.98</v>
       </c>
       <c r="K18" s="26" t="n">
@@ -12632,12 +12658,12 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -12671,14 +12697,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E25" s="30" t="n">
         <f aca="false">Inputs!$B$37/(Inputs!$B$37+Inputs!$B$38)</f>
         <v>0.5</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -12691,14 +12717,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E26" s="30" t="n">
         <f aca="false">Inputs!$B$22+Inputs!$B$27*(E25-Inputs!$B$22)</f>
         <v>0.64</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -12711,7 +12737,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D28" s="31" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
@@ -12721,7 +12747,7 @@
       <c r="J28" s="31"/>
       <c r="K28" s="31"/>
       <c r="L28" s="31" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M28" s="31"/>
       <c r="N28" s="31"/>
@@ -12731,7 +12757,7 @@
       <c r="R28" s="31"/>
       <c r="S28" s="31"/>
       <c r="T28" s="31" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="U28" s="31"/>
       <c r="V28" s="31"/>
@@ -12741,7 +12767,7 @@
       <c r="Z28" s="31"/>
       <c r="AA28" s="31"/>
       <c r="AB28" s="31" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AC28" s="31"/>
       <c r="AD28" s="31"/>
@@ -12753,109 +12779,109 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E29" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="G29" s="6" t="s">
+      <c r="M29" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="N29" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="O29" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="P29" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="Q29" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="R29" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="L29" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="M29" s="6" t="s">
+      <c r="S29" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="T29" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="N29" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="O29" s="6" t="s">
+      <c r="U29" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="P29" s="6" t="s">
+      <c r="V29" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="W29" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="Q29" s="6" t="s">
+      <c r="X29" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="R29" s="6" t="s">
+      <c r="Y29" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="S29" s="6" t="s">
+      <c r="Z29" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="T29" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="U29" s="6" t="s">
+      <c r="AA29" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="AB29" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="V29" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="W29" s="6" t="s">
+      <c r="AC29" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="X29" s="6" t="s">
+      <c r="AD29" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="AE29" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="Y29" s="6" t="s">
+      <c r="AF29" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="Z29" s="6" t="s">
+      <c r="AG29" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="AA29" s="6" t="s">
+      <c r="AH29" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="AB29" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="AC29" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="AD29" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="AE29" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="AF29" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="AG29" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="AH29" s="6" t="s">
-        <v>376</v>
-      </c>
       <c r="AI29" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13000,7 +13026,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B31" s="16" t="n">
         <v>25</v>
@@ -13140,7 +13166,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B32" s="16" t="n">
         <v>47</v>
@@ -13280,7 +13306,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>79</v>
@@ -13420,7 +13446,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>123</v>
@@ -13560,7 +13586,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B35" s="16" t="n">
         <v>178</v>
@@ -13700,7 +13726,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B36" s="16" t="n">
         <v>236</v>
@@ -13840,7 +13866,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B37" s="16" t="n">
         <v>289</v>
@@ -13980,7 +14006,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B38" s="16" t="n">
         <v>326</v>
@@ -14120,7 +14146,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B39" s="16" t="n">
         <v>340</v>
@@ -14260,7 +14286,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B40" s="16" t="n">
         <v>326</v>
@@ -14400,7 +14426,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B41" s="16" t="n">
         <v>289</v>
@@ -14540,7 +14566,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B42" s="16" t="n">
         <v>236</v>
@@ -14680,7 +14706,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B43" s="16" t="n">
         <v>178</v>
@@ -14820,7 +14846,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B44" s="16" t="n">
         <v>123</v>
@@ -14960,7 +14986,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B45" s="16" t="n">
         <v>79</v>
@@ -15100,7 +15126,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B46" s="16" t="n">
         <v>47</v>
@@ -15240,7 +15266,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B47" s="16" t="n">
         <v>25</v>
@@ -15380,37 +15406,37 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
       <c r="D50" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -15441,7 +15467,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -15464,7 +15490,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -15487,7 +15513,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -15510,7 +15536,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -15533,7 +15559,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -15556,7 +15582,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -15579,7 +15605,7 @@
     </row>
     <row r="59" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -15639,7 +15665,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15653,12 +15679,12 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="36" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -15672,19 +15698,19 @@
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -15693,13 +15719,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B7" s="37" t="n">
         <v>2.5</v>
       </c>
       <c r="C7" s="37" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="D7" s="37" t="n">
         <v>15</v>
@@ -15712,7 +15738,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B8" s="37" t="n">
         <v>0.7</v>
@@ -15731,7 +15757,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B9" s="37" t="n">
         <v>0.7</v>
@@ -15750,7 +15776,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B10" s="37" t="n">
         <v>1.5</v>
@@ -15769,7 +15795,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B11" s="37" t="n">
         <v>0.5</v>
@@ -15783,29 +15809,29 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="B14" s="20" t="n">
+        <v>424</v>
+      </c>
+      <c r="B14" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="17" t="n">
         <v>0.2</v>
       </c>
       <c r="E14" s="25" t="n">
@@ -15813,12 +15839,12 @@
         <v>1</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -15827,44 +15853,44 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B19" s="22" t="n">
         <f aca="false">B$7-B7</f>
@@ -15905,7 +15931,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">B$7-B8</f>
@@ -15913,7 +15939,7 @@
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">C$7-C8</f>
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="D20" s="22" t="n">
         <f aca="false">D$7-D8</f>
@@ -15933,20 +15959,20 @@
       </c>
       <c r="H20" s="22" t="n">
         <f aca="false">AVERAGE(B20:D20)</f>
-        <v>5.7</v>
+        <v>5.73333333333333</v>
       </c>
       <c r="I20" s="29" t="n">
         <f aca="false">SUMPRODUCT(B20:D20,$B$14:$D$14)</f>
-        <v>5.49</v>
+        <v>5.54</v>
       </c>
       <c r="J20" s="40" t="n">
         <f aca="false">I20*$B$15/60</f>
-        <v>270.84</v>
+        <v>273.306666666667</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">B$7-B9</f>
@@ -15954,7 +15980,7 @@
       </c>
       <c r="C21" s="22" t="n">
         <f aca="false">C$7-C9</f>
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="D21" s="22" t="n">
         <f aca="false">D$7-D9</f>
@@ -15974,20 +16000,20 @@
       </c>
       <c r="H21" s="22" t="n">
         <f aca="false">AVERAGE(B21:D21)</f>
-        <v>6.53333333333333</v>
+        <v>6.56666666666667</v>
       </c>
       <c r="I21" s="29" t="n">
         <f aca="false">SUMPRODUCT(B21:D21,$B$14:$D$14)</f>
-        <v>5.99</v>
+        <v>6.04</v>
       </c>
       <c r="J21" s="40" t="n">
         <f aca="false">I21*$B$15/60</f>
-        <v>295.506666666667</v>
+        <v>297.973333333333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B22" s="22" t="n">
         <f aca="false">B$7-B10</f>
@@ -15995,7 +16021,7 @@
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">C$7-C10</f>
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">D$7-D10</f>
@@ -16015,20 +16041,20 @@
       </c>
       <c r="H22" s="22" t="n">
         <f aca="false">AVERAGE(B22:D22)</f>
-        <v>3.53333333333333</v>
+        <v>3.56666666666667</v>
       </c>
       <c r="I22" s="29" t="n">
         <f aca="false">SUMPRODUCT(B22:D22,$B$14:$D$14)</f>
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J22" s="40" t="n">
         <f aca="false">I22*$B$15/60</f>
-        <v>162.8</v>
+        <v>165.266666666667</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B23" s="22" t="n">
         <f aca="false">B$7-B11</f>
@@ -16036,7 +16062,7 @@
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">C$7-C11</f>
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="D23" s="22" t="n">
         <f aca="false">D$7-D11</f>
@@ -16056,20 +16082,20 @@
       </c>
       <c r="H23" s="22" t="n">
         <f aca="false">AVERAGE(B23:D23)</f>
-        <v>6.33333333333333</v>
+        <v>6.36666666666667</v>
       </c>
       <c r="I23" s="29" t="n">
         <f aca="false">SUMPRODUCT(B23:D23,$B$14:$D$14)</f>
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="J23" s="40" t="n">
         <f aca="false">I23*$B$15/60</f>
-        <v>293.533333333333</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E24" s="41" t="str">
         <f aca="false">INDEX($A$19:$A$23,MATCH(MAX(E19:E23),E19:E23,0))</f>
@@ -16094,7 +16120,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B26" s="37" t="n">
         <v>0.4</v>
@@ -16102,32 +16128,32 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B19</f>
@@ -16135,7 +16161,7 @@
       </c>
       <c r="C30" s="22" t="n">
         <f aca="false">MAX(C$19:C$23)-C19</f>
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="D30" s="22" t="n">
         <f aca="false">MAX(D$19:D$23)-D19</f>
@@ -16147,12 +16173,12 @@
       </c>
       <c r="F30" s="29" t="n">
         <f aca="false">SUMPRODUCT(B30:D30,$B$14:$D$14)</f>
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B31" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B20</f>
@@ -16177,7 +16203,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B32" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B21</f>
@@ -16202,7 +16228,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B33" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B22</f>
@@ -16227,7 +16253,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B34" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B23</f>
@@ -16252,7 +16278,7 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E35" s="41" t="str">
         <f aca="false">INDEX($A$30:$A$34,MATCH(MIN(E30:E34),E30:E34,0))</f>
@@ -16261,7 +16287,7 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F36" s="41" t="str">
         <f aca="false">INDEX($A$30:$A$34,MATCH(MIN(F30:F34),F30:F34,0))</f>
@@ -16270,30 +16296,30 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B39" s="29" t="n">
         <f aca="false">B14*MAX(B19:B23)+C14*MAX(C19:C23)+D14*MAX(D19:D23)</f>
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B40" s="29" t="n">
         <f aca="false">MAX(I19:I23)</f>
-        <v>5.99</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B41" s="42" t="n">
         <f aca="false">B39-B40</f>
@@ -16302,7 +16328,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B42" s="29" t="n">
         <f aca="false">MIN(F30:F34)</f>
@@ -16311,7 +16337,7 @@
     </row>
     <row r="44" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -16355,7 +16381,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16365,15 +16391,15 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -16382,13 +16408,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="B5" s="20" t="n">
+        <v>452</v>
+      </c>
+      <c r="B5" s="17" t="n">
         <v>0.4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -16401,13 +16427,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -16420,13 +16446,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>300</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -16439,13 +16465,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -16458,7 +16484,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B9" s="43" t="n">
         <f aca="false">Inputs!$B$33</f>
@@ -16472,7 +16498,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B10" s="43" t="n">
         <f aca="false">Inputs!$B$32</f>
@@ -16493,7 +16519,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -16503,19 +16529,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -16525,7 +16551,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="44"/>
@@ -16542,7 +16568,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B15" s="25" t="n">
         <f aca="false">B5</f>
@@ -16560,7 +16586,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B16" s="25" t="n">
         <f aca="false">1-B5</f>
@@ -16578,7 +16604,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B17" s="25"/>
       <c r="C17" s="44"/>
@@ -16590,7 +16616,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">B5</f>
@@ -16608,7 +16634,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">1-B5</f>
@@ -16626,7 +16652,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B21" s="45" t="str">
         <f aca="false">IF(E14&lt;=E17,"Pre-stage","Wait and react")</f>
@@ -16635,14 +16661,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B22" s="46" t="n">
         <f aca="false">(C16-C19)/((C16-C19)+(C18-C15))</f>
         <v>0.0740740740740741</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -16650,25 +16676,25 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="n">
+      <c r="A26" s="17" t="n">
         <v>0</v>
       </c>
       <c r="B26" s="44" t="n">
@@ -16685,7 +16711,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="n">
+      <c r="A27" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="B27" s="44" t="n">
@@ -16702,7 +16728,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="n">
+      <c r="A28" s="17" t="n">
         <v>0.2</v>
       </c>
       <c r="B28" s="44" t="n">
@@ -16719,7 +16745,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="n">
+      <c r="A29" s="17" t="n">
         <v>0.3</v>
       </c>
       <c r="B29" s="44" t="n">
@@ -16736,7 +16762,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="n">
+      <c r="A30" s="17" t="n">
         <v>0.4</v>
       </c>
       <c r="B30" s="44" t="n">
@@ -16753,7 +16779,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="n">
+      <c r="A31" s="17" t="n">
         <v>0.5</v>
       </c>
       <c r="B31" s="44" t="n">
@@ -16770,7 +16796,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="n">
+      <c r="A32" s="17" t="n">
         <v>0.6</v>
       </c>
       <c r="B32" s="44" t="n">
@@ -16787,7 +16813,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="n">
+      <c r="A33" s="17" t="n">
         <v>0.7</v>
       </c>
       <c r="B33" s="44" t="n">
@@ -16804,7 +16830,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="n">
+      <c r="A34" s="17" t="n">
         <v>0.8</v>
       </c>
       <c r="B34" s="44" t="n">
@@ -16821,7 +16847,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="n">
+      <c r="A35" s="17" t="n">
         <v>0.9</v>
       </c>
       <c r="B35" s="44" t="n">
@@ -16838,7 +16864,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="n">
+      <c r="A36" s="17" t="n">
         <v>1</v>
       </c>
       <c r="B36" s="44" t="n">
@@ -16889,7 +16915,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -16899,17 +16925,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -16919,7 +16945,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -16929,7 +16955,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -16939,12 +16965,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B10" s="13" t="n">
         <v>1000</v>
@@ -16952,13 +16978,13 @@
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B11" s="13" t="n">
         <v>650</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -16966,7 +16992,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B12" s="13" t="n">
         <v>400</v>
@@ -16978,7 +17004,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B13" s="47" t="n">
         <v>60</v>
@@ -16986,7 +17012,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B14" s="47" t="n">
         <v>45</v>
@@ -16994,12 +17020,12 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B17" s="48" t="n">
         <v>650</v>
@@ -17007,7 +17033,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B18" s="48" t="n">
         <v>350</v>
@@ -17015,7 +17041,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B19" s="49" t="n">
         <f aca="false">B13*B17+B14*B18</f>
@@ -17024,36 +17050,36 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B23" s="40" t="n">
         <f aca="false">B17+B18</f>
         <v>1000</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D23" s="40" t="n">
         <f aca="false">B10</f>
@@ -17066,14 +17092,14 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B24" s="40" t="n">
         <f aca="false">B17</f>
         <v>650</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D24" s="40" t="n">
         <f aca="false">B11</f>
@@ -17086,14 +17112,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B25" s="40" t="n">
         <f aca="false">B18</f>
         <v>350</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D25" s="40" t="n">
         <f aca="false">B12</f>
@@ -17106,17 +17132,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B26" s="40" t="n">
         <f aca="false">MIN(B17:B18)</f>
         <v>350</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E26" s="7" t="str">
         <f aca="false">IF(B26&gt;=0,"OK","Violated")</f>
@@ -17125,29 +17151,29 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B30" s="40" t="n">
         <v>0</v>
@@ -17166,7 +17192,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B31" s="40" t="n">
         <f aca="false">B11</f>
@@ -17186,7 +17212,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B32" s="40" t="n">
         <f aca="false">B11</f>
@@ -17207,7 +17233,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B33" s="40" t="n">
         <f aca="false">MIN(B11,B10-B12)</f>
@@ -17228,7 +17254,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B34" s="40" t="n">
         <v>0</v>
@@ -17248,7 +17274,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B36" s="41" t="str">
         <f aca="false">INDEX(A30:A34,MATCH(MAX(E30:E34),E30:E34,0))</f>
@@ -17260,7 +17286,7 @@
     </row>
     <row r="38" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -17270,12 +17296,12 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>

--- a/docs/MDS_Decision_Workbook.xlsx
+++ b/docs/MDS_Decision_Workbook.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Output of our prototype's simulator</t>
   </si>
   <si>
-    <t xml:space="preserve">Average wait 7.2 → 0.8 min</t>
+    <t xml:space="preserve">Average wait 7.2 → 1.1 min</t>
   </si>
   <si>
     <t xml:space="preserve">Tabs and course sessions</t>
@@ -1278,7 +1278,7 @@
     <t xml:space="preserve">Session 7: Decision making under certainty, risk and uncertainty (maximax, maximin, minimax regret, Hurwicz, Laplace, EMV, EVPI)</t>
   </si>
   <si>
-    <t xml:space="preserve">Everything on this tab is in MINUTES of waiting per student, so no rupee values are needed. Blue = input. S2 values for A1 and A2 come from our simulator (7.2 → 0.8 min); the other cells are illustrative estimates.</t>
+    <t xml:space="preserve">Everything on this tab is in MINUTES of waiting per student, so no rupee values are needed. Blue = input. S2 values for A1 and A2 come from our simulator (7.2 → 1.1 min); the other cells are illustrative estimates.</t>
   </si>
   <si>
     <t xml:space="preserve">Average wait per student (minutes)  [lower is better]</t>
@@ -1782,7 +1782,7 @@
     <t xml:space="preserve">Best alternative (AHP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Service-level scores can be anchored to the queuing results (S15) and the payoff matrix (S7): e.g. average wait 7.2 min → 3, 0.8 min → 8. Criteria come from our Phase 1 deck's weighted decision table.</t>
+    <t xml:space="preserve">Service-level scores can be anchored to the queuing results (S15) and the payoff matrix (S7): e.g. average wait 7.2 min → 3, 1.1 min → 8. Criteria come from our Phase 1 deck's weighted decision table.</t>
   </si>
   <si>
     <t xml:space="preserve">Best–Worst Method: the same criteria weights with fewer comparisons</t>
@@ -2088,7 +2088,7 @@
     <t xml:space="preserve">The spreadsheet model is simpler than the simulator (fixed 10-min bins, no stock-outs, no seat limit), so the two will not match exactly; both should show the same direction and rough size of improvement.</t>
   </si>
   <si>
-    <t xml:space="preserve">Findings from the simulator: (1) Moving students moves the food run-outs: with screens Munch feeds more students and a 30-min call-back restock cannot keep up, so routing and food allocation (S10-11 LP) must be planned together; if the next batch is always made before the call (10–14 min to send), run-outs disappear in the model (table below). (2) The single face scanner (~30 scans/min at an assumed 2 s each) is close to Central's peak arrival rate, so a queue of 20–25 people can form OUTSIDE the scanner, which the biometric data cannot see.</t>
+    <t xml:space="preserve">Findings from the simulator: (1) Routing and food interact: when the next batch is rarely ready, run-outs stay about the same with screens (Munch feeds more students and a 30-min call-back cannot keep up); when food is usually ready, screens cut run-outs, because a star dish marked 'out' sends students to the other mess at once. Plan routing and food allocation (S10-11 LP) together; if the next batch is always made before the call (10–14 min), run-outs disappear (table below). (2) The single face scanner (~30 scans/min at an assumed 2 s each) is close to Central's peak arrival rate, so a queue of 20–25 people can form OUTSIDE the scanner, which the biometric data cannot see.</t>
   </si>
   <si>
     <t xml:space="preserve">Next batch already made when the mess calls?</t>
@@ -2878,11 +2878,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="62409454"/>
-        <c:axId val="29120686"/>
+        <c:axId val="21186051"/>
+        <c:axId val="36980189"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="62409454"/>
+        <c:axId val="21186051"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2948,7 +2948,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29120686"/>
+        <c:crossAx val="36980189"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2956,7 +2956,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29120686"/>
+        <c:axId val="36980189"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3032,7 +3032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62409454"/>
+        <c:crossAx val="21186051"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3832,11 +3832,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="48426104"/>
-        <c:axId val="91551624"/>
+        <c:axId val="78154611"/>
+        <c:axId val="73859903"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="48426104"/>
+        <c:axId val="78154611"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3868,7 +3868,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91551624"/>
+        <c:crossAx val="73859903"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3876,7 +3876,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91551624"/>
+        <c:axId val="73859903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3952,7 +3952,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48426104"/>
+        <c:crossAx val="78154611"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4130,16 +4130,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.54</c:v>
+                  <c:v>5.33</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.04</c:v>
+                  <c:v>5.83</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3.35</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6</c:v>
+                  <c:v>5.87</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4147,11 +4147,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74992750"/>
-        <c:axId val="66402931"/>
+        <c:axId val="25705602"/>
+        <c:axId val="23205098"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74992750"/>
+        <c:axId val="25705602"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4183,7 +4183,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66402931"/>
+        <c:crossAx val="23205098"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4191,7 +4191,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66402931"/>
+        <c:axId val="23205098"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4233,7 +4233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74992750"/>
+        <c:crossAx val="25705602"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4589,11 +4589,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="61766926"/>
-        <c:axId val="59186027"/>
+        <c:axId val="53313538"/>
+        <c:axId val="95202996"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="61766926"/>
+        <c:axId val="53313538"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4625,7 +4625,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59186027"/>
+        <c:crossAx val="95202996"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4633,7 +4633,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59186027"/>
+        <c:axId val="95202996"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4675,7 +4675,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61766926"/>
+        <c:crossAx val="53313538"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4907,11 +4907,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="19812427"/>
-        <c:axId val="70670018"/>
+        <c:axId val="65048712"/>
+        <c:axId val="84066847"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="19812427"/>
+        <c:axId val="65048712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4987,12 +4987,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70670018"/>
+        <c:crossAx val="84066847"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="70670018"/>
+        <c:axId val="84066847"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5068,7 +5068,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19812427"/>
+        <c:crossAx val="65048712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5219,13 +5219,13 @@
                   <c:v>7.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.8</c:v>
+                  <c:v>1.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5233,11 +5233,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="22127919"/>
-        <c:axId val="95985930"/>
+        <c:axId val="97367826"/>
+        <c:axId val="94085906"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="22127919"/>
+        <c:axId val="97367826"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5269,7 +5269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95985930"/>
+        <c:crossAx val="94085906"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5277,7 +5277,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95985930"/>
+        <c:axId val="94085906"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5319,7 +5319,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22127919"/>
+        <c:crossAx val="97367826"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10338,10 +10338,10 @@
         <v>658</v>
       </c>
       <c r="B22" s="37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C22" s="37" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>659</v>
@@ -10352,10 +10352,10 @@
         <v>660</v>
       </c>
       <c r="B23" s="37" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="C23" s="37" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>661</v>
@@ -10472,19 +10472,19 @@
         <v>0.3</v>
       </c>
       <c r="C6" s="37" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="D6" s="37" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G6" s="37" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10495,19 +10495,19 @@
         <v>0.6</v>
       </c>
       <c r="C7" s="37" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D7" s="37" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G7" s="37" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10518,19 +10518,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="37" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D8" s="37" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G8" s="37" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="C10" s="62" t="n">
         <f aca="false">1-C7/C5</f>
-        <v>0.888888888888889</v>
+        <v>0.847222222222222</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10647,13 +10647,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="37" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="E25" s="37" t="n">
         <v>7</v>
       </c>
       <c r="F25" s="37" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10667,13 +10667,13 @@
         <v>1.3</v>
       </c>
       <c r="D26" s="37" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="E26" s="37" t="n">
         <v>7.1</v>
       </c>
       <c r="F26" s="37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10687,13 +10687,13 @@
         <v>0.8</v>
       </c>
       <c r="D27" s="37" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E27" s="37" t="n">
         <v>7.2</v>
       </c>
       <c r="F27" s="37" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15741,10 +15741,10 @@
         <v>306</v>
       </c>
       <c r="B8" s="37" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="C8" s="37" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D8" s="37" t="n">
         <v>6</v>
@@ -15760,10 +15760,10 @@
         <v>309</v>
       </c>
       <c r="B9" s="37" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="C9" s="37" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D9" s="37" t="n">
         <v>3.5</v>
@@ -15798,10 +15798,10 @@
         <v>422</v>
       </c>
       <c r="B11" s="37" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C11" s="37" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D11" s="37" t="n">
         <v>4.5</v>
@@ -15935,11 +15935,11 @@
       </c>
       <c r="B20" s="22" t="n">
         <f aca="false">B$7-B8</f>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">C$7-C8</f>
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="D20" s="22" t="n">
         <f aca="false">D$7-D8</f>
@@ -15951,23 +15951,23 @@
       </c>
       <c r="F20" s="22" t="n">
         <f aca="false">MIN(B20:D20)</f>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="G20" s="22" t="n">
         <f aca="false">$B$26*E20+(1-$B$26)*F20</f>
-        <v>4.68</v>
+        <v>4.56</v>
       </c>
       <c r="H20" s="22" t="n">
         <f aca="false">AVERAGE(B20:D20)</f>
-        <v>5.73333333333333</v>
+        <v>5.56666666666667</v>
       </c>
       <c r="I20" s="29" t="n">
         <f aca="false">SUMPRODUCT(B20:D20,$B$14:$D$14)</f>
-        <v>5.54</v>
+        <v>5.33</v>
       </c>
       <c r="J20" s="40" t="n">
         <f aca="false">I20*$B$15/60</f>
-        <v>273.306666666667</v>
+        <v>262.946666666667</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15976,11 +15976,11 @@
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">B$7-B9</f>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="C21" s="22" t="n">
         <f aca="false">C$7-C9</f>
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="D21" s="22" t="n">
         <f aca="false">D$7-D9</f>
@@ -15992,23 +15992,23 @@
       </c>
       <c r="F21" s="22" t="n">
         <f aca="false">MIN(B21:D21)</f>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="G21" s="22" t="n">
         <f aca="false">$B$26*E21+(1-$B$26)*F21</f>
-        <v>5.68</v>
+        <v>5.56</v>
       </c>
       <c r="H21" s="22" t="n">
         <f aca="false">AVERAGE(B21:D21)</f>
-        <v>6.56666666666667</v>
+        <v>6.4</v>
       </c>
       <c r="I21" s="29" t="n">
         <f aca="false">SUMPRODUCT(B21:D21,$B$14:$D$14)</f>
-        <v>6.04</v>
+        <v>5.83</v>
       </c>
       <c r="J21" s="40" t="n">
         <f aca="false">I21*$B$15/60</f>
-        <v>297.973333333333</v>
+        <v>287.613333333333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16058,11 +16058,11 @@
       </c>
       <c r="B23" s="22" t="n">
         <f aca="false">B$7-B11</f>
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">C$7-C11</f>
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="D23" s="22" t="n">
         <f aca="false">D$7-D11</f>
@@ -16074,23 +16074,23 @@
       </c>
       <c r="F23" s="22" t="n">
         <f aca="false">MIN(B23:D23)</f>
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="G23" s="22" t="n">
         <f aca="false">$B$26*E23+(1-$B$26)*F23</f>
-        <v>5.4</v>
+        <v>5.34</v>
       </c>
       <c r="H23" s="22" t="n">
         <f aca="false">AVERAGE(B23:D23)</f>
-        <v>6.36666666666667</v>
+        <v>6.26666666666667</v>
       </c>
       <c r="I23" s="29" t="n">
         <f aca="false">SUMPRODUCT(B23:D23,$B$14:$D$14)</f>
-        <v>6</v>
+        <v>5.87</v>
       </c>
       <c r="J23" s="40" t="n">
         <f aca="false">I23*$B$15/60</f>
-        <v>296</v>
+        <v>289.586666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="I24" s="41" t="str">
         <f aca="false">INDEX($A$19:$A$23,MATCH(MAX(I19:I23),I19:I23,0))</f>
-        <v>A3 Screens + kitchen early alerts</v>
+        <v>A5 Screens + 3rd serving station</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16157,11 +16157,11 @@
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B19</f>
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="C30" s="22" t="n">
         <f aca="false">MAX(C$19:C$23)-C19</f>
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="D30" s="22" t="n">
         <f aca="false">MAX(D$19:D$23)-D19</f>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="F30" s="29" t="n">
         <f aca="false">SUMPRODUCT(B30:D30,$B$14:$D$14)</f>
-        <v>6.2</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16182,11 +16182,11 @@
       </c>
       <c r="B31" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B20</f>
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C31" s="22" t="n">
         <f aca="false">MAX(C$19:C$23)-C20</f>
-        <v>0.2</v>
+        <v>0.300000000000001</v>
       </c>
       <c r="D31" s="22" t="n">
         <f aca="false">MAX(D$19:D$23)-D20</f>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="F31" s="29" t="n">
         <f aca="false">SUMPRODUCT(B31:D31,$B$14:$D$14)</f>
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16207,11 +16207,11 @@
       </c>
       <c r="B32" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B21</f>
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C32" s="22" t="n">
         <f aca="false">MAX(C$19:C$23)-C21</f>
-        <v>0.2</v>
+        <v>0.300000000000001</v>
       </c>
       <c r="D32" s="22" t="n">
         <f aca="false">MAX(D$19:D$23)-D21</f>
@@ -16219,11 +16219,11 @@
       </c>
       <c r="E32" s="22" t="n">
         <f aca="false">MAX(B32:D32)</f>
-        <v>0.2</v>
+        <v>0.300000000000001</v>
       </c>
       <c r="F32" s="29" t="n">
         <f aca="false">SUMPRODUCT(B32:D32,$B$14:$D$14)</f>
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16232,11 +16232,11 @@
       </c>
       <c r="B33" s="22" t="n">
         <f aca="false">MAX(B$19:B$23)-B22</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C33" s="22" t="n">
         <f aca="false">MAX(C$19:C$23)-C22</f>
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="D33" s="22" t="n">
         <f aca="false">MAX(D$19:D$23)-D22</f>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="F33" s="29" t="n">
         <f aca="false">SUMPRODUCT(B33:D33,$B$14:$D$14)</f>
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="F36" s="41" t="str">
         <f aca="false">INDEX($A$30:$A$34,MATCH(MIN(F30:F34),F30:F34,0))</f>
-        <v>A3 Screens + kitchen early alerts</v>
+        <v>A5 Screens + 3rd serving station</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="B39" s="29" t="n">
         <f aca="false">B14*MAX(B19:B23)+C14*MAX(C19:C23)+D14*MAX(D19:D23)</f>
-        <v>6.2</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="B40" s="29" t="n">
         <f aca="false">MAX(I19:I23)</f>
-        <v>6.04</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="B41" s="42" t="n">
         <f aca="false">B39-B40</f>
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="B42" s="29" t="n">
         <f aca="false">MIN(F30:F34)</f>
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/MDS_Decision_Workbook.xlsx
+++ b/docs/MDS_Decision_Workbook.xlsx
@@ -36,10 +36,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="699">
   <si>
-    <t xml:space="preserve">MDS decision workbook — Mess queue and allocation project (Group WGB3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every Management Decision Science course topic applied to the Chefs Touch lunch problem (Central CT and Munch Mess, lunch 11:30–14:30).</t>
+    <t xml:space="preserve">MDS decision workbook — Beyond the Bottleneck (Group WGB3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beyond the Bottleneck: Enabling Smarter Lunch Flow by Optimising Queue Management and Capacity Utilisation Across Chefs Touch Centres. Every MDS course topic applied (Central CT and Munch Mess, lunch 11:30–14:30).</t>
   </si>
   <si>
     <t xml:space="preserve">How to use</t>
@@ -501,10 +501,10 @@
     <t xml:space="preserve">Sessions 2–3: Nature of business decisions · Problem identification, structuring, root cause analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Problem statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">During the 11:30–14:30 lunch window, Chefs Touch serves about 2,960 plates. Demand is concentrated while kitchen, delivery and serving capacity are fixed, so students wait (~15 min observed), star dishes run out mid-service and replenishment arrives during the peak. Decision question: are resources (food, serving lines, students' choice of mess) reaching the right centre, in the right quantity, at the right time?</t>
+    <t xml:space="preserve">Problem statement (Phase 2: Beyond the Bottleneck)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During the 11:30–14:30 lunch window, Chefs Touch serves about 2,960 students. Total serving capacity is enough on average but is used unevenly: one centre is saturated while another has spare capacity, so students wait (~15 min observed) and star-dish run-outs at the busy centre make it worse. Decision question: how should student flow and serving capacity be balanced across CT's centres, minute by minute, so that waiting falls without adding staff or space? (Phase 1, 'The Two-Hour Bottleneck', asked whether food reached the right centre in the right quantity at the right time; that question continues in S7 and S10-11.)</t>
   </si>
   <si>
     <t xml:space="preserve">Session 2: nature of the decision</t>
@@ -2878,11 +2878,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="21186051"/>
-        <c:axId val="36980189"/>
+        <c:axId val="41725249"/>
+        <c:axId val="33609352"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21186051"/>
+        <c:axId val="41725249"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2948,7 +2948,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36980189"/>
+        <c:crossAx val="33609352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2956,7 +2956,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36980189"/>
+        <c:axId val="33609352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3032,7 +3032,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21186051"/>
+        <c:crossAx val="41725249"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3832,11 +3832,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="78154611"/>
-        <c:axId val="73859903"/>
+        <c:axId val="42397101"/>
+        <c:axId val="96811856"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="78154611"/>
+        <c:axId val="42397101"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3868,7 +3868,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73859903"/>
+        <c:crossAx val="96811856"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3876,7 +3876,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73859903"/>
+        <c:axId val="96811856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3952,7 +3952,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78154611"/>
+        <c:crossAx val="42397101"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4147,11 +4147,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="25705602"/>
-        <c:axId val="23205098"/>
+        <c:axId val="76788725"/>
+        <c:axId val="43018370"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25705602"/>
+        <c:axId val="76788725"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4183,7 +4183,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23205098"/>
+        <c:crossAx val="43018370"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4191,7 +4191,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23205098"/>
+        <c:axId val="43018370"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4233,7 +4233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25705602"/>
+        <c:crossAx val="76788725"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4589,11 +4589,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="53313538"/>
-        <c:axId val="95202996"/>
+        <c:axId val="3830711"/>
+        <c:axId val="5675616"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="53313538"/>
+        <c:axId val="3830711"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4625,7 +4625,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95202996"/>
+        <c:crossAx val="5675616"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4633,7 +4633,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="95202996"/>
+        <c:axId val="5675616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4675,7 +4675,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53313538"/>
+        <c:crossAx val="3830711"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4907,11 +4907,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="65048712"/>
-        <c:axId val="84066847"/>
+        <c:axId val="23516426"/>
+        <c:axId val="92118349"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="65048712"/>
+        <c:axId val="23516426"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4987,12 +4987,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84066847"/>
+        <c:crossAx val="92118349"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="84066847"/>
+        <c:axId val="92118349"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5068,7 +5068,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65048712"/>
+        <c:crossAx val="23516426"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5233,11 +5233,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="97367826"/>
-        <c:axId val="94085906"/>
+        <c:axId val="46110289"/>
+        <c:axId val="19228237"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97367826"/>
+        <c:axId val="46110289"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5269,7 +5269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94085906"/>
+        <c:crossAx val="19228237"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5277,7 +5277,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94085906"/>
+        <c:axId val="19228237"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5319,7 +5319,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97367826"/>
+        <c:crossAx val="46110289"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5747,7 +5747,7 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -11404,7 +11404,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="91.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
         <v>156</v>
       </c>

--- a/docs/MDS_Decision_Workbook.xlsx
+++ b/docs/MDS_Decision_Workbook.xlsx
@@ -276,7 +276,7 @@
     <t xml:space="preserve">From field work, CT or the group</t>
   </si>
   <si>
-    <t xml:space="preserve">2,960 students; seats 900 / 500; 2 stations + 1 scanner per mess</t>
+    <t xml:space="preserve">2,960 students; seats 900 / 492; 2 stations + 1 scanner per mess</t>
   </si>
   <si>
     <t xml:space="preserve">Group estimate</t>
@@ -2985,7 +2985,7 @@
     <t xml:space="preserve">Stage 3: eating</t>
   </si>
   <si>
-    <t xml:space="preserve">Take a seat if free (900 / 500), else wait; eat for uniform 12–15 min</t>
+    <t xml:space="preserve">Take a seat if free (900 / 492), else wait; eat for uniform 12–15 min</t>
   </si>
   <si>
     <t xml:space="preserve">seats, eat_lo/hi</t>
@@ -5336,11 +5336,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="48609536"/>
-        <c:axId val="61275530"/>
+        <c:axId val="50982440"/>
+        <c:axId val="10555494"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48609536"/>
+        <c:axId val="50982440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5372,7 +5372,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61275530"/>
+        <c:crossAx val="10555494"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5380,7 +5380,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61275530"/>
+        <c:axId val="10555494"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5456,7 +5456,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48609536"/>
+        <c:crossAx val="50982440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5704,11 +5704,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="45861843"/>
-        <c:axId val="62849978"/>
+        <c:axId val="83326717"/>
+        <c:axId val="40401674"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="45861843"/>
+        <c:axId val="83326717"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5774,7 +5774,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62849978"/>
+        <c:crossAx val="40401674"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5782,7 +5782,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62849978"/>
+        <c:axId val="40401674"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5858,7 +5858,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45861843"/>
+        <c:crossAx val="83326717"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6658,11 +6658,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="12605798"/>
-        <c:axId val="55105881"/>
+        <c:axId val="35481415"/>
+        <c:axId val="88590308"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="12605798"/>
+        <c:axId val="35481415"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6694,7 +6694,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55105881"/>
+        <c:crossAx val="88590308"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6702,7 +6702,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55105881"/>
+        <c:axId val="88590308"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6778,7 +6778,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12605798"/>
+        <c:crossAx val="35481415"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7422,11 +7422,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="36984693"/>
-        <c:axId val="90611264"/>
+        <c:axId val="47636435"/>
+        <c:axId val="43479"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="36984693"/>
+        <c:axId val="47636435"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7458,7 +7458,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90611264"/>
+        <c:crossAx val="43479"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7466,7 +7466,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90611264"/>
+        <c:axId val="43479"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7542,7 +7542,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36984693"/>
+        <c:crossAx val="47636435"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7737,11 +7737,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="88720546"/>
-        <c:axId val="41637514"/>
+        <c:axId val="28356669"/>
+        <c:axId val="68303611"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="88720546"/>
+        <c:axId val="28356669"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7773,7 +7773,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41637514"/>
+        <c:crossAx val="68303611"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7781,7 +7781,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41637514"/>
+        <c:axId val="68303611"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7823,7 +7823,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88720546"/>
+        <c:crossAx val="28356669"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7988,11 +7988,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="64340041"/>
-        <c:axId val="33257741"/>
+        <c:axId val="26361118"/>
+        <c:axId val="73593723"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="64340041"/>
+        <c:axId val="26361118"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8024,7 +8024,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33257741"/>
+        <c:crossAx val="73593723"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8032,7 +8032,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33257741"/>
+        <c:axId val="73593723"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8074,7 +8074,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64340041"/>
+        <c:crossAx val="26361118"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13115,7 +13115,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="31" t="n">
         <f aca="false">Inputs!$B$9/(Inputs!$B$9+Inputs!$B$10)</f>
-        <v>0.642857142857143</v>
+        <v>0.646551724137931</v>
       </c>
       <c r="H39" s="31"/>
       <c r="I39" s="31"/>
@@ -13805,7 +13805,7 @@
         <v>105</v>
       </c>
       <c r="B10" s="14" t="n">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>102</v>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="B92" s="27" t="n">
         <f aca="false">Inputs!$B$10/Inputs!$B$87</f>
-        <v>37.037037037037</v>
+        <v>36.4444444444444</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>138</v>
@@ -21628,7 +21628,7 @@
       </c>
       <c r="F58" s="32" t="n">
         <f aca="false">Inputs!$B$10</f>
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="G58" s="32" t="n">
         <f aca="false">Inputs!$B$9</f>
@@ -21636,7 +21636,7 @@
       </c>
       <c r="H58" s="32" t="n">
         <f aca="false">Inputs!$B$10</f>
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/MDS_Decision_Workbook.xlsx
+++ b/docs/MDS_Decision_Workbook.xlsx
@@ -49,7 +49,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.14 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.13 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -73,7 +73,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.04 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.05 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -85,7 +85,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.01 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.02 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -109,7 +109,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.53 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.63 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -133,7 +133,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.09 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.10 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -145,7 +145,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.42 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.38 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -157,7 +157,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.12 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.16 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -169,7 +169,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.62 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.55 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -181,7 +181,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.18 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.24 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -193,7 +193,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.32 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.31 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -205,7 +205,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.50 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.45 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -217,7 +217,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Simulated: 20 lunches, ±0.28 (95% CI)</t>
+          <t xml:space="preserve">Simulated: 20 lunches, ±0.26 (95% CI)</t>
         </r>
       </text>
     </comment>
@@ -226,7 +226,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="1037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="1036">
   <si>
     <t xml:space="preserve">MDS decision workbook — Beyond the Bottleneck (Group WGB3)</t>
   </si>
@@ -285,7 +285,7 @@
     <t xml:space="preserve">The group's figure, not yet timed</t>
   </si>
   <si>
-    <t xml:space="preserve">Eating 12–15 min; disposal ≤ 2 min; food ready 70% of the time</t>
+    <t xml:space="preserve">Eating 14–18 min; disposal ≤ 2 min; food ready 70% of the time</t>
   </si>
   <si>
     <t xml:space="preserve">Assumed</t>
@@ -312,7 +312,7 @@
     <t xml:space="preserve">Output of the simulator, 20 lunches per row</t>
   </si>
   <si>
-    <t xml:space="preserve">Average wait 4.4 → 0.8 min on a busy day</t>
+    <t xml:space="preserve">Average wait 4.3 → 0.8 min on a busy day</t>
   </si>
   <si>
     <t xml:space="preserve">Policy</t>
@@ -573,7 +573,7 @@
     <t xml:space="preserve">Normal visit, scan to leaving (quiet times)</t>
   </si>
   <si>
-    <t xml:space="preserve">Group observation on a normal day</t>
+    <t xml:space="preserve">Group: about 20 min on a normal day</t>
   </si>
   <si>
     <t xml:space="preserve">Checks (calibration)</t>
@@ -582,7 +582,7 @@
     <t xml:space="preserve">Throughput time range: low (quiet)</t>
   </si>
   <si>
-    <t xml:space="preserve">Group: door to leaving takes 17–25 min depending on the surge</t>
+    <t xml:space="preserve">Group: door to leaving takes 17–35 min depending on the rush</t>
   </si>
   <si>
     <t xml:space="preserve">Throughput time range: high (surge)</t>
@@ -633,7 +633,7 @@
     <t xml:space="preserve">Stage 1: collect a plate after the scan (low)</t>
   </si>
   <si>
-    <t xml:space="preserve">Group: scanning + plate takes up to ~45 s. Time it</t>
+    <t xml:space="preserve">Group: scan + plate takes 30–45 s</t>
   </si>
   <si>
     <t xml:space="preserve">Stage 1: collect a plate after the scan (high)</t>
@@ -651,19 +651,19 @@
     <t xml:space="preserve">S15, LP, Decision Rule, simulator</t>
   </si>
   <si>
-    <t xml:space="preserve">Stage 2: walk the rest of the food line after the station (low)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time a few students from station to table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stage 2: walk the rest of the food line (high)</t>
+    <t xml:space="preserve">Stage 2: rest of food collection after the station (low)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group: collecting food takes 1–2 min without a queue, incl. ~6 s at the station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage 2: rest of food collection (high)</t>
   </si>
   <si>
     <t xml:space="preserve">Stage 3: eating at a table (low)</t>
   </si>
   <si>
-    <t xml:space="preserve">Group: 12–15 min</t>
+    <t xml:space="preserve">Group: 14–18 min</t>
   </si>
   <si>
     <t xml:space="preserve">Stage 3: eating at a table (high)</t>
@@ -711,7 +711,7 @@
     <t xml:space="preserve">Minutes from the start of a department's lunch break to the mess door: mean</t>
   </si>
   <si>
-    <t xml:space="preserve">Chosen so the no-screen simulation fits the 17–25 min visit and ~15 min peak delay. Logs + timetable measure it</t>
+    <t xml:space="preserve">Chosen so the no-screen simulation fits the 17–35 min visit and ~15 min peak delay. Logs + timetable measure it</t>
   </si>
   <si>
     <t xml:space="preserve">Arrival Curve, simulator</t>
@@ -1557,7 +1557,7 @@
     <t xml:space="preserve">A2 Door screens, queue information only</t>
   </si>
   <si>
-    <t xml:space="preserve">Busy day: wait 4.4 → 1.3 min (simulated)</t>
+    <t xml:space="preserve">Busy day: wait 4.3 → 1.2 min (simulated)</t>
   </si>
   <si>
     <t xml:space="preserve">Two screens + a laptop; needs data access</t>
@@ -1566,7 +1566,7 @@
     <t xml:space="preserve">A3 Screens + food status (proposal)</t>
   </si>
   <si>
-    <t xml:space="preserve">Busy day: wait 4.4 → 0.8 min (simulated)</t>
+    <t xml:space="preserve">Busy day: wait 4.3 → 0.8 min (simulated)</t>
   </si>
   <si>
     <t xml:space="preserve">Same as A2 + manager taps food status</t>
@@ -1575,7 +1575,7 @@
     <t xml:space="preserve">A4 3rd serving station at Central</t>
   </si>
   <si>
-    <t xml:space="preserve">Busy day: 4.4 → 1.1 min; best on normal days</t>
+    <t xml:space="preserve">Busy day: 4.3 → 0.6 min; best on normal days</t>
   </si>
   <si>
     <t xml:space="preserve">Staff cost every day; space at counter</t>
@@ -1593,7 +1593,7 @@
     <t xml:space="preserve">A7 Stagger class end times</t>
   </si>
   <si>
-    <t xml:space="preserve">SMI 15 min earlier: today's wait 4.4 → 3.2 min; TAPMI 15 min later: → 1.9 (simulated)</t>
+    <t xml:space="preserve">SMI 15 min earlier: today's wait 4.3 → 3.3 min; TAPMI 15 min later: → 1.7 (simulated)</t>
   </si>
   <si>
     <t xml:space="preserve">Needs academic administration</t>
@@ -2253,544 +2253,541 @@
     <t xml:space="preserve">A1 No system (today)</t>
   </si>
   <si>
+    <t xml:space="preserve">±0.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A3 Door screens + food status (proposal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4 3rd serving station at Central (no screens)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A5 Proposal + 3rd serving station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability of each kind of day (Inputs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(kind of day): from the biometric logs once available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← must be 100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students per lunch (busy day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoff = minutes saved per student compared with today = wait(A1) − wait(alternative)   [higher is better]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximax (optimistic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximin (pessimistic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurwicz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laplace (equal likelihood)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMV (with probabilities)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student-hours saved per lunch (EMV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best alternative by criterion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best without an extra station's staff (A1–A3 only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurwicz α (degree of optimism, analyst's choice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regret (opportunity loss, minutes) = best payoff on that kind of day − this payoff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum regret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected regret (EOL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimax regret choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum expected regret (= EMV choice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value of perfect information (minutes per student)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected payoff WITH perfect information (best alternative for each kind of day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best EMV without perfect information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVPI = extra minutes per student if we knew the kind of day in advance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check: EVPI equals the minimum expected regret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reading it: the payoff is waiting time only, so the objective stays explicit. A5 has the lowest wait on every kind of day, so EVPI is 0: knowing the kind of day in advance would not change the choice. Staff cost is not in these minutes: A4 and A5 need a third station's staff every day, while A3 needs two screens and the manager's taps. Without extra staff, the proposal (A3) is the best choice (row 25). On normal days a third station alone does a little better (0.1 vs 0.4 min). A1 and A4 are without the system; A2, A3 and A5 are with it. For a table of waits (lower is better) the criteria would be minimin and minimax; turning waits into minutes saved makes higher better, so the maximax / maximin names apply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heuristics: simple rules that give good answers fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session 18: Heuristics and metaheuristics — concepts and business applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Door-screen switching rule (used in the prototype)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predicted wait if you stay (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predicted wait at the other mess (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum saving to suggest a switch (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saving after the walk (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen says</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. When should the manager tap 'running low' (call the kitchen)? A reorder point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star dish served per minute at peak (= Central's serving capacity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead time from the call (worst case: has to be made, then sent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead time from the call (expected: 70% already made)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reorder point, worst case (portions left when the call must go)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The protocol (20 min of food) covers the expected refill but not the worst case (30 min): in that case a gap opens, and the Decision Rule charges it only to students who would reach the empty tray.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reorder point, expected case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our protocol: tap 'running low' with this many minutes of food left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portions left at the tap (at peak)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Heuristic vs full model (busy day, 60% follow the screens)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average wait (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90th pct wait (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No advice (today)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline (simulated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naive heuristic: send people to the shorter queue (≥ 2 min saving)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple rule; works at the doors because feedback is fast (30 s walk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equal-wait split, queues only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ignores food status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equal-wait split + food status (proposal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bisection search for the split; food delays only for students who would meet an empty tray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LP lower bound (fluid model, perfect foresight)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not achievable live: no randomness, no estimation delay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Metaheuristics (next step)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A replenishment schedule that minimises waiting + waste over a whole lunch has no closed-form answer because of the queues. A metaheuristic (simulated annealing or a genetic algorithm) can search over schedules, scoring each candidate by running our simulator: 'simulation-optimisation'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision rule: when the screen outside Central recommends Munch, and when it gives no advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The objective stays explicit: minimise each student's expected time to food (queue + walk + any food delay), without overloading the other mess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rule (the same logic the prototype runs; config/default.toml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. No advice if the data are stale: a scanner silent for longer than the limit on the Inputs tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. No advice if the star dish is out at both messes (no better option).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Time if you stay = queue wait here + food delay here. Time if you switch = walk + queue wait there + food delay there.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Food delay for a tray marked 'running low' or 'out': only if you would reach the counter after it empties and before its refill (refill clock runs from the call).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Recommend switching only if it saves at least the minimum saving + an uncertainty margin, AND the other mess still has spare capacity after the move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Never send everyone: move only enough students to equalise utilisation (capacity-weighted), so the other mess doesn't become the new bottleneck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Situation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wait at Central (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wait at Munch (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central star dish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min since Central called kitchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Munch star dish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min since Munch called kitchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrivals Central (/min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrivals Munch (/min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min since last scan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central refill due in (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central food delay (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Munch refill due in (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Munch food delay (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time if you stay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time if you switch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saving (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move /min to equalise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Munch ρ after the move</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen outside Central says</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quiet start of lunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak: Central queue, Munch quiet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak, but Munch is nearly full too</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central star dish OUT, kitchen just called</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central star dish OUT, called 16 min ago (late batch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central running low, called 2 min ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central running low, called 18 min ago, 4-min queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central scanner silent for 5 minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Star dish out at both messes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue cells are example situations: change them to test the rule. 'Refill due in' is the expected time still to wait given the minutes since the call and no refill yet: if 15 minutes have passed, the 10–14 minute 'already made' case is ruled out, so only the 30-minute case remains. 'Move /min to equalise' is how many students per minute would make both messes equally busy; the screen asks only that share (never everyone). The simulator applies the same rule through an equal-wait split (bisection), which also accounts for the walk and the queues the moved students create.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline vs intervention: four scenarios and stress tests (simulated, same students in every scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulated: python -m messq.scenarios, 20 lunches per row (seeds 0–19, the same students in every scenario); ± = 95% confidence interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The four scenarios on a busy day (2,960 students, 60% follow the screens)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg queue wait (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±95% CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg throughput, door to leaving (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90th pct throughput (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total incl. walk, decision to leaving (min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central stations busy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Munch stations busy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central peak load (30 min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Munch peak load (30 min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-outs per lunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirected students</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Followed the advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsuccessful redirects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Current system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Queue information only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Queue + food (proposal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N Naive: go to the shorter queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change vs today (proposal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definitions. Queue wait = minutes queueing for the scanner, a serving station and a seat (eating, the food line and disposal are activity time, not waiting). Throughput = door to leaving, all four stages. 90th percentile = the wait that 1 in 10 students exceed, per lunch, then averaged. Stations busy = share of 11:30–14:30 the serving stations were in use; peak load = arrivals ÷ capacity in the busiest 30 minutes (above 100% the queue grows). Unsuccessful redirect = a redirected student whose wait + walk exceeded the average wait of students who stayed at the mess they left and arrived within 2 minutes. Scenario 2 = the screens use queues but never hear about food; N = a naive 'go to the shorter queue' rule, shown for the herding point.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Stress tests: does the benefit persist? One input changed at a time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stress test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Current: wait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Queue only: wait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Proposal: wait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Proposal: ±95% CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Current: p90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Proposal: p90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduction (3 vs 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 beats 2?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-outs: 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-outs: 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsuccessful: 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsuccessful: 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demand +20% (3,552 students)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Students rush at the bell (lag 15 +/- 10 min, not 20 +/- 20)</t>
+  </si>
+  <si>
     <t xml:space="preserve">±0.14</t>
   </si>
   <si>
-    <t xml:space="preserve">±0.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A3 Door screens + food status (proposal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.04</t>
+    <t xml:space="preserve">Heavy lab day: 70% of MIT eat 13:00-14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No MIT labs: all MIT eat 12:00-13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stagger: SMI lunch 15 min earlier (11:45-12:45)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stagger: TAPMI lunch 15 min later (13:20-14:15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One bell curve (old assumption: peak 13:05, spread 35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only 30% follow the screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everyone follows the screens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slower serving: 8 students/min per station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faster serving: 12 students/min per station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More stock-outs: next batch never ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No stock-outs: next batch always ready</t>
   </si>
   <si>
     <t xml:space="preserve">±0.09</t>
   </si>
   <si>
-    <t xml:space="preserve">±0.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A4 3rd serving station at Central (no screens)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A5 Proposal + 3rd serving station</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probability of each kind of day (Inputs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(kind of day): from the biometric logs once available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">← must be 100%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Students per lunch (busy day)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoff = minutes saved per student compared with today = wait(A1) − wait(alternative)   [higher is better]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alternative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximax (optimistic)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximin (pessimistic)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurwicz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laplace (equal likelihood)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMV (with probabilities)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student-hours saved per lunch (EMV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best alternative by criterion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best without an extra station's staff (A1–A3 only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurwicz α (degree of optimism, analyst's choice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regret (opportunity loss, minutes) = best payoff on that kind of day − this payoff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum regret</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected regret (EOL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimax regret choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum expected regret (= EMV choice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value of perfect information (minutes per student)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected payoff WITH perfect information (best alternative for each kind of day)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Best EMV without perfect information</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVPI = extra minutes per student if we knew the kind of day in advance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check: EVPI equals the minimum expected regret</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reading it: the payoff is waiting time only, so the objective stays explicit. A5 has the lowest wait on every kind of day, so EVPI is 0: knowing the kind of day in advance would not change the choice. Staff cost is not in these minutes: A4 and A5 need a third station's staff every day, while A3 needs two screens and the manager's taps. Without extra staff, the proposal (A3) is the best choice (row 25). On normal days a third station alone does a little better (0.1 vs 0.4 min). A1 and A4 are without the system; A2, A3 and A5 are with it. For a table of waits (lower is better) the criteria would be minimin and minimax; turning waits into minutes saved makes higher better, so the maximax / maximin names apply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heuristics: simple rules that give good answers fast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session 18: Heuristics and metaheuristics — concepts and business applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Door-screen switching rule (used in the prototype)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predicted wait if you stay (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predicted wait at the other mess (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum saving to suggest a switch (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saving after the walk (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screen says</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. When should the manager tap 'running low' (call the kitchen)? A reorder point</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star dish served per minute at peak (= Central's serving capacity)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead time from the call (worst case: has to be made, then sent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead time from the call (expected: 70% already made)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reorder point, worst case (portions left when the call must go)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The protocol (20 min of food) covers the expected refill but not the worst case (30 min): in that case a gap opens, and the Decision Rule charges it only to students who would reach the empty tray.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reorder point, expected case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Our protocol: tap 'running low' with this many minutes of food left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portions left at the tap (at peak)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Heuristic vs full model (busy day, 60% follow the screens)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average wait (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90th pct wait (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No advice (today)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline (simulated)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naive heuristic: send people to the shorter queue (≥ 2 min saving)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple rule; works at the doors because feedback is fast (30 s walk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equal-wait split, queues only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ignores food status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equal-wait split + food status (proposal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bisection search for the split; food delays only for students who would meet an empty tray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LP lower bound (fluid model, perfect foresight)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not achievable live: no randomness, no estimation delay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Metaheuristics (next step)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A replenishment schedule that minimises waiting + waste over a whole lunch has no closed-form answer because of the queues. A metaheuristic (simulated annealing or a genetic algorithm) can search over schedules, scoring each candidate by running our simulator: 'simulation-optimisation'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decision rule: when the screen outside Central recommends Munch, and when it gives no advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The objective stays explicit: minimise each student's expected time to food (queue + walk + any food delay), without overloading the other mess</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The rule (the same logic the prototype runs; config/default.toml)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. No advice if the data are stale: a scanner silent for longer than the limit on the Inputs tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. No advice if the star dish is out at both messes (no better option).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Time if you stay = queue wait here + food delay here. Time if you switch = walk + queue wait there + food delay there.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Food delay for a tray marked 'running low' or 'out': only if you would reach the counter after it empties and before its refill (refill clock runs from the call).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Recommend switching only if it saves at least the minimum saving + an uncertainty margin, AND the other mess still has spare capacity after the move.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Never send everyone: move only enough students to equalise utilisation (capacity-weighted), so the other mess doesn't become the new bottleneck.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Situation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wait at Central (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wait at Munch (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central star dish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min since Central called kitchen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Munch star dish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min since Munch called kitchen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrivals Central (/min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrivals Munch (/min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min since last scan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central refill due in (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central food delay (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Munch refill due in (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Munch food delay (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time if you stay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time if you switch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saving (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Move /min to equalise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Munch ρ after the move</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screen outside Central says</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiet start of lunch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak: Central queue, Munch quiet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak, but Munch is nearly full too</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central star dish OUT, kitchen just called</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OUT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central star dish OUT, called 16 min ago (late batch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central running low, called 2 min ago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central running low, called 18 min ago, 4-min queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central scanner silent for 5 minutes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Star dish out at both messes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue cells are example situations: change them to test the rule. 'Refill due in' is the expected time still to wait given the minutes since the call and no refill yet: if 15 minutes have passed, the 10–14 minute 'already made' case is ruled out, so only the 30-minute case remains. 'Move /min to equalise' is how many students per minute would make both messes equally busy; the screen asks only that share (never everyone). The simulator applies the same rule through an equal-wait split (bisection), which also accounts for the walk and the queues the moved students create.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline vs intervention: four scenarios and stress tests (simulated, same students in every scenario)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulated: python -m messq.scenarios, 20 lunches per row (seeds 0–19, the same students in every scenario); ± = 95% confidence interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The four scenarios on a busy day (2,960 students, 60% follow the screens)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg queue wait (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg throughput, door to leaving (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90th pct throughput (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total incl. walk, decision to leaving (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central stations busy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Munch stations busy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central peak load (30 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Munch peak load (30 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run-outs per lunch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redirected students</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Followed the advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unsuccessful redirects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Current system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">–</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Queue information only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Queue + food (proposal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N Naive: go to the shorter queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change vs today (proposal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definitions. Queue wait = minutes queueing for the scanner, a serving station and a seat (eating, the food line and disposal are activity time, not waiting). Throughput = door to leaving, all four stages. 90th percentile = the wait that 1 in 10 students exceed, per lunch, then averaged. Stations busy = share of 11:30–14:30 the serving stations were in use; peak load = arrivals ÷ capacity in the busiest 30 minutes (above 100% the queue grows). Unsuccessful redirect = a redirected student whose wait + walk exceeded the average wait of students who stayed at the mess they left and arrived within 2 minutes. Scenario 2 = the screens use queues but never hear about food; N = a naive 'go to the shorter queue' rule, shown for the herding point.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Stress tests: does the benefit persist? One input changed at a time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stress test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Current: wait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Queue only: wait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Proposal: wait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Proposal: ±95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Current: p90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Proposal: p90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reduction (3 vs 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 beats 2?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run-outs: 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Run-outs: 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unsuccessful: 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unsuccessful: 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demand +20% (3,552 students)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Students rush at the bell (lag 15 +/- 10 min, not 20 +/- 20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heavy lab day: 70% of MIT eat 13:00-14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No MIT labs: all MIT eat 12:00-13:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stagger: SMI lunch 15 min earlier (11:45-12:45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stagger: TAPMI lunch 15 min later (13:20-14:15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One bell curve (old assumption: peak 13:05, spread 35)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only 30% follow the screens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everyone follows the screens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slower serving: 8 students/min per station</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faster serving: 12 students/min per station</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More stock-outs: next batch never ready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">±0.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No stock-outs: next batch always ready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slower eating: 15-18 min</t>
+    <t xml:space="preserve">Slower eating: 17-21 min</t>
   </si>
   <si>
     <t xml:space="preserve">Smallest reduction across all stress tests</t>
@@ -2850,7 +2847,7 @@
     <t xml:space="preserve">Simulator 4 + seat limits</t>
   </si>
   <si>
-    <t xml:space="preserve">Seats rarely fill (eating 12–15 min): no change</t>
+    <t xml:space="preserve">Seats rarely fill (eating 14–18 min): no change</t>
   </si>
   <si>
     <t xml:space="preserve">Simulator 5 + food run-outs and refills (full model)</t>
@@ -2943,7 +2940,7 @@
     <t xml:space="preserve">Stage 1: entrance</t>
   </si>
   <si>
-    <t xml:space="preserve">FCFS queue for the face scanner (2 s each, cv 0.3), then collecting a plate (uniform 15–35 s). The scan time is what the biometric log records</t>
+    <t xml:space="preserve">FCFS queue for the face scanner (2 s each, cv 0.3), then collecting a plate (uniform 28–43 s; 30–45 s with the scan). The scan time is what the biometric log records</t>
   </si>
   <si>
     <t xml:space="preserve">scan_s, plate_lo/hi</t>
@@ -2952,7 +2949,7 @@
     <t xml:space="preserve">Stage 2: food</t>
   </si>
   <si>
-    <t xml:space="preserve">FCFS queue for 2 serving stations; service time gamma with mean 6 s and cv 0.6 (M/G/c); then walking the food line (uniform 40–80 s)</t>
+    <t xml:space="preserve">FCFS queue for 2 serving stations; service time gamma with mean 6 s and cv 0.6 (M/G/c); then the rest of food collection (uniform 54–114 s; 1–2 min in all)</t>
   </si>
   <si>
     <t xml:space="preserve">mu, line_lo/hi, service_cv</t>
@@ -2985,7 +2982,7 @@
     <t xml:space="preserve">Stage 3: eating</t>
   </si>
   <si>
-    <t xml:space="preserve">Take a seat if free (900 / 492), else wait; eat for uniform 12–15 min</t>
+    <t xml:space="preserve">Take a seat if free (900 / 492), else wait; eat for uniform 14–18 min</t>
   </si>
   <si>
     <t xml:space="preserve">seats, eat_lo/hi</t>
@@ -3048,7 +3045,7 @@
     <t xml:space="preserve">--runs</t>
   </si>
   <si>
-    <t xml:space="preserve">Validation so far: the simulated normal visit and peak throughput fall in the measured 17–25 min range (Checks), the no-screen 90th percentile wait is close to the ~15 min observed, and the spreadsheet-like simulator reproduces S15 without screens (Reconciliation). Not yet validated: the arrival curve, the habit split and the service rate (Data Collection).</t>
+    <t xml:space="preserve">Validation so far: the simulated normal visit and peak throughput fall in the group's 17–35 min range (Checks), the no-screen 90th percentile wait is close to the ~15 min observed, and the spreadsheet-like simulator reproduces S15 without screens (Reconciliation). Not yet validated: the arrival curve, the habit split and the service rate (Data Collection).</t>
   </si>
   <si>
     <t xml:space="preserve">Stage 2: collect the minimum data to prove (or disprove) the bottleneck</t>
@@ -3303,7 +3300,7 @@
     <t xml:space="preserve">Throughput with no queues is within the measured range</t>
   </si>
   <si>
-    <t xml:space="preserve">17–25 min (group); quiet visit ~18</t>
+    <t xml:space="preserve">17–35 min (group); quiet visit ~18</t>
   </si>
   <si>
     <t xml:space="preserve">Simulated throughput for students who met no queue (today)</t>
@@ -5336,11 +5333,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="50982440"/>
-        <c:axId val="10555494"/>
+        <c:axId val="14523566"/>
+        <c:axId val="31784252"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50982440"/>
+        <c:axId val="14523566"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5372,7 +5369,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10555494"/>
+        <c:crossAx val="31784252"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5380,7 +5377,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10555494"/>
+        <c:axId val="31784252"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5456,7 +5453,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50982440"/>
+        <c:crossAx val="14523566"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5704,11 +5701,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="83326717"/>
-        <c:axId val="40401674"/>
+        <c:axId val="945789"/>
+        <c:axId val="87990573"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="83326717"/>
+        <c:axId val="945789"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5774,7 +5771,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40401674"/>
+        <c:crossAx val="87990573"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5782,7 +5779,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40401674"/>
+        <c:axId val="87990573"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5858,7 +5855,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83326717"/>
+        <c:crossAx val="945789"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6658,11 +6655,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="35481415"/>
-        <c:axId val="88590308"/>
+        <c:axId val="84259706"/>
+        <c:axId val="90036534"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="35481415"/>
+        <c:axId val="84259706"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6694,7 +6691,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88590308"/>
+        <c:crossAx val="90036534"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6702,7 +6699,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88590308"/>
+        <c:axId val="90036534"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6778,7 +6775,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35481415"/>
+        <c:crossAx val="84259706"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7422,11 +7419,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="47636435"/>
-        <c:axId val="43479"/>
+        <c:axId val="18725888"/>
+        <c:axId val="40268349"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="47636435"/>
+        <c:axId val="18725888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7458,7 +7455,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43479"/>
+        <c:crossAx val="40268349"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7466,7 +7463,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43479"/>
+        <c:axId val="40268349"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7542,7 +7539,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47636435"/>
+        <c:crossAx val="18725888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7720,16 +7717,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.652</c:v>
+                  <c:v>3.664</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.077</c:v>
+                  <c:v>4.022</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.411</c:v>
+                  <c:v>3.534</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.545</c:v>
+                  <c:v>4.558</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7737,11 +7734,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="28356669"/>
-        <c:axId val="68303611"/>
+        <c:axId val="27119591"/>
+        <c:axId val="70456556"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="28356669"/>
+        <c:axId val="27119591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7773,7 +7770,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68303611"/>
+        <c:crossAx val="70456556"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7781,7 +7778,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="68303611"/>
+        <c:axId val="70456556"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7823,7 +7820,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28356669"/>
+        <c:crossAx val="27119591"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7971,16 +7968,16 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4.385</c:v>
+                  <c:v>4.31</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.299</c:v>
+                  <c:v>1.191</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.814</c:v>
+                  <c:v>0.798</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.741</c:v>
+                  <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7988,11 +7985,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="26361118"/>
-        <c:axId val="73593723"/>
+        <c:axId val="71433800"/>
+        <c:axId val="4122800"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26361118"/>
+        <c:axId val="71433800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8024,7 +8021,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73593723"/>
+        <c:crossAx val="4122800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8032,7 +8029,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73593723"/>
+        <c:axId val="4122800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8074,7 +8071,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26361118"/>
+        <c:crossAx val="71433800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8949,13 +8946,13 @@
         <v>674</v>
       </c>
       <c r="B7" s="51" t="n">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="C7" s="51" t="n">
-        <v>4.38</v>
+        <v>4.31</v>
       </c>
       <c r="D7" s="51" t="n">
-        <v>14.99</v>
+        <v>14.82</v>
       </c>
       <c r="F7" s="54" t="s">
         <v>675</v>
@@ -8972,13 +8969,13 @@
         <v>442</v>
       </c>
       <c r="B8" s="51" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="C8" s="51" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="D8" s="51" t="n">
-        <v>5.09</v>
+        <v>4.96</v>
       </c>
       <c r="F8" s="54" t="s">
         <v>678</v>
@@ -8995,62 +8992,62 @@
         <v>681</v>
       </c>
       <c r="B9" s="51" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="C9" s="51" t="n">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="D9" s="51" t="n">
-        <v>4.25</v>
+        <v>4.13</v>
       </c>
       <c r="F9" s="54" t="s">
+        <v>678</v>
+      </c>
+      <c r="G9" s="54" t="s">
         <v>682</v>
       </c>
-      <c r="G9" s="54" t="s">
+      <c r="H9" s="54" t="s">
         <v>683</v>
-      </c>
-      <c r="H9" s="54" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
+        <v>684</v>
+      </c>
+      <c r="B10" s="51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C10" s="51" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D10" s="51" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="F10" s="54" t="s">
         <v>685</v>
       </c>
-      <c r="B10" s="51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C10" s="51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="D10" s="51" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="F10" s="54" t="s">
+      <c r="G10" s="54" t="s">
         <v>686</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="H10" s="54" t="s">
         <v>687</v>
-      </c>
-      <c r="H10" s="54" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B11" s="51" t="n">
         <v>0.05</v>
       </c>
       <c r="C11" s="51" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="D11" s="51" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="F11" s="54" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="G11" s="54" t="s">
         <v>690</v>
@@ -9194,15 +9191,15 @@
       </c>
       <c r="C20" s="28" t="n">
         <f aca="false">C$7-C8</f>
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="D20" s="28" t="n">
         <f aca="false">D$7-D8</f>
-        <v>9.9</v>
+        <v>9.86</v>
       </c>
       <c r="E20" s="28" t="n">
         <f aca="false">MAX(B20:D20)</f>
-        <v>9.9</v>
+        <v>9.86</v>
       </c>
       <c r="F20" s="28" t="n">
         <f aca="false">MIN(B20:D20)</f>
@@ -9210,7 +9207,7 @@
       </c>
       <c r="G20" s="28" t="n">
         <f aca="false">$B$27*E20+(1-$B$27)*F20</f>
-        <v>4.224</v>
+        <v>4.208</v>
       </c>
       <c r="H20" s="28" t="n">
         <f aca="false">AVERAGE(B20:D20)</f>
@@ -9218,11 +9215,11 @@
       </c>
       <c r="I20" s="28" t="n">
         <f aca="false">SUMPRODUCT(B20:D20,$B$14:$D$14)</f>
-        <v>3.652</v>
+        <v>3.664</v>
       </c>
       <c r="J20" s="35" t="n">
         <f aca="false">I20*$B$15/60</f>
-        <v>180.165333333333</v>
+        <v>180.757333333333</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9231,121 +9228,121 @@
       </c>
       <c r="B21" s="28" t="n">
         <f aca="false">B$7-B9</f>
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="C21" s="28" t="n">
         <f aca="false">C$7-C9</f>
-        <v>3.57</v>
+        <v>3.51</v>
       </c>
       <c r="D21" s="28" t="n">
         <f aca="false">D$7-D9</f>
-        <v>10.74</v>
+        <v>10.69</v>
       </c>
       <c r="E21" s="28" t="n">
         <f aca="false">MAX(B21:D21)</f>
-        <v>10.74</v>
+        <v>10.69</v>
       </c>
       <c r="F21" s="28" t="n">
         <f aca="false">MIN(B21:D21)</f>
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="G21" s="28" t="n">
         <f aca="false">$B$27*E21+(1-$B$27)*F21</f>
-        <v>4.584</v>
+        <v>4.534</v>
       </c>
       <c r="H21" s="28" t="n">
         <f aca="false">AVERAGE(B21:D21)</f>
-        <v>4.93</v>
+        <v>4.87666666666667</v>
       </c>
       <c r="I21" s="28" t="n">
         <f aca="false">SUMPRODUCT(B21:D21,$B$14:$D$14)</f>
-        <v>4.077</v>
+        <v>4.022</v>
       </c>
       <c r="J21" s="35" t="n">
         <f aca="false">I21*$B$15/60</f>
-        <v>201.132</v>
+        <v>198.418666666667</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B22" s="28" t="n">
         <f aca="false">B$7-B10</f>
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="C22" s="28" t="n">
         <f aca="false">C$7-C10</f>
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="D22" s="28" t="n">
         <f aca="false">D$7-D10</f>
-        <v>7.62</v>
+        <v>7.37</v>
       </c>
       <c r="E22" s="28" t="n">
         <f aca="false">MAX(B22:D22)</f>
-        <v>7.62</v>
+        <v>7.37</v>
       </c>
       <c r="F22" s="28" t="n">
         <f aca="false">MIN(B22:D22)</f>
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="G22" s="28" t="n">
         <f aca="false">$B$27*E22+(1-$B$27)*F22</f>
-        <v>3.522</v>
+        <v>3.398</v>
       </c>
       <c r="H22" s="28" t="n">
         <f aca="false">AVERAGE(B22:D22)</f>
-        <v>3.90333333333333</v>
+        <v>3.93</v>
       </c>
       <c r="I22" s="28" t="n">
         <f aca="false">SUMPRODUCT(B22:D22,$B$14:$D$14)</f>
-        <v>3.411</v>
+        <v>3.534</v>
       </c>
       <c r="J22" s="35" t="n">
         <f aca="false">I22*$B$15/60</f>
-        <v>168.276</v>
+        <v>174.344</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B23" s="28" t="n">
         <f aca="false">B$7-B11</f>
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="C23" s="28" t="n">
         <f aca="false">C$7-C11</f>
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="D23" s="28" t="n">
         <f aca="false">D$7-D11</f>
-        <v>11.59</v>
+        <v>11.65</v>
       </c>
       <c r="E23" s="28" t="n">
         <f aca="false">MAX(B23:D23)</f>
-        <v>11.59</v>
+        <v>11.65</v>
       </c>
       <c r="F23" s="28" t="n">
         <f aca="false">MIN(B23:D23)</f>
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="G23" s="28" t="n">
         <f aca="false">$B$27*E23+(1-$B$27)*F23</f>
-        <v>5.11</v>
+        <v>5.116</v>
       </c>
       <c r="H23" s="28" t="n">
         <f aca="false">AVERAGE(B23:D23)</f>
-        <v>5.45333333333333</v>
+        <v>5.47</v>
       </c>
       <c r="I23" s="28" t="n">
         <f aca="false">SUMPRODUCT(B23:D23,$B$14:$D$14)</f>
-        <v>4.545</v>
+        <v>4.558</v>
       </c>
       <c r="J23" s="35" t="n">
         <f aca="false">I23*$B$15/60</f>
-        <v>224.22</v>
+        <v>224.861333333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9358,7 +9355,7 @@
       </c>
       <c r="F24" s="53" t="str">
         <f aca="false">INDEX($A$19:$A$23,MATCH(MAX(F19:F23),F19:F23,0))</f>
-        <v>A4 3rd serving station at Central (no screens)</v>
+        <v>A5 Proposal + 3rd serving station</v>
       </c>
       <c r="G24" s="53" t="str">
         <f aca="false">INDEX($A$19:$A$23,MATCH(MAX(G19:G23),G19:G23,0))</f>
@@ -9383,7 +9380,7 @@
       </c>
       <c r="F25" s="53" t="str">
         <f aca="false">INDEX($A$19:$A$21,MATCH(MAX(F19:F21),F19:F21,0))</f>
-        <v>A3 Door screens + food status (proposal)</v>
+        <v>A2 Door screens, queue information only</v>
       </c>
       <c r="G25" s="53" t="str">
         <f aca="false">INDEX($A$19:$A$21,MATCH(MAX(G19:G21),G19:G21,0))</f>
@@ -9437,23 +9434,23 @@
       </c>
       <c r="B30" s="28" t="n">
         <f aca="false">MAX(B$19:B$23)-B19</f>
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="C30" s="28" t="n">
         <f aca="false">MAX(C$19:C$23)-C19</f>
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="D30" s="28" t="n">
         <f aca="false">MAX(D$19:D$23)-D19</f>
-        <v>11.59</v>
+        <v>11.65</v>
       </c>
       <c r="E30" s="28" t="n">
         <f aca="false">MAX(B30:D30)</f>
-        <v>11.59</v>
+        <v>11.65</v>
       </c>
       <c r="F30" s="28" t="n">
         <f aca="false">SUMPRODUCT(B30:D30,$B$14:$D$14)</f>
-        <v>4.545</v>
+        <v>4.558</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9462,23 +9459,23 @@
       </c>
       <c r="B31" s="28" t="n">
         <f aca="false">MAX(B$19:B$23)-B20</f>
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="C31" s="28" t="n">
         <f aca="false">MAX(C$19:C$23)-C20</f>
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="D31" s="28" t="n">
         <f aca="false">MAX(D$19:D$23)-D20</f>
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="E31" s="28" t="n">
         <f aca="false">MAX(B31:D31)</f>
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="F31" s="28" t="n">
         <f aca="false">SUMPRODUCT(B31:D31,$B$14:$D$14)</f>
-        <v>0.893</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9487,53 +9484,53 @@
       </c>
       <c r="B32" s="28" t="n">
         <f aca="false">MAX(B$19:B$23)-B21</f>
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="C32" s="28" t="n">
         <f aca="false">MAX(C$19:C$23)-C21</f>
-        <v>0.41</v>
+        <v>0.49</v>
       </c>
       <c r="D32" s="28" t="n">
         <f aca="false">MAX(D$19:D$23)-D21</f>
-        <v>0.85</v>
+        <v>0.959999999999999</v>
       </c>
       <c r="E32" s="28" t="n">
         <f aca="false">MAX(B32:D32)</f>
-        <v>0.85</v>
+        <v>0.959999999999999</v>
       </c>
       <c r="F32" s="28" t="n">
         <f aca="false">SUMPRODUCT(B32:D32,$B$14:$D$14)</f>
-        <v>0.468</v>
+        <v>0.536</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B33" s="28" t="n">
         <f aca="false">MAX(B$19:B$23)-B22</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C33" s="28" t="n">
         <f aca="false">MAX(C$19:C$23)-C22</f>
-        <v>0.68</v>
+        <v>0.33</v>
       </c>
       <c r="D33" s="28" t="n">
         <f aca="false">MAX(D$19:D$23)-D22</f>
-        <v>3.97</v>
+        <v>4.28</v>
       </c>
       <c r="E33" s="28" t="n">
         <f aca="false">MAX(B33:D33)</f>
-        <v>3.97</v>
+        <v>4.28</v>
       </c>
       <c r="F33" s="28" t="n">
         <f aca="false">SUMPRODUCT(B33:D33,$B$14:$D$14)</f>
-        <v>1.134</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B34" s="28" t="n">
         <f aca="false">MAX(B$19:B$23)-B23</f>
@@ -9585,7 +9582,7 @@
       </c>
       <c r="B39" s="28" t="n">
         <f aca="false">B14*MAX(B19:B23)+C14*MAX(C19:C23)+D14*MAX(D19:D23)</f>
-        <v>4.545</v>
+        <v>4.558</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9594,7 +9591,7 @@
       </c>
       <c r="B40" s="28" t="n">
         <f aca="false">MAX(I19:I23)</f>
-        <v>4.545</v>
+        <v>4.558</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9833,10 +9830,10 @@
         <v>739</v>
       </c>
       <c r="B23" s="51" t="n">
-        <v>4.38</v>
+        <v>4.31</v>
       </c>
       <c r="C23" s="26" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>740</v>
@@ -9847,7 +9844,7 @@
         <v>741</v>
       </c>
       <c r="B24" s="51" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="C24" s="26" t="n">
         <v>2</v>
@@ -9861,10 +9858,10 @@
         <v>743</v>
       </c>
       <c r="B25" s="51" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="C25" s="26" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>744</v>
@@ -9875,10 +9872,10 @@
         <v>745</v>
       </c>
       <c r="B26" s="51" t="n">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="C26" s="26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>746</v>
@@ -10968,34 +10965,34 @@
         <v>810</v>
       </c>
       <c r="B6" s="51" t="n">
-        <v>4.385</v>
+        <v>4.31</v>
       </c>
       <c r="C6" s="54" t="s">
         <v>676</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>13.472</v>
+        <v>13.906</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>20.935</v>
+        <v>23.94</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>29.805</v>
+        <v>33.212</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>20.935</v>
+        <v>23.94</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>0.654</v>
+        <v>0.658</v>
       </c>
       <c r="I6" s="25" t="n">
-        <v>0.166</v>
+        <v>0.165</v>
       </c>
       <c r="J6" s="25" t="n">
-        <v>1.342</v>
+        <v>1.345</v>
       </c>
       <c r="K6" s="25" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="L6" s="26" t="n">
         <v>0.45</v>
@@ -11015,46 +11012,46 @@
         <v>812</v>
       </c>
       <c r="B7" s="51" t="n">
-        <v>1.299</v>
+        <v>1.191</v>
       </c>
       <c r="C7" s="54" t="s">
         <v>679</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>3.443</v>
+        <v>3.126</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>17.852</v>
+        <v>20.815</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>20.377</v>
+        <v>23.38</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>17.892</v>
+        <v>20.856</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>0.588</v>
+        <v>0.591</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>0.234</v>
+        <v>0.232</v>
       </c>
       <c r="J7" s="25" t="n">
-        <v>1.039</v>
+        <v>1.04</v>
       </c>
       <c r="K7" s="25" t="n">
-        <v>0.683</v>
+        <v>0.684</v>
       </c>
       <c r="L7" s="26" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>239.5</v>
+        <v>239</v>
       </c>
       <c r="N7" s="25" t="n">
-        <v>0.613</v>
+        <v>0.61</v>
       </c>
       <c r="O7" s="25" t="n">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11062,46 +11059,46 @@
         <v>813</v>
       </c>
       <c r="B8" s="51" t="n">
-        <v>0.814</v>
+        <v>0.798</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D8" s="26" t="n">
-        <v>2.247</v>
+        <v>2.104</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>17.365</v>
+        <v>20.423</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>19.166</v>
+        <v>22.423</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>17.414</v>
+        <v>20.467</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>0.576</v>
+        <v>0.584</v>
       </c>
       <c r="I8" s="25" t="n">
-        <v>0.244</v>
+        <v>0.237</v>
       </c>
       <c r="J8" s="25" t="n">
-        <v>1.037</v>
+        <v>1.034</v>
       </c>
       <c r="K8" s="25" t="n">
-        <v>0.697</v>
+        <v>0.688</v>
       </c>
       <c r="L8" s="26" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>286.05</v>
+        <v>260.95</v>
       </c>
       <c r="N8" s="25" t="n">
-        <v>0.609</v>
+        <v>0.612</v>
       </c>
       <c r="O8" s="25" t="n">
-        <v>0.028</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11109,72 +11106,72 @@
         <v>814</v>
       </c>
       <c r="B9" s="51" t="n">
-        <v>0.741</v>
+        <v>0.76</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>815</v>
+        <v>682</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>2.001</v>
+        <v>2.008</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>17.294</v>
+        <v>20.383</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>18.962</v>
+        <v>22.355</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>17.341</v>
+        <v>20.429</v>
       </c>
       <c r="H9" s="25" t="n">
-        <v>0.578</v>
+        <v>0.583</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>0.243</v>
+        <v>0.241</v>
       </c>
       <c r="J9" s="25" t="n">
-        <v>1.032</v>
+        <v>1.035</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>0.692</v>
+        <v>0.697</v>
       </c>
       <c r="L9" s="26" t="n">
         <v>0.5</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>276.95</v>
+        <v>271.3</v>
       </c>
       <c r="N9" s="25" t="n">
-        <v>0.609</v>
+        <v>0.611</v>
       </c>
       <c r="O9" s="25" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B11" s="55" t="n">
         <f aca="false">B8-B6</f>
-        <v>-3.571</v>
+        <v>-3.512</v>
       </c>
       <c r="C11" s="56" t="n">
         <f aca="false">1-B8/B6</f>
-        <v>0.814367160775371</v>
+        <v>0.814849187935035</v>
       </c>
       <c r="D11" s="57" t="n">
         <f aca="false">D8-D6</f>
-        <v>-11.225</v>
+        <v>-11.802</v>
       </c>
       <c r="E11" s="57" t="n">
         <f aca="false">E8-E6</f>
-        <v>-3.57</v>
+        <v>-3.517</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -11193,177 +11190,177 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>820</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="7" t="s">
         <v>821</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>823</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>824</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="H16" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="I16" s="7" t="s">
         <v>826</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="J16" s="7" t="s">
         <v>827</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="K16" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="L16" s="7" t="s">
         <v>829</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="M16" s="7" t="s">
         <v>830</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="58" t="s">
+        <v>831</v>
+      </c>
+      <c r="B17" s="51" t="n">
+        <v>12.046</v>
+      </c>
+      <c r="C17" s="51" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="D17" s="51" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="E17" s="59" t="s">
         <v>832</v>
       </c>
-      <c r="B17" s="51" t="n">
-        <v>11.414</v>
-      </c>
-      <c r="C17" s="51" t="n">
-        <v>2.805</v>
-      </c>
-      <c r="D17" s="51" t="n">
-        <v>2.039</v>
-      </c>
-      <c r="E17" s="59" t="s">
-        <v>833</v>
-      </c>
       <c r="F17" s="26" t="n">
-        <v>30.666</v>
+        <v>32.16</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>5.562</v>
+        <v>5.599</v>
       </c>
       <c r="H17" s="31" t="n">
         <f aca="false">1-D17/B17</f>
-        <v>0.821359733660417</v>
+        <v>0.83206043499917</v>
       </c>
       <c r="I17" s="8" t="str">
-        <f aca="false">IF(D17+0.379&lt;C17-0.515,"Yes",IF(D17&lt;C17,"Tie (within noise)","No"))</f>
+        <f aca="false">IF(D17+0.472&lt;C17-0.385,"Yes",IF(D17&lt;C17,"Tie (within noise)","No"))</f>
         <v>Tie (within noise)</v>
       </c>
       <c r="J17" s="26" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K17" s="26" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="L17" s="25" t="n">
-        <v>0.1</v>
+        <v>0.084</v>
       </c>
       <c r="M17" s="25" t="n">
-        <v>0.077</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="58" t="s">
+        <v>833</v>
+      </c>
+      <c r="B18" s="51" t="n">
+        <v>8.524</v>
+      </c>
+      <c r="C18" s="51" t="n">
+        <v>2.046</v>
+      </c>
+      <c r="D18" s="51" t="n">
+        <v>1.684</v>
+      </c>
+      <c r="E18" s="59" t="s">
         <v>834</v>
       </c>
-      <c r="B18" s="51" t="n">
-        <v>8.855</v>
-      </c>
-      <c r="C18" s="51" t="n">
-        <v>1.931</v>
-      </c>
-      <c r="D18" s="51" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E18" s="59" t="s">
-        <v>835</v>
-      </c>
       <c r="F18" s="26" t="n">
-        <v>23.235</v>
+        <v>22.574</v>
       </c>
       <c r="G18" s="26" t="n">
-        <v>4.83</v>
+        <v>4.395</v>
       </c>
       <c r="H18" s="31" t="n">
         <f aca="false">1-D18/B18</f>
-        <v>0.798983625070582</v>
+        <v>0.802440168934772</v>
       </c>
       <c r="I18" s="8" t="str">
-        <f aca="false">IF(D18+0.186&lt;C18-0.228,"Yes",IF(D18&lt;C18,"Tie (within noise)","No"))</f>
+        <f aca="false">IF(D18+0.138&lt;C18-0.267,"Yes",IF(D18&lt;C18,"Tie (within noise)","No"))</f>
         <v>Tie (within noise)</v>
       </c>
       <c r="J18" s="26" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="K18" s="26" t="n">
         <v>0.75</v>
       </c>
       <c r="L18" s="25" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="M18" s="25" t="n">
-        <v>0.032</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="58" t="s">
+        <v>835</v>
+      </c>
+      <c r="B19" s="51" t="n">
+        <v>5.955</v>
+      </c>
+      <c r="C19" s="51" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="D19" s="51" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="E19" s="59" t="s">
         <v>836</v>
       </c>
-      <c r="B19" s="51" t="n">
-        <v>6.002</v>
-      </c>
-      <c r="C19" s="51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D19" s="51" t="n">
-        <v>1.134</v>
-      </c>
-      <c r="E19" s="59" t="s">
-        <v>675</v>
-      </c>
       <c r="F19" s="26" t="n">
-        <v>19.854</v>
+        <v>19.684</v>
       </c>
       <c r="G19" s="26" t="n">
-        <v>3.471</v>
+        <v>4.504</v>
       </c>
       <c r="H19" s="31" t="n">
         <f aca="false">1-D19/B19</f>
-        <v>0.811062979006998</v>
+        <v>0.774811083123426</v>
       </c>
       <c r="I19" s="8" t="str">
-        <f aca="false">IF(D19+0.144&lt;C19-0.2,"Yes",IF(D19&lt;C19,"Tie (within noise)","No"))</f>
+        <f aca="false">IF(D19+0.362&lt;C19-0.234,"Yes",IF(D19&lt;C19,"Tie (within noise)","No"))</f>
         <v>Tie (within noise)</v>
       </c>
       <c r="J19" s="26" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="K19" s="26" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="L19" s="25" t="n">
-        <v>0.076</v>
+        <v>0.149</v>
       </c>
       <c r="M19" s="25" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11371,42 +11368,42 @@
         <v>837</v>
       </c>
       <c r="B20" s="51" t="n">
-        <v>8.864</v>
+        <v>8.778</v>
       </c>
       <c r="C20" s="51" t="n">
-        <v>1.275</v>
+        <v>1.203</v>
       </c>
       <c r="D20" s="51" t="n">
-        <v>1.289</v>
+        <v>0.953</v>
       </c>
       <c r="E20" s="59" t="s">
         <v>838</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>17.369</v>
+        <v>17.315</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>3.648</v>
+        <v>2.531</v>
       </c>
       <c r="H20" s="31" t="n">
         <f aca="false">1-D20/B20</f>
-        <v>0.854580324909747</v>
+        <v>0.891433128275234</v>
       </c>
       <c r="I20" s="8" t="str">
-        <f aca="false">IF(D20+0.296&lt;C20-0.227,"Yes",IF(D20&lt;C20,"Tie (within noise)","No"))</f>
-        <v>No</v>
+        <f aca="false">IF(D20+0.17&lt;C20-0.298,"Yes",IF(D20&lt;C20,"Tie (within noise)","No"))</f>
+        <v>Tie (within noise)</v>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>0.102</v>
+        <v>0.064</v>
       </c>
       <c r="M20" s="25" t="n">
-        <v>0.063</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11414,42 +11411,42 @@
         <v>839</v>
       </c>
       <c r="B21" s="51" t="n">
-        <v>3.16</v>
+        <v>3.275</v>
       </c>
       <c r="C21" s="51" t="n">
-        <v>0.652</v>
+        <v>0.694</v>
       </c>
       <c r="D21" s="51" t="n">
-        <v>0.621</v>
+        <v>0.56</v>
       </c>
       <c r="E21" s="59" t="s">
         <v>840</v>
       </c>
       <c r="F21" s="26" t="n">
-        <v>11.948</v>
+        <v>12.306</v>
       </c>
       <c r="G21" s="26" t="n">
-        <v>2.043</v>
+        <v>1.903</v>
       </c>
       <c r="H21" s="31" t="n">
         <f aca="false">1-D21/B21</f>
-        <v>0.803481012658228</v>
+        <v>0.829007633587786</v>
       </c>
       <c r="I21" s="8" t="str">
-        <f aca="false">IF(D21+0.076&lt;C21-0.112,"Yes",IF(D21&lt;C21,"Tie (within noise)","No"))</f>
+        <f aca="false">IF(D21+0.069&lt;C21-0.131,"Yes",IF(D21&lt;C21,"Tie (within noise)","No"))</f>
         <v>Tie (within noise)</v>
       </c>
       <c r="J21" s="26" t="n">
         <v>0.5</v>
       </c>
       <c r="K21" s="26" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="L21" s="25" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="M21" s="25" t="n">
-        <v>0.036</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11457,128 +11454,128 @@
         <v>841</v>
       </c>
       <c r="B22" s="51" t="n">
-        <v>1.897</v>
+        <v>1.654</v>
       </c>
       <c r="C22" s="51" t="n">
-        <v>0.904</v>
+        <v>0.851</v>
       </c>
       <c r="D22" s="51" t="n">
-        <v>0.56</v>
+        <v>0.548</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="F22" s="26" t="n">
-        <v>5.744</v>
+        <v>5.023</v>
       </c>
       <c r="G22" s="26" t="n">
-        <v>1.629</v>
+        <v>1.467</v>
       </c>
       <c r="H22" s="31" t="n">
         <f aca="false">1-D22/B22</f>
-        <v>0.70479704797048</v>
+        <v>0.668681983071342</v>
       </c>
       <c r="I22" s="8" t="str">
-        <f aca="false">IF(D22+0.076&lt;C22-0.217,"Yes",IF(D22&lt;C22,"Tie (within noise)","No"))</f>
+        <f aca="false">IF(D22+0.062&lt;C22-0.176,"Yes",IF(D22&lt;C22,"Tie (within noise)","No"))</f>
         <v>Yes</v>
       </c>
       <c r="J22" s="26" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="26" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="L22" s="25" t="n">
-        <v>0.035</v>
+        <v>0.041</v>
       </c>
       <c r="M22" s="25" t="n">
-        <v>0.074</v>
+        <v>0.072</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="58" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B23" s="51" t="n">
-        <v>5.193</v>
+        <v>5.757</v>
       </c>
       <c r="C23" s="51" t="n">
-        <v>1.035</v>
+        <v>1.571</v>
       </c>
       <c r="D23" s="51" t="n">
-        <v>0.857</v>
+        <v>0.879</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F23" s="26" t="n">
-        <v>14.204</v>
+        <v>14.914</v>
       </c>
       <c r="G23" s="26" t="n">
-        <v>2.546</v>
+        <v>2.54</v>
       </c>
       <c r="H23" s="31" t="n">
         <f aca="false">1-D23/B23</f>
-        <v>0.834970152127864</v>
+        <v>0.847316310578426</v>
       </c>
       <c r="I23" s="8" t="str">
-        <f aca="false">IF(D23+0.232&lt;C23-0.327,"Yes",IF(D23&lt;C23,"Tie (within noise)","No"))</f>
-        <v>Tie (within noise)</v>
+        <f aca="false">IF(D23+0.228&lt;C23-0.392,"Yes",IF(D23&lt;C23,"Tie (within noise)","No"))</f>
+        <v>Yes</v>
       </c>
       <c r="J23" s="26" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="K23" s="26" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="L23" s="25" t="n">
-        <v>0.122</v>
+        <v>0.073</v>
       </c>
       <c r="M23" s="25" t="n">
-        <v>0.095</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="58" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B24" s="51" t="n">
-        <v>4.385</v>
+        <v>4.31</v>
       </c>
       <c r="C24" s="51" t="n">
-        <v>1.493</v>
+        <v>1.176</v>
       </c>
       <c r="D24" s="51" t="n">
-        <v>1.001</v>
+        <v>1.104</v>
       </c>
       <c r="E24" s="59" t="s">
-        <v>845</v>
+        <v>675</v>
       </c>
       <c r="F24" s="26" t="n">
-        <v>13.472</v>
+        <v>13.906</v>
       </c>
       <c r="G24" s="26" t="n">
-        <v>2.852</v>
+        <v>3.014</v>
       </c>
       <c r="H24" s="31" t="n">
         <f aca="false">1-D24/B24</f>
-        <v>0.771721778791334</v>
+        <v>0.74385150812065</v>
       </c>
       <c r="I24" s="8" t="str">
-        <f aca="false">IF(D24+0.107&lt;C24-0.32,"Yes",IF(D24&lt;C24,"Tie (within noise)","No"))</f>
-        <v>Yes</v>
+        <f aca="false">IF(D24+0.134&lt;C24-0.293,"Yes",IF(D24&lt;C24,"Tie (within noise)","No"))</f>
+        <v>Tie (within noise)</v>
       </c>
       <c r="J24" s="26" t="n">
         <v>0.45</v>
       </c>
       <c r="K24" s="26" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="L24" s="25" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="M24" s="25" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11586,42 +11583,42 @@
         <v>846</v>
       </c>
       <c r="B25" s="51" t="n">
-        <v>4.385</v>
+        <v>4.31</v>
       </c>
       <c r="C25" s="51" t="n">
-        <v>1.124</v>
+        <v>1.159</v>
       </c>
       <c r="D25" s="51" t="n">
-        <v>0.704</v>
+        <v>0.756</v>
       </c>
       <c r="E25" s="59" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F25" s="26" t="n">
-        <v>13.472</v>
+        <v>13.906</v>
       </c>
       <c r="G25" s="26" t="n">
-        <v>1.873</v>
+        <v>2.004</v>
       </c>
       <c r="H25" s="31" t="n">
         <f aca="false">1-D25/B25</f>
-        <v>0.83945267958951</v>
+        <v>0.824593967517401</v>
       </c>
       <c r="I25" s="8" t="str">
-        <f aca="false">IF(D25+0.085&lt;C25-0.274,"Yes",IF(D25&lt;C25,"Tie (within noise)","No"))</f>
-        <v>Yes</v>
+        <f aca="false">IF(D25+0.103&lt;C25-0.335,"Yes",IF(D25&lt;C25,"Tie (within noise)","No"))</f>
+        <v>Tie (within noise)</v>
       </c>
       <c r="J25" s="26" t="n">
         <v>0.45</v>
       </c>
       <c r="K25" s="26" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="L25" s="25" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="M25" s="25" t="n">
-        <v>0.095</v>
+        <v>0.071</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11629,159 +11626,159 @@
         <v>847</v>
       </c>
       <c r="B26" s="51" t="n">
-        <v>12.878</v>
+        <v>12.883</v>
       </c>
       <c r="C26" s="51" t="n">
-        <v>1.964</v>
+        <v>1.826</v>
       </c>
       <c r="D26" s="51" t="n">
-        <v>1.779</v>
+        <v>1.857</v>
       </c>
       <c r="E26" s="59" t="s">
-        <v>848</v>
+        <v>690</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>33.687</v>
+        <v>33.864</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>4.612</v>
+        <v>4.945</v>
       </c>
       <c r="H26" s="31" t="n">
         <f aca="false">1-D26/B26</f>
-        <v>0.861857431278149</v>
+        <v>0.855856555150198</v>
       </c>
       <c r="I26" s="8" t="str">
-        <f aca="false">IF(D26+0.195&lt;C26-0.308,"Yes",IF(D26&lt;C26,"Tie (within noise)","No"))</f>
-        <v>Tie (within noise)</v>
+        <f aca="false">IF(D26+0.162&lt;C26-0.155,"Yes",IF(D26&lt;C26,"Tie (within noise)","No"))</f>
+        <v>No</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K26" s="26" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="L26" s="25" t="n">
-        <v>0.092</v>
+        <v>0.065</v>
       </c>
       <c r="M26" s="25" t="n">
-        <v>0.064</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="58" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B27" s="51" t="n">
-        <v>2.11</v>
+        <v>1.793</v>
       </c>
       <c r="C27" s="51" t="n">
-        <v>1.178</v>
+        <v>1.031</v>
       </c>
       <c r="D27" s="51" t="n">
-        <v>0.691</v>
+        <v>0.557</v>
       </c>
       <c r="E27" s="59" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>8.165</v>
+        <v>6.807</v>
       </c>
       <c r="G27" s="26" t="n">
-        <v>2.254</v>
+        <v>1.73</v>
       </c>
       <c r="H27" s="31" t="n">
         <f aca="false">1-D27/B27</f>
-        <v>0.672511848341232</v>
+        <v>0.689347462353597</v>
       </c>
       <c r="I27" s="8" t="str">
-        <f aca="false">IF(D27+0.156&lt;C27-0.384,"Yes",IF(D27&lt;C27,"Tie (within noise)","No"))</f>
-        <v>Tie (within noise)</v>
+        <f aca="false">IF(D27+0.056&lt;C27-0.375,"Yes",IF(D27&lt;C27,"Tie (within noise)","No"))</f>
+        <v>Yes</v>
       </c>
       <c r="J27" s="26" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="K27" s="26" t="n">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="L27" s="25" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="M27" s="25" t="n">
-        <v>0.037</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="58" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B28" s="51" t="n">
-        <v>6.397</v>
+        <v>6.524</v>
       </c>
       <c r="C28" s="51" t="n">
-        <v>2.506</v>
+        <v>2.558</v>
       </c>
       <c r="D28" s="51" t="n">
-        <v>0.901</v>
+        <v>0.938</v>
       </c>
       <c r="E28" s="59" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>20.338</v>
+        <v>20.512</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>2.334</v>
+        <v>2.312</v>
       </c>
       <c r="H28" s="31" t="n">
         <f aca="false">1-D28/B28</f>
-        <v>0.859152727841176</v>
+        <v>0.856223175965665</v>
       </c>
       <c r="I28" s="8" t="str">
-        <f aca="false">IF(D28+0.1&lt;C28-0.291,"Yes",IF(D28&lt;C28,"Tie (within noise)","No"))</f>
+        <f aca="false">IF(D28+0.122&lt;C28-0.236,"Yes",IF(D28&lt;C28,"Tie (within noise)","No"))</f>
         <v>Yes</v>
       </c>
       <c r="J28" s="26" t="n">
         <v>2</v>
       </c>
       <c r="K28" s="26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L28" s="25" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="M28" s="25" t="n">
-        <v>0.056</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="58" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B29" s="51" t="n">
-        <v>3.506</v>
+        <v>3.611</v>
       </c>
       <c r="C29" s="51" t="n">
-        <v>0.724</v>
+        <v>0.78</v>
       </c>
       <c r="D29" s="51" t="n">
-        <v>0.73</v>
+        <v>0.762</v>
       </c>
       <c r="E29" s="59" t="s">
-        <v>683</v>
+        <v>852</v>
       </c>
       <c r="F29" s="26" t="n">
-        <v>11.246</v>
+        <v>11.778</v>
       </c>
       <c r="G29" s="26" t="n">
-        <v>2.047</v>
+        <v>2.102</v>
       </c>
       <c r="H29" s="31" t="n">
         <f aca="false">1-D29/B29</f>
-        <v>0.791785510553337</v>
+        <v>0.788978122403766</v>
       </c>
       <c r="I29" s="8" t="str">
-        <f aca="false">IF(D29+0.09&lt;C29-0.076,"Yes",IF(D29&lt;C29,"Tie (within noise)","No"))</f>
-        <v>No</v>
+        <f aca="false">IF(D29+0.092&lt;C29-0.09,"Yes",IF(D29&lt;C29,"Tie (within noise)","No"))</f>
+        <v>Tie (within noise)</v>
       </c>
       <c r="J29" s="26" t="n">
         <v>0</v>
@@ -11790,67 +11787,67 @@
         <v>0</v>
       </c>
       <c r="L29" s="25" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M29" s="25" t="n">
         <v>0.013</v>
-      </c>
-      <c r="M29" s="25" t="n">
-        <v>0.036</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="58" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B30" s="51" t="n">
-        <v>4.385</v>
+        <v>4.31</v>
       </c>
       <c r="C30" s="51" t="n">
-        <v>1.299</v>
+        <v>1.191</v>
       </c>
       <c r="D30" s="51" t="n">
-        <v>0.814</v>
+        <v>0.798</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F30" s="26" t="n">
-        <v>13.472</v>
+        <v>13.906</v>
       </c>
       <c r="G30" s="26" t="n">
-        <v>2.247</v>
+        <v>2.104</v>
       </c>
       <c r="H30" s="31" t="n">
         <f aca="false">1-D30/B30</f>
-        <v>0.814367160775371</v>
+        <v>0.814849187935035</v>
       </c>
       <c r="I30" s="8" t="str">
-        <f aca="false">IF(D30+0.09&lt;C30-0.326,"Yes",IF(D30&lt;C30,"Tie (within noise)","No"))</f>
-        <v>Yes</v>
+        <f aca="false">IF(D30+0.101&lt;C30-0.328,"Yes",IF(D30&lt;C30,"Tie (within noise)","No"))</f>
+        <v>Tie (within noise)</v>
       </c>
       <c r="J30" s="26" t="n">
         <v>0.45</v>
       </c>
       <c r="K30" s="26" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="L30" s="25" t="n">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="M30" s="25" t="n">
-        <v>0.028</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H31" s="60" t="n">
         <f aca="false">MIN(H17:H30)</f>
-        <v>0.672511848341232</v>
+        <v>0.668681983071342</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -11896,7 +11893,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11906,32 +11903,32 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>859</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>860</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>861</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>862</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>863</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B5" s="45" t="n">
         <f aca="false">'S15 Queuing'!$I$51</f>
@@ -11942,112 +11939,112 @@
         <v>0.467940725838283</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
+        <v>866</v>
+      </c>
+      <c r="B6" s="51" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="C6" s="51" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>867</v>
-      </c>
-      <c r="B6" s="51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C6" s="51" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D6" s="26" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
+        <v>868</v>
+      </c>
+      <c r="B7" s="51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C7" s="51" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>869</v>
-      </c>
-      <c r="B7" s="51" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="C7" s="51" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
+        <v>870</v>
+      </c>
+      <c r="B8" s="51" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C8" s="51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>871</v>
-      </c>
-      <c r="B8" s="51" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="C8" s="51" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="D8" s="26" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
+        <v>872</v>
+      </c>
+      <c r="B9" s="51" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="C9" s="51" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>873</v>
-      </c>
-      <c r="B9" s="51" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="C9" s="51" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="D9" s="26" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
+        <v>874</v>
+      </c>
+      <c r="B10" s="51" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="C10" s="51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>875</v>
-      </c>
-      <c r="B10" s="51" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="C10" s="51" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="D10" s="26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B11" s="45" t="n">
         <f aca="false">'LP Student Flow'!$B$44</f>
@@ -12058,30 +12055,30 @@
         <v>0.0440989503378378</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B12" s="61" t="n">
         <f aca="false">B6-B5</f>
-        <v>0.279942993859916</v>
+        <v>0.249942993859916</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B13" s="62" t="n">
         <f aca="false">B12/B6</f>
-        <v>0.0736692089105042</v>
+        <v>0.0662978763554154</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -12119,7 +12116,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12127,18 +12124,18 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
+        <v>883</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>884</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>885</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>886</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>81</v>
@@ -12146,41 +12143,41 @@
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>886</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>887</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>888</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>889</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
+        <v>890</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>891</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>892</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>893</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
+        <v>894</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>895</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>896</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>897</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>20</v>
@@ -12188,13 +12185,13 @@
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>898</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>899</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>900</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>29</v>
@@ -12202,13 +12199,13 @@
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>901</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>902</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>903</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>20</v>
@@ -12216,13 +12213,13 @@
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>904</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>905</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>906</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>20</v>
@@ -12230,41 +12227,41 @@
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>907</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="9" t="s">
         <v>908</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>909</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>911</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="C12" s="9" t="s">
         <v>912</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="D12" s="9" t="s">
         <v>913</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
+        <v>914</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>915</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="9" t="s">
         <v>916</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>917</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>20</v>
@@ -12272,27 +12269,27 @@
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
+        <v>917</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>918</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>919</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>920</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>922</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>923</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>924</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>17</v>
@@ -12300,77 +12297,77 @@
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>925</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
         <v>926</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>927</v>
-      </c>
       <c r="D16" s="9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>928</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="C17" s="9" t="s">
         <v>929</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>930</v>
-      </c>
       <c r="D17" s="9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>931</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9" t="s">
         <v>932</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>933</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
+        <v>934</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>935</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>936</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
+        <v>936</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>937</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="C20" s="9" t="s">
         <v>938</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>939</v>
-      </c>
       <c r="D20" s="9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -12404,7 +12401,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12421,124 +12418,124 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
+        <v>942</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>943</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>944</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>945</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>947</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>948</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>949</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>951</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>952</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>953</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>955</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>956</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>957</v>
-      </c>
       <c r="D7" s="9" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>958</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>959</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>960</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>962</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>963</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>964</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>967</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>968</v>
-      </c>
       <c r="D10" s="9" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>969</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C11" s="9" t="s">
         <v>970</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>971</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -12549,42 +12546,42 @@
         <v>497</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>974</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>975</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>976</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>977</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="G15" s="7" t="s">
         <v>978</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="H15" s="7" t="s">
         <v>979</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="I15" s="7" t="s">
         <v>980</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="J15" s="7" t="s">
         <v>981</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="K15" s="7" t="s">
         <v>982</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="L15" s="7" t="s">
         <v>983</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="54" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B16" s="54" t="n">
         <v>240</v>
@@ -13063,12 +13060,12 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -13087,7 +13084,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -13106,7 +13103,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -13125,7 +13122,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -13144,7 +13141,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -13163,7 +13160,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -13182,7 +13179,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -13201,7 +13198,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -13220,7 +13217,7 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -13281,7 +13278,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -13289,26 +13286,26 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>998</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>999</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B5" s="45" t="n">
         <f aca="false">COUNT(Inputs!$B$5:$B$78)</f>
@@ -13319,12 +13316,12 @@
         <v>OK</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B6" s="45" t="n">
         <f aca="false">SUMPRODUCT(--ISERROR('S15 Queuing'!$A$30:$AN$47))</f>
@@ -13335,12 +13332,12 @@
         <v>OK</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B7" s="45" t="n">
         <f aca="false">SUMPRODUCT(--ISERROR('LP Student Flow'!$A$19:$N$40))</f>
@@ -13354,7 +13351,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B8" s="45" t="n">
         <f aca="false">SUMPRODUCT(--ISERROR('Decision Rule'!$A$14:$T$22))</f>
@@ -13368,7 +13365,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B9" s="45" t="n">
         <f aca="false">SUM('S15 Queuing'!$B$30:$B$47)</f>
@@ -13379,12 +13376,12 @@
         <v>OK</v>
       </c>
       <c r="D9" s="54" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B10" s="45" t="n">
         <f aca="false">SUM('S15 Queuing'!$C$30:$C$47)-Inputs!$B$6</f>
@@ -13395,12 +13392,12 @@
         <v>OK</v>
       </c>
       <c r="D10" s="54" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B11" s="45" t="n">
         <f aca="false">AND(Inputs!$B$34&gt;=0,Inputs!$B$34&lt;=1,Inputs!$B$35&gt;=0,Inputs!$B$35&lt;=1)</f>
@@ -13414,7 +13411,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B12" s="45" t="n">
         <f aca="false">Inputs!$B$71+Inputs!$B$72+Inputs!$B$73</f>
@@ -13425,12 +13422,12 @@
         <v>OK</v>
       </c>
       <c r="D12" s="54" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B13" s="45" t="n">
         <f aca="false">'LP Student Flow'!$B$49</f>
@@ -13441,12 +13438,12 @@
         <v>OK</v>
       </c>
       <c r="D13" s="54" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B14" s="45" t="str">
         <f aca="false">'LP Student Flow'!$B$50</f>
@@ -13457,12 +13454,12 @@
         <v>OK</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B15" s="45" t="str">
         <f aca="false">'LP Student Flow'!$B$48</f>
@@ -13473,12 +13470,12 @@
         <v>OK</v>
       </c>
       <c r="D15" s="54" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B16" s="45" t="n">
         <f aca="false">'LP Student Flow'!$B$43-'LP Student Flow'!$B$44</f>
@@ -13492,7 +13489,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B17" s="45" t="n">
         <f aca="false">IF(17/(2*(1.1*Inputs!$B$26))&lt;1,((17/(1.1*Inputs!$B$26))^2/2*2/(2-17/(1.1*Inputs!$B$26)))/(1+17/(1.1*Inputs!$B$26)+(17/(1.1*Inputs!$B$26))^2/2*2/(2-17/(1.1*Inputs!$B$26)))/(2*(1.1*Inputs!$B$26)-17),99)-IF(17/(2*Inputs!$B$26)&lt;1,((17/Inputs!$B$26)^2/2*2/(2-17/Inputs!$B$26))/(1+17/Inputs!$B$26+(17/Inputs!$B$26)^2/2*2/(2-17/Inputs!$B$26))/(2*Inputs!$B$26-17),99)</f>
@@ -13503,12 +13500,12 @@
         <v>OK</v>
       </c>
       <c r="D17" s="54" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B18" s="45" t="n">
         <f aca="false">'S15 Queuing'!$H$53</f>
@@ -13519,74 +13516,74 @@
         <v>OK</v>
       </c>
       <c r="D18" s="54" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B19" s="45" t="n">
         <f aca="false">Inputs!$B$89</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="C19" s="39" t="str">
         <f aca="false">IF(AND(B19&gt;=Inputs!$B$16-1,B19&lt;=Inputs!$B$17),"OK","CHECK")</f>
         <v>OK</v>
       </c>
       <c r="D19" s="54" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B20" s="51" t="n">
-        <v>16.7</v>
+        <v>19.8</v>
       </c>
       <c r="C20" s="39" t="str">
         <f aca="false">IF(AND(B20&gt;=Inputs!$B$16-1,B20&lt;=Inputs!$B$17),"OK","CHECK")</f>
         <v>OK</v>
       </c>
       <c r="D20" s="54" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B21" s="51" t="n">
-        <v>22.7</v>
+        <v>25.6</v>
       </c>
       <c r="C21" s="39" t="str">
         <f aca="false">IF(AND(B21&gt;=Inputs!$B$16,B21&lt;=Inputs!$B$17+3),"OK","CHECK")</f>
         <v>OK</v>
       </c>
       <c r="D21" s="54" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B22" s="45" t="n">
         <f aca="false">Reconciliation!$B$12</f>
-        <v>0.279942993859916</v>
+        <v>0.249942993859916</v>
       </c>
       <c r="C22" s="39" t="str">
         <f aca="false">IF(ABS(B22)&lt;=0.15*Reconciliation!$B$6,"OK","CHECK")</f>
         <v>OK</v>
       </c>
       <c r="D22" s="54" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B23" s="45" t="n">
         <f aca="false">SUMPRODUCT(--ISERROR('S7 Payoff Matrix'!$A$6:$J$42))</f>
@@ -13600,7 +13597,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B24" s="45" t="n">
         <f aca="false">SUMPRODUCT(--ISERROR('Arrival Curve'!$A$3:$N$40))</f>
@@ -13614,7 +13611,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B25" s="45" t="n">
         <f aca="false">'Arrival Curve'!$B$14-Inputs!$B$6</f>
@@ -13625,12 +13622,12 @@
         <v>OK</v>
       </c>
       <c r="D25" s="54" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C27" s="39" t="str">
         <f aca="false">IF(COUNTIF(C5:C25,"OK")=21,"ALL OK","CHECK")</f>
@@ -13919,14 +13916,14 @@
       <c r="A15" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="17" t="n">
-        <v>18</v>
+      <c r="B15" s="18" t="n">
+        <v>20</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>14</v>
+      <c r="D15" s="13" t="s">
+        <v>17</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>115</v>
@@ -13966,7 +13963,7 @@
         <v>119</v>
       </c>
       <c r="B17" s="18" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>98</v>
@@ -14109,13 +14106,13 @@
         <v>134</v>
       </c>
       <c r="B24" s="18" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>132</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>135</v>
@@ -14132,13 +14129,13 @@
         <v>136</v>
       </c>
       <c r="B25" s="18" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>132</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>120</v>
@@ -14173,18 +14170,18 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
         <v>141</v>
       </c>
       <c r="B27" s="18" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>132</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>142</v>
@@ -14201,13 +14198,13 @@
         <v>143</v>
       </c>
       <c r="B28" s="18" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>132</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>120</v>
@@ -14224,7 +14221,7 @@
         <v>144</v>
       </c>
       <c r="B29" s="18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>98</v>
@@ -14247,7 +14244,7 @@
         <v>146</v>
       </c>
       <c r="B30" s="18" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>98</v>
@@ -15350,7 +15347,7 @@
       </c>
       <c r="B85" s="28" t="n">
         <f aca="false">(Inputs!$B$23+(Inputs!$B$24+Inputs!$B$25)/2)/60</f>
-        <v>0.45</v>
+        <v>0.625</v>
       </c>
       <c r="C85" s="13" t="s">
         <v>98</v>
@@ -15365,7 +15362,7 @@
       </c>
       <c r="B86" s="28" t="n">
         <f aca="false">(Inputs!$B$27+Inputs!$B$28)/2/60</f>
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="C86" s="13" t="s">
         <v>98</v>
@@ -15380,7 +15377,7 @@
       </c>
       <c r="B87" s="28" t="n">
         <f aca="false">(Inputs!$B$29+Inputs!$B$30)/2</f>
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="C87" s="13" t="s">
         <v>98</v>
@@ -15410,7 +15407,7 @@
       </c>
       <c r="B89" s="27" t="n">
         <f aca="false">Inputs!$B$85+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="C89" s="13" t="s">
         <v>98</v>
@@ -15440,7 +15437,7 @@
       </c>
       <c r="B91" s="27" t="n">
         <f aca="false">Inputs!$B$9/Inputs!$B$87</f>
-        <v>66.6666666666667</v>
+        <v>56.25</v>
       </c>
       <c r="C91" s="13" t="s">
         <v>138</v>
@@ -15455,7 +15452,7 @@
       </c>
       <c r="B92" s="27" t="n">
         <f aca="false">Inputs!$B$10/Inputs!$B$87</f>
-        <v>36.4444444444444</v>
+        <v>30.75</v>
       </c>
       <c r="C92" s="13" t="s">
         <v>138</v>
@@ -18548,7 +18545,7 @@
       </c>
       <c r="L30" s="43" t="n">
         <f aca="false">Inputs!$B$85+K30+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="M30" s="32" t="n">
         <f aca="false">E30*L30</f>
@@ -18584,7 +18581,7 @@
       </c>
       <c r="U30" s="43" t="n">
         <f aca="false">Inputs!$B$85+T30+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="V30" s="32" t="n">
         <f aca="false">N30*U30</f>
@@ -18620,7 +18617,7 @@
       </c>
       <c r="AD30" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC30+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AE30" s="32" t="n">
         <f aca="false">W30*AD30</f>
@@ -18656,7 +18653,7 @@
       </c>
       <c r="AM30" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL30+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AN30" s="32" t="n">
         <f aca="false">AF30*AM30</f>
@@ -18709,7 +18706,7 @@
       </c>
       <c r="L31" s="43" t="n">
         <f aca="false">Inputs!$B$85+K31+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="M31" s="32" t="n">
         <f aca="false">E31*L31</f>
@@ -18745,7 +18742,7 @@
       </c>
       <c r="U31" s="43" t="n">
         <f aca="false">Inputs!$B$85+T31+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="V31" s="32" t="n">
         <f aca="false">N31*U31</f>
@@ -18781,7 +18778,7 @@
       </c>
       <c r="AD31" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC31+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AE31" s="32" t="n">
         <f aca="false">W31*AD31</f>
@@ -18817,7 +18814,7 @@
       </c>
       <c r="AM31" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL31+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AN31" s="32" t="n">
         <f aca="false">AF31*AM31</f>
@@ -18870,7 +18867,7 @@
       </c>
       <c r="L32" s="43" t="n">
         <f aca="false">Inputs!$B$85+K32+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="M32" s="32" t="n">
         <f aca="false">E32*L32</f>
@@ -18906,7 +18903,7 @@
       </c>
       <c r="U32" s="43" t="n">
         <f aca="false">Inputs!$B$85+T32+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="V32" s="32" t="n">
         <f aca="false">N32*U32</f>
@@ -18942,7 +18939,7 @@
       </c>
       <c r="AD32" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC32+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AE32" s="32" t="n">
         <f aca="false">W32*AD32</f>
@@ -18978,7 +18975,7 @@
       </c>
       <c r="AM32" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL32+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AN32" s="32" t="n">
         <f aca="false">AF32*AM32</f>
@@ -19031,11 +19028,11 @@
       </c>
       <c r="L33" s="43" t="n">
         <f aca="false">Inputs!$B$85+K33+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.6597416095262</v>
+        <v>19.7347416095262</v>
       </c>
       <c r="M33" s="32" t="n">
         <f aca="false">E33*L33</f>
-        <v>241.01363978786</v>
+        <v>285.499140206659</v>
       </c>
       <c r="N33" s="43" t="n">
         <f aca="false">$D33*(1-Inputs!$B$34)</f>
@@ -19067,11 +19064,11 @@
       </c>
       <c r="U33" s="43" t="n">
         <f aca="false">Inputs!$B$85+T33+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5535136607706</v>
+        <v>19.6285136607707</v>
       </c>
       <c r="V33" s="32" t="n">
         <f aca="false">N33*U33</f>
-        <v>60.9959877158977</v>
+        <v>72.3266735189294</v>
       </c>
       <c r="W33" s="43" t="n">
         <f aca="false">$D33*$E$26</f>
@@ -19103,11 +19100,11 @@
       </c>
       <c r="AD33" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC33+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5960720939758</v>
+        <v>19.6710720939758</v>
       </c>
       <c r="AE33" s="32" t="n">
         <f aca="false">W33*AD33</f>
-        <v>186.410622438791</v>
+        <v>220.94967847286</v>
       </c>
       <c r="AF33" s="43" t="n">
         <f aca="false">$D33*(1-$E$26)</f>
@@ -19139,11 +19136,11 @@
       </c>
       <c r="AM33" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL33+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.563596987014</v>
+        <v>19.638596987014</v>
       </c>
       <c r="AN33" s="32" t="n">
         <f aca="false">AF33*AM33</f>
-        <v>114.610019339941</v>
+        <v>135.887149527703</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19192,11 +19189,11 @@
       </c>
       <c r="L34" s="43" t="n">
         <f aca="false">Inputs!$B$85+K34+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>17.1339691805587</v>
+        <v>20.2089691805587</v>
       </c>
       <c r="M34" s="32" t="n">
         <f aca="false">E34*L34</f>
-        <v>316.639196130402</v>
+        <v>373.46581451873</v>
       </c>
       <c r="N34" s="43" t="n">
         <f aca="false">$D34*(1-Inputs!$B$34)</f>
@@ -19228,11 +19225,11 @@
       </c>
       <c r="U34" s="43" t="n">
         <f aca="false">Inputs!$B$85+T34+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5558637593689</v>
+        <v>19.6308637593689</v>
       </c>
       <c r="V34" s="32" t="n">
         <f aca="false">N34*U34</f>
-        <v>77.9284885982557</v>
+        <v>92.4025206344296</v>
       </c>
       <c r="W34" s="43" t="n">
         <f aca="false">$D34*$E$26</f>
@@ -19264,11 +19261,11 @@
       </c>
       <c r="AD34" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC34+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.6560496517009</v>
+        <v>19.7310496517009</v>
       </c>
       <c r="AE34" s="32" t="n">
         <f aca="false">W34*AD34</f>
-        <v>238.985022135422</v>
+        <v>283.105864618104</v>
       </c>
       <c r="AF34" s="43" t="n">
         <f aca="false">$D34*(1-$E$26)</f>
@@ -19300,11 +19297,11 @@
       </c>
       <c r="AM34" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL34+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5742727126062</v>
+        <v>19.6492727126062</v>
       </c>
       <c r="AN34" s="32" t="n">
         <f aca="false">AF34*AM34</f>
-        <v>146.499365562272</v>
+        <v>173.679173504092</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19353,11 +19350,11 @@
       </c>
       <c r="L35" s="43" t="n">
         <f aca="false">Inputs!$B$85+K35+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>17.1339691805587</v>
+        <v>20.2089691805587</v>
       </c>
       <c r="M35" s="32" t="n">
         <f aca="false">E35*L35</f>
-        <v>316.639196130402</v>
+        <v>373.46581451873</v>
       </c>
       <c r="N35" s="43" t="n">
         <f aca="false">$D35*(1-Inputs!$B$34)</f>
@@ -19389,11 +19386,11 @@
       </c>
       <c r="U35" s="43" t="n">
         <f aca="false">Inputs!$B$85+T35+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5558637593689</v>
+        <v>19.6308637593689</v>
       </c>
       <c r="V35" s="32" t="n">
         <f aca="false">N35*U35</f>
-        <v>77.9284885982557</v>
+        <v>92.4025206344296</v>
       </c>
       <c r="W35" s="43" t="n">
         <f aca="false">$D35*$E$26</f>
@@ -19425,11 +19422,11 @@
       </c>
       <c r="AD35" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC35+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.6560496517009</v>
+        <v>19.7310496517009</v>
       </c>
       <c r="AE35" s="32" t="n">
         <f aca="false">W35*AD35</f>
-        <v>238.985022135422</v>
+        <v>283.105864618104</v>
       </c>
       <c r="AF35" s="43" t="n">
         <f aca="false">$D35*(1-$E$26)</f>
@@ -19461,11 +19458,11 @@
       </c>
       <c r="AM35" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL35+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5742727126062</v>
+        <v>19.6492727126062</v>
       </c>
       <c r="AN35" s="32" t="n">
         <f aca="false">AF35*AM35</f>
-        <v>146.499365562272</v>
+        <v>173.679173504092</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19514,11 +19511,11 @@
       </c>
       <c r="L36" s="43" t="n">
         <f aca="false">Inputs!$B$85+K36+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>17.8972050542308</v>
+        <v>20.9722050542308</v>
       </c>
       <c r="M36" s="32" t="n">
         <f aca="false">E36*L36</f>
-        <v>406.166511295945</v>
+        <v>475.951822379465</v>
       </c>
       <c r="N36" s="43" t="n">
         <f aca="false">$D36*(1-Inputs!$B$34)</f>
@@ -19550,11 +19547,11 @@
       </c>
       <c r="U36" s="43" t="n">
         <f aca="false">Inputs!$B$85+T36+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5591145654188</v>
+        <v>19.6341145654188</v>
       </c>
       <c r="V36" s="32" t="n">
         <f aca="false">N36*U36</f>
-        <v>95.7180243501437</v>
+        <v>113.49270207907</v>
       </c>
       <c r="W36" s="43" t="n">
         <f aca="false">$D36*$E$26</f>
@@ -19586,11 +19583,11 @@
       </c>
       <c r="AD36" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC36+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.8967851902105</v>
+        <v>19.9717851902105</v>
       </c>
       <c r="AE36" s="32" t="n">
         <f aca="false">W36*AD36</f>
-        <v>297.724767801769</v>
+        <v>351.906888878911</v>
       </c>
       <c r="AF36" s="43" t="n">
         <f aca="false">$D36*(1-$E$26)</f>
@@ -19622,11 +19619,11 @@
       </c>
       <c r="AM36" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL36+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5917545700771</v>
+        <v>19.6667545700771</v>
       </c>
       <c r="AN36" s="32" t="n">
         <f aca="false">AF36*AM36</f>
-        <v>180.096712044444</v>
+        <v>213.474579779748</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19675,11 +19672,11 @@
       </c>
       <c r="L37" s="43" t="n">
         <f aca="false">Inputs!$B$85+K37+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>18.2705158968729</v>
+        <v>21.3455158968729</v>
       </c>
       <c r="M37" s="32" t="n">
         <f aca="false">E37*L37</f>
-        <v>379.051481307396</v>
+        <v>442.847342989645</v>
       </c>
       <c r="N37" s="43" t="n">
         <f aca="false">$D37*(1-Inputs!$B$34)</f>
@@ -19711,11 +19708,11 @@
       </c>
       <c r="U37" s="43" t="n">
         <f aca="false">Inputs!$B$85+T37+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5575047804871</v>
+        <v>19.6325047804871</v>
       </c>
       <c r="V37" s="32" t="n">
         <f aca="false">N37*U37</f>
-        <v>87.49434681281</v>
+        <v>103.743480967762</v>
       </c>
       <c r="W37" s="43" t="n">
         <f aca="false">$D37*$E$26</f>
@@ -19747,11 +19744,11 @@
       </c>
       <c r="AD37" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC37+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.7346265567137</v>
+        <v>19.8096265567137</v>
       </c>
       <c r="AE37" s="32" t="n">
         <f aca="false">W37*AD37</f>
-        <v>269.559968249515</v>
+        <v>319.091811673575</v>
       </c>
       <c r="AF37" s="43" t="n">
         <f aca="false">$D37*(1-$E$26)</f>
@@ -19783,11 +19780,11 @@
       </c>
       <c r="AM37" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL37+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.582654786645</v>
+        <v>19.657654786645</v>
       </c>
       <c r="AN37" s="32" t="n">
         <f aca="false">AF37*AM37</f>
-        <v>164.549292006309</v>
+        <v>195.06244441945</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19836,11 +19833,11 @@
       </c>
       <c r="L38" s="43" t="n">
         <f aca="false">Inputs!$B$85+K38+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>17.1544283285738</v>
+        <v>20.2294283285738</v>
       </c>
       <c r="M38" s="32" t="n">
         <f aca="false">E38*L38</f>
-        <v>295.053098112662</v>
+        <v>347.942547957235</v>
       </c>
       <c r="N38" s="43" t="n">
         <f aca="false">$D38*(1-Inputs!$B$34)</f>
@@ -19872,11 +19869,11 @@
       </c>
       <c r="U38" s="43" t="n">
         <f aca="false">Inputs!$B$85+T38+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5550398473499</v>
+        <v>19.6300398473499</v>
       </c>
       <c r="V38" s="32" t="n">
         <f aca="false">N38*U38</f>
-        <v>72.5256911733265</v>
+        <v>85.996906127465</v>
       </c>
       <c r="W38" s="43" t="n">
         <f aca="false">$D38*$E$26</f>
@@ -19908,11 +19905,11 @@
       </c>
       <c r="AD38" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC38+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.6304508934148</v>
+        <v>19.7054508934148</v>
       </c>
       <c r="AE38" s="32" t="n">
         <f aca="false">W38*AD38</f>
-        <v>222.085363422687</v>
+        <v>263.14934280013</v>
       </c>
       <c r="AF38" s="43" t="n">
         <f aca="false">$D38*(1-$E$26)</f>
@@ -19944,11 +19941,11 @@
       </c>
       <c r="AM38" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL38+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5703645944355</v>
+        <v>19.6453645944355</v>
       </c>
       <c r="AN38" s="32" t="n">
         <f aca="false">AF38*AM38</f>
-        <v>136.317170881681</v>
+        <v>161.61385630295</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19997,11 +19994,11 @@
       </c>
       <c r="L39" s="43" t="n">
         <f aca="false">Inputs!$B$85+K39+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>18.3919018799548</v>
+        <v>21.4669018799548</v>
       </c>
       <c r="M39" s="32" t="n">
         <f aca="false">E39*L39</f>
-        <v>423.803691581948</v>
+        <v>494.660765533328</v>
       </c>
       <c r="N39" s="43" t="n">
         <f aca="false">$D39*(1-Inputs!$B$34)</f>
@@ -20033,11 +20030,11 @@
       </c>
       <c r="U39" s="43" t="n">
         <f aca="false">Inputs!$B$85+T39+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5594232624957</v>
+        <v>19.6344232624957</v>
       </c>
       <c r="V39" s="32" t="n">
         <f aca="false">N39*U39</f>
-        <v>97.1898736426973</v>
+        <v>115.237534887528</v>
       </c>
       <c r="W39" s="43" t="n">
         <f aca="false">$D39*$E$26</f>
@@ -20069,11 +20066,11 @@
       </c>
       <c r="AD39" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC39+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.9505079637441</v>
+        <v>20.0255079637441</v>
       </c>
       <c r="AE39" s="32" t="n">
         <f aca="false">W39*AD39</f>
-        <v>303.258369140673</v>
+        <v>358.272619280088</v>
       </c>
       <c r="AF39" s="43" t="n">
         <f aca="false">$D39*(1-$E$26)</f>
@@ -20105,11 +20102,11 @@
       </c>
       <c r="AM39" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL39+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5936105672289</v>
+        <v>19.6686105672289</v>
       </c>
       <c r="AN39" s="32" t="n">
         <f aca="false">AF39*AM39</f>
-        <v>182.883092997384</v>
+        <v>216.77357805418</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20158,11 +20155,11 @@
       </c>
       <c r="L40" s="43" t="n">
         <f aca="false">Inputs!$B$85+K40+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>23.3100465027</v>
+        <v>26.3850465027</v>
       </c>
       <c r="M40" s="32" t="n">
         <f aca="false">E40*L40</f>
-        <v>695.485289780386</v>
+        <v>787.231879210269</v>
       </c>
       <c r="N40" s="43" t="n">
         <f aca="false">$D40*(1-Inputs!$B$34)</f>
@@ -20194,11 +20191,11 @@
       </c>
       <c r="U40" s="43" t="n">
         <f aca="false">Inputs!$B$85+T40+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5668742235269</v>
+        <v>19.6418742235269</v>
       </c>
       <c r="V40" s="32" t="n">
         <f aca="false">N40*U40</f>
-        <v>125.899237639952</v>
+        <v>149.267565938906</v>
       </c>
       <c r="W40" s="43" t="n">
         <f aca="false">$D40*$E$26</f>
@@ -20230,11 +20227,11 @@
       </c>
       <c r="AD40" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC40+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>18.1326196895291</v>
+        <v>21.2076196895291</v>
       </c>
       <c r="AE40" s="32" t="n">
         <f aca="false">W40*AD40</f>
-        <v>420.046475677366</v>
+        <v>491.27958676797</v>
       </c>
       <c r="AF40" s="43" t="n">
         <f aca="false">$D40*(1-$E$26)</f>
@@ -20266,11 +20263,11 @@
       </c>
       <c r="AM40" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL40+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.6537150991796</v>
+        <v>19.7287150991796</v>
       </c>
       <c r="AN40" s="32" t="n">
         <f aca="false">AF40*AM40</f>
-        <v>237.656944972492</v>
+        <v>281.538751610724</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20319,11 +20316,11 @@
       </c>
       <c r="L41" s="43" t="n">
         <f aca="false">Inputs!$B$85+K41+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>27.4594522651827</v>
+        <v>30.5344522651827</v>
       </c>
       <c r="M41" s="32" t="n">
         <f aca="false">E41*L41</f>
-        <v>777.069864231186</v>
+        <v>864.088709670455</v>
       </c>
       <c r="N41" s="43" t="n">
         <f aca="false">$D41*(1-Inputs!$B$34)</f>
@@ -20355,11 +20352,11 @@
       </c>
       <c r="U41" s="43" t="n">
         <f aca="false">Inputs!$B$85+T41+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5649270542156</v>
+        <v>19.6399270542156</v>
       </c>
       <c r="V41" s="32" t="n">
         <f aca="false">N41*U41</f>
-        <v>119.397557054336</v>
+        <v>141.561704637989</v>
       </c>
       <c r="W41" s="43" t="n">
         <f aca="false">$D41*$E$26</f>
@@ -20391,11 +20388,11 @@
       </c>
       <c r="AD41" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC41+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>19.1183816541769</v>
+        <v>22.1933816541769</v>
       </c>
       <c r="AE41" s="32" t="n">
         <f aca="false">W41*AD41</f>
-        <v>420.059980004152</v>
+        <v>487.622416086736</v>
       </c>
       <c r="AF41" s="43" t="n">
         <f aca="false">$D41*(1-$E$26)</f>
@@ -20427,11 +20424,11 @@
       </c>
       <c r="AM41" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL41+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.6345018684211</v>
+        <v>19.7095018684211</v>
       </c>
       <c r="AN41" s="32" t="n">
         <f aca="false">AF41*AM41</f>
-        <v>225.150319410983</v>
+        <v>266.770876351321</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20480,11 +20477,11 @@
       </c>
       <c r="L42" s="43" t="n">
         <f aca="false">Inputs!$B$85+K42+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>28.2031998634237</v>
+        <v>31.2781998634237</v>
       </c>
       <c r="M42" s="32" t="n">
         <f aca="false">E42*L42</f>
-        <v>606.016121590738</v>
+        <v>672.090169319921</v>
       </c>
       <c r="N42" s="43" t="n">
         <f aca="false">$D42*(1-Inputs!$B$34)</f>
@@ -20516,11 +20513,11 @@
       </c>
       <c r="U42" s="43" t="n">
         <f aca="false">Inputs!$B$85+T42+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5580945120182</v>
+        <v>19.6330945120182</v>
       </c>
       <c r="V42" s="32" t="n">
         <f aca="false">N42*U42</f>
-        <v>90.622046658528</v>
+        <v>107.451446519286</v>
       </c>
       <c r="W42" s="43" t="n">
         <f aca="false">$D42*$E$26</f>
@@ -20552,11 +20549,11 @@
       </c>
       <c r="AD42" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC42+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>17.6887016884115</v>
+        <v>20.7637016884115</v>
       </c>
       <c r="AE42" s="32" t="n">
         <f aca="false">W42*AD42</f>
-        <v>295.103074425606</v>
+        <v>346.403727794261</v>
       </c>
       <c r="AF42" s="43" t="n">
         <f aca="false">$D42*(1-$E$26)</f>
@@ -20588,11 +20585,11 @@
       </c>
       <c r="AM42" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL42+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5858804309519</v>
+        <v>19.6608804309519</v>
       </c>
       <c r="AN42" s="32" t="n">
         <f aca="false">AF42*AM42</f>
-        <v>170.458590646573</v>
+        <v>202.061384867858</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20641,11 +20638,11 @@
       </c>
       <c r="L43" s="43" t="n">
         <f aca="false">Inputs!$B$85+K43+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>25.2846575519284</v>
+        <v>28.3596575519284</v>
       </c>
       <c r="M43" s="32" t="n">
         <f aca="false">E43*L43</f>
-        <v>353.283437270397</v>
+        <v>396.2480915227</v>
       </c>
       <c r="N43" s="43" t="n">
         <f aca="false">$D43*(1-Inputs!$B$34)</f>
@@ -20677,11 +20674,11 @@
       </c>
       <c r="U43" s="43" t="n">
         <f aca="false">Inputs!$B$85+T43+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5532697999257</v>
+        <v>19.6282697999257</v>
       </c>
       <c r="V43" s="32" t="n">
         <f aca="false">N43*U43</f>
-        <v>58.9098221096896</v>
+        <v>69.8531405704392</v>
       </c>
       <c r="W43" s="43" t="n">
         <f aca="false">$D43*$E$26</f>
@@ -20713,11 +20710,11 @@
       </c>
       <c r="AD43" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC43+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5916850607775</v>
+        <v>19.6666850607775</v>
       </c>
       <c r="AE43" s="32" t="n">
         <f aca="false">W43*AD43</f>
-        <v>179.990125689672</v>
+        <v>213.348379204509</v>
       </c>
       <c r="AF43" s="43" t="n">
         <f aca="false">$D43*(1-$E$26)</f>
@@ -20749,11 +20746,11 @@
       </c>
       <c r="AM43" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL43+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.562568336518</v>
+        <v>19.637568336518</v>
       </c>
       <c r="AN43" s="32" t="n">
         <f aca="false">AF43*AM43</f>
-        <v>110.684919842829</v>
+        <v>131.234639041045</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20802,11 +20799,11 @@
       </c>
       <c r="L44" s="43" t="n">
         <f aca="false">Inputs!$B$85+K44+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>18.8073030190101</v>
+        <v>21.8823030190101</v>
       </c>
       <c r="M44" s="32" t="n">
         <f aca="false">E44*L44</f>
-        <v>135.527745991999</v>
+        <v>157.686575384185</v>
       </c>
       <c r="N44" s="43" t="n">
         <f aca="false">$D44*(1-Inputs!$B$34)</f>
@@ -20838,11 +20835,11 @@
       </c>
       <c r="U44" s="43" t="n">
         <f aca="false">Inputs!$B$85+T44+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5508493603374</v>
+        <v>19.6258493603374</v>
       </c>
       <c r="V44" s="32" t="n">
         <f aca="false">N44*U44</f>
-        <v>30.3780362522521</v>
+        <v>36.0220040899106</v>
       </c>
       <c r="W44" s="43" t="n">
         <f aca="false">$D44*$E$26</f>
@@ -20874,11 +20871,11 @@
       </c>
       <c r="AD44" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC44+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5584901989848</v>
+        <v>19.6334901989848</v>
       </c>
       <c r="AE44" s="32" t="n">
         <f aca="false">W44*AD44</f>
-        <v>92.6433845056982</v>
+        <v>109.847755431526</v>
       </c>
       <c r="AF44" s="43" t="n">
         <f aca="false">$D44*(1-$E$26)</f>
@@ -20910,11 +20907,11 @@
       </c>
       <c r="AM44" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL44+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.5530607353099</v>
+        <v>19.6280607353099</v>
       </c>
       <c r="AN44" s="32" t="n">
         <f aca="false">AF44*AM44</f>
-        <v>57.0524859541779</v>
+        <v>67.6509122581948</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20963,7 +20960,7 @@
       </c>
       <c r="L45" s="43" t="n">
         <f aca="false">Inputs!$B$85+K45+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="M45" s="32" t="n">
         <f aca="false">E45*L45</f>
@@ -20999,7 +20996,7 @@
       </c>
       <c r="U45" s="43" t="n">
         <f aca="false">Inputs!$B$85+T45+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="V45" s="32" t="n">
         <f aca="false">N45*U45</f>
@@ -21035,7 +21032,7 @@
       </c>
       <c r="AD45" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC45+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AE45" s="32" t="n">
         <f aca="false">W45*AD45</f>
@@ -21071,7 +21068,7 @@
       </c>
       <c r="AM45" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL45+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AN45" s="32" t="n">
         <f aca="false">AF45*AM45</f>
@@ -21124,7 +21121,7 @@
       </c>
       <c r="L46" s="43" t="n">
         <f aca="false">Inputs!$B$85+K46+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="M46" s="32" t="n">
         <f aca="false">E46*L46</f>
@@ -21160,7 +21157,7 @@
       </c>
       <c r="U46" s="43" t="n">
         <f aca="false">Inputs!$B$85+T46+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="V46" s="32" t="n">
         <f aca="false">N46*U46</f>
@@ -21196,7 +21193,7 @@
       </c>
       <c r="AD46" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC46+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AE46" s="32" t="n">
         <f aca="false">W46*AD46</f>
@@ -21232,7 +21229,7 @@
       </c>
       <c r="AM46" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL46+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AN46" s="32" t="n">
         <f aca="false">AF46*AM46</f>
@@ -21285,7 +21282,7 @@
       </c>
       <c r="L47" s="43" t="n">
         <f aca="false">Inputs!$B$85+K47+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="M47" s="32" t="n">
         <f aca="false">E47*L47</f>
@@ -21321,7 +21318,7 @@
       </c>
       <c r="U47" s="43" t="n">
         <f aca="false">Inputs!$B$85+T47+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="V47" s="32" t="n">
         <f aca="false">N47*U47</f>
@@ -21357,7 +21354,7 @@
       </c>
       <c r="AD47" s="43" t="n">
         <f aca="false">Inputs!$B$85+AC47+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AE47" s="32" t="n">
         <f aca="false">W47*AD47</f>
@@ -21393,7 +21390,7 @@
       </c>
       <c r="AM47" s="43" t="n">
         <f aca="false">Inputs!$B$85+AL47+1/Inputs!$B$26+Inputs!$B$86+Inputs!$B$87+Inputs!$B$88</f>
-        <v>16.55</v>
+        <v>19.625</v>
       </c>
       <c r="AN47" s="32" t="n">
         <f aca="false">AF47*AM47</f>
@@ -21472,27 +21469,27 @@
       <c r="D52" s="5"/>
       <c r="E52" s="27" t="n">
         <f aca="false">SUMPRODUCT(L30:L47,E30:E47)/SUM(E30:E47)</f>
-        <v>20.9643819441627</v>
+        <v>24.0393819441627</v>
       </c>
       <c r="F52" s="27" t="n">
         <f aca="false">SUMPRODUCT(U30:U47,N30:N47)/SUM(N30:N47)</f>
-        <v>16.5588403775487</v>
+        <v>19.6338403775487</v>
       </c>
       <c r="G52" s="27" t="n">
         <f aca="false">SUMPRODUCT(AD30:AD47,W30:W47)/SUM(W30:W47)</f>
-        <v>17.2787138993233</v>
+        <v>20.3537138993233</v>
       </c>
       <c r="H52" s="27" t="n">
         <f aca="false">SUMPRODUCT(AM30:AM47,AF30:AF47)/SUM(AF30:AF47)</f>
-        <v>16.5946289741265</v>
+        <v>19.6696289741265</v>
       </c>
       <c r="I52" s="47" t="n">
         <f aca="false">(E52*SUM(E30:E47)+F52*SUM(N30:N47))/SUM(D30:D47)</f>
-        <v>20.0700570061401</v>
+        <v>23.1450570061401</v>
       </c>
       <c r="J52" s="47" t="n">
         <f aca="false">(G52*SUM(W30:W47)+H52*SUM(AF30:AF47))/SUM(D30:D47)</f>
-        <v>17.0179407258383</v>
+        <v>20.0929407258383</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21600,19 +21597,19 @@
       <c r="D57" s="5"/>
       <c r="E57" s="32" t="n">
         <f aca="false">MAX(M30:M47)</f>
-        <v>777.069864231186</v>
+        <v>864.088709670455</v>
       </c>
       <c r="F57" s="32" t="n">
         <f aca="false">MAX(V30:V47)</f>
-        <v>125.899237639952</v>
+        <v>149.267565938906</v>
       </c>
       <c r="G57" s="32" t="n">
         <f aca="false">MAX(AE30:AE47)</f>
-        <v>420.059980004152</v>
+        <v>491.27958676797</v>
       </c>
       <c r="H57" s="32" t="n">
         <f aca="false">MAX(AN30:AN47)</f>
-        <v>237.656944972492</v>
+        <v>281.538751610724</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
